--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -1182,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M232"/>
+  <dimension ref="A1:M234"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="10.75" customWidth="1" style="56" min="1" max="1"/>
@@ -1456,78 +1456,68 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="n">
-        <v>10100001</v>
-      </c>
-      <c r="B6" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="55" t="n">
-        <v>1500001</v>
-      </c>
-      <c r="G6" s="55" t="inlineStr">
-        <is>
-          <t>Human_Atlas_Hat_Hat_1</t>
-        </is>
-      </c>
-      <c r="K6" s="55" t="n">
-        <v>10100001</v>
-      </c>
-      <c r="L6" s="55" t="inlineStr">
-        <is>
-          <t>钢头盔-------------------------------</t>
-        </is>
-      </c>
-      <c r="M6" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+      <c r="A6" t="n">
+        <v>200002</v>
+      </c>
+      <c r="B6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Item_TransformPotion_1</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>200002</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>幻化药(对生物使用替换spine形象,以最后吃的为准,Portrait优先,Mod移除后失效)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="n">
-        <v>10100002</v>
-      </c>
-      <c r="B7" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="55" t="n">
-        <v>1500002</v>
-      </c>
-      <c r="G7" s="55" t="inlineStr">
-        <is>
-          <t>Human_Atlas_Hat_Hat_2</t>
-        </is>
-      </c>
-      <c r="K7" s="55" t="n">
-        <v>10100002</v>
-      </c>
-      <c r="L7" s="55" t="inlineStr">
-        <is>
-          <t>大魔法师帽</t>
-        </is>
-      </c>
-      <c r="M7" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+      <c r="A7" t="n">
+        <v>200003</v>
+      </c>
+      <c r="B7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Item_RestorePotion_1</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>200003</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>幻原药(清除幻化,恢复原本形象)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="55" t="n">
-        <v>10100003</v>
+        <v>10100001</v>
       </c>
       <c r="B8" s="55" t="n">
         <v>1</v>
@@ -1539,26 +1529,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="55" t="n">
-        <v>1500003</v>
+        <v>1500001</v>
       </c>
       <c r="G8" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_3</t>
+          <t>Human_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K8" s="55" t="n">
-        <v>10100003</v>
+        <v>10100001</v>
       </c>
       <c r="L8" s="55" t="inlineStr">
         <is>
-          <t>铁头盔</t>
-        </is>
-      </c>
-      <c r="M8" s="55" t="inlineStr"/>
+          <t>钢头盔-------------------------------</t>
+        </is>
+      </c>
+      <c r="M8" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="55" t="n">
-        <v>10100004</v>
+        <v>10100002</v>
       </c>
       <c r="B9" s="55" t="n">
         <v>1</v>
@@ -1570,25 +1564,30 @@
         <v>1</v>
       </c>
       <c r="F9" s="55" t="n">
-        <v>1500004</v>
+        <v>1500002</v>
       </c>
       <c r="G9" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_4</t>
+          <t>Human_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K9" s="55" t="n">
-        <v>10100004</v>
+        <v>10100002</v>
       </c>
       <c r="L9" s="55" t="inlineStr">
         <is>
-          <t>射手兜帽</t>
+          <t>大魔法师帽</t>
+        </is>
+      </c>
+      <c r="M9" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="55" t="n">
-        <v>10100005</v>
+        <v>10100003</v>
       </c>
       <c r="B10" s="55" t="n">
         <v>1</v>
@@ -1600,30 +1599,26 @@
         <v>1</v>
       </c>
       <c r="F10" s="55" t="n">
-        <v>1500005</v>
+        <v>1500003</v>
       </c>
       <c r="G10" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_5</t>
+          <t>Human_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K10" s="55" t="n">
-        <v>10100005</v>
+        <v>10100003</v>
       </c>
       <c r="L10" s="55" t="inlineStr">
         <is>
-          <t>魔法师帽</t>
-        </is>
-      </c>
-      <c r="M10" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>铁头盔</t>
+        </is>
+      </c>
+      <c r="M10" s="55" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="55" t="n">
-        <v>10100007</v>
+        <v>10100004</v>
       </c>
       <c r="B11" s="55" t="n">
         <v>1</v>
@@ -1635,30 +1630,25 @@
         <v>1</v>
       </c>
       <c r="F11" s="55" t="n">
-        <v>1500007</v>
+        <v>1500004</v>
       </c>
       <c r="G11" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_7</t>
+          <t>Human_Atlas_Hat_Hat_4</t>
         </is>
       </c>
       <c r="K11" s="55" t="n">
-        <v>10100007</v>
+        <v>10100004</v>
       </c>
       <c r="L11" s="55" t="inlineStr">
         <is>
-          <t>精英魔法师兜帽</t>
-        </is>
-      </c>
-      <c r="M11" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>射手兜帽</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="55" t="n">
-        <v>10100008</v>
+        <v>10100005</v>
       </c>
       <c r="B12" s="55" t="n">
         <v>1</v>
@@ -1670,30 +1660,30 @@
         <v>1</v>
       </c>
       <c r="F12" s="55" t="n">
-        <v>1500008</v>
+        <v>1500005</v>
       </c>
       <c r="G12" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_8</t>
+          <t>Human_Atlas_Hat_Hat_5</t>
         </is>
       </c>
       <c r="K12" s="55" t="n">
-        <v>10100008</v>
+        <v>10100005</v>
       </c>
       <c r="L12" s="55" t="inlineStr">
         <is>
-          <t>暗杀者兜帽</t>
+          <t>魔法师帽</t>
         </is>
       </c>
       <c r="M12" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="55" t="n">
-        <v>10100010</v>
+        <v>10100007</v>
       </c>
       <c r="B13" s="55" t="n">
         <v>1</v>
@@ -1705,30 +1695,30 @@
         <v>1</v>
       </c>
       <c r="F13" s="55" t="n">
-        <v>1500010</v>
+        <v>1500007</v>
       </c>
       <c r="G13" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_10</t>
+          <t>Human_Atlas_Hat_Hat_7</t>
         </is>
       </c>
       <c r="K13" s="55" t="n">
-        <v>10100010</v>
+        <v>10100007</v>
       </c>
       <c r="L13" s="55" t="inlineStr">
         <is>
-          <t>骑士头盔</t>
+          <t>精英魔法师兜帽</t>
         </is>
       </c>
       <c r="M13" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="55" t="n">
-        <v>10100012</v>
+        <v>10100008</v>
       </c>
       <c r="B14" s="55" t="n">
         <v>1</v>
@@ -1740,19 +1730,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="55" t="n">
-        <v>1500012</v>
+        <v>1500008</v>
       </c>
       <c r="G14" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_12</t>
+          <t>Human_Atlas_Hat_Hat_8</t>
         </is>
       </c>
       <c r="K14" s="55" t="n">
-        <v>10100012</v>
+        <v>10100008</v>
       </c>
       <c r="L14" s="55" t="inlineStr">
         <is>
-          <t>死灵师面具</t>
+          <t>暗杀者兜帽</t>
         </is>
       </c>
       <c r="M14" s="55" t="inlineStr">
@@ -1763,7 +1753,7 @@
     </row>
     <row r="15">
       <c r="A15" s="55" t="n">
-        <v>10100013</v>
+        <v>10100010</v>
       </c>
       <c r="B15" s="55" t="n">
         <v>1</v>
@@ -1775,19 +1765,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="55" t="n">
-        <v>1500013</v>
+        <v>1500010</v>
       </c>
       <c r="G15" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_13</t>
+          <t>Human_Atlas_Hat_Hat_10</t>
         </is>
       </c>
       <c r="K15" s="55" t="n">
-        <v>10100013</v>
+        <v>10100010</v>
       </c>
       <c r="L15" s="55" t="inlineStr">
         <is>
-          <t>金骑士头盔</t>
+          <t>骑士头盔</t>
         </is>
       </c>
       <c r="M15" s="55" t="inlineStr">
@@ -1798,7 +1788,7 @@
     </row>
     <row r="16">
       <c r="A16" s="55" t="n">
-        <v>10100014</v>
+        <v>10100012</v>
       </c>
       <c r="B16" s="55" t="n">
         <v>1</v>
@@ -1810,30 +1800,30 @@
         <v>1</v>
       </c>
       <c r="F16" s="55" t="n">
-        <v>1500014</v>
+        <v>1500012</v>
       </c>
       <c r="G16" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_14</t>
+          <t>Human_Atlas_Hat_Hat_12</t>
         </is>
       </c>
       <c r="K16" s="55" t="n">
-        <v>10100014</v>
+        <v>10100012</v>
       </c>
       <c r="L16" s="55" t="inlineStr">
         <is>
-          <t>勇者头盔</t>
+          <t>死灵师面具</t>
         </is>
       </c>
       <c r="M16" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="55" t="n">
-        <v>10100015</v>
+        <v>10100013</v>
       </c>
       <c r="B17" s="55" t="n">
         <v>1</v>
@@ -1845,19 +1835,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="55" t="n">
-        <v>1500015</v>
+        <v>1500013</v>
       </c>
       <c r="G17" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_15</t>
+          <t>Human_Atlas_Hat_Hat_13</t>
         </is>
       </c>
       <c r="K17" s="55" t="n">
-        <v>10100015</v>
+        <v>10100013</v>
       </c>
       <c r="L17" s="55" t="inlineStr">
         <is>
-          <t>魔力帽</t>
+          <t>金骑士头盔</t>
         </is>
       </c>
       <c r="M17" s="55" t="inlineStr">
@@ -1868,7 +1858,7 @@
     </row>
     <row r="18">
       <c r="A18" s="55" t="n">
-        <v>10100016</v>
+        <v>10100014</v>
       </c>
       <c r="B18" s="55" t="n">
         <v>1</v>
@@ -1880,19 +1870,19 @@
         <v>1</v>
       </c>
       <c r="F18" s="55" t="n">
-        <v>1500016</v>
+        <v>1500014</v>
       </c>
       <c r="G18" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_16</t>
+          <t>Human_Atlas_Hat_Hat_14</t>
         </is>
       </c>
       <c r="K18" s="55" t="n">
-        <v>10100016</v>
+        <v>10100014</v>
       </c>
       <c r="L18" s="55" t="inlineStr">
         <is>
-          <t>暗黑骑士头盔</t>
+          <t>勇者头盔</t>
         </is>
       </c>
       <c r="M18" s="55" t="inlineStr">
@@ -1903,7 +1893,7 @@
     </row>
     <row r="19">
       <c r="A19" s="55" t="n">
-        <v>10100017</v>
+        <v>10100015</v>
       </c>
       <c r="B19" s="55" t="n">
         <v>1</v>
@@ -1915,33 +1905,33 @@
         <v>1</v>
       </c>
       <c r="F19" s="55" t="n">
-        <v>1500017</v>
+        <v>1500015</v>
       </c>
       <c r="G19" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_17</t>
+          <t>Human_Atlas_Hat_Hat_15</t>
         </is>
       </c>
       <c r="K19" s="55" t="n">
-        <v>10100017</v>
+        <v>10100015</v>
       </c>
       <c r="L19" s="55" t="inlineStr">
         <is>
-          <t>银色骑士头盔</t>
+          <t>魔力帽</t>
         </is>
       </c>
       <c r="M19" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="55" t="n">
-        <v>10200001</v>
+        <v>10100016</v>
       </c>
       <c r="B20" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="55" t="n">
         <v>1</v>
@@ -1950,33 +1940,33 @@
         <v>1</v>
       </c>
       <c r="F20" s="55" t="n">
-        <v>1510001</v>
+        <v>1500016</v>
       </c>
       <c r="G20" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_1</t>
+          <t>Human_Atlas_Hat_Hat_16</t>
         </is>
       </c>
       <c r="K20" s="55" t="n">
-        <v>10200001</v>
+        <v>10100016</v>
       </c>
       <c r="L20" s="55" t="inlineStr">
         <is>
-          <t>钢盔甲上衣---------------------------</t>
+          <t>暗黑骑士头盔</t>
         </is>
       </c>
       <c r="M20" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="55" t="n">
-        <v>10200002</v>
+        <v>10100017</v>
       </c>
       <c r="B21" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="55" t="n">
         <v>1</v>
@@ -1985,30 +1975,30 @@
         <v>1</v>
       </c>
       <c r="F21" s="55" t="n">
-        <v>1510002</v>
+        <v>1500017</v>
       </c>
       <c r="G21" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_2</t>
+          <t>Human_Atlas_Hat_Hat_17</t>
         </is>
       </c>
       <c r="K21" s="55" t="n">
-        <v>10200002</v>
+        <v>10100017</v>
       </c>
       <c r="L21" s="55" t="inlineStr">
         <is>
-          <t>大魔法师上衣</t>
+          <t>银色骑士头盔</t>
         </is>
       </c>
       <c r="M21" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="55" t="n">
-        <v>10200003</v>
+        <v>10200001</v>
       </c>
       <c r="B22" s="55" t="n">
         <v>2</v>
@@ -2020,26 +2010,30 @@
         <v>1</v>
       </c>
       <c r="F22" s="55" t="n">
-        <v>1510003</v>
+        <v>1510001</v>
       </c>
       <c r="G22" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_3</t>
+          <t>Human_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K22" s="55" t="n">
-        <v>10200003</v>
+        <v>10200001</v>
       </c>
       <c r="L22" s="55" t="inlineStr">
         <is>
-          <t>冒险者上衣</t>
-        </is>
-      </c>
-      <c r="M22" s="55" t="inlineStr"/>
+          <t>钢盔甲上衣---------------------------</t>
+        </is>
+      </c>
+      <c r="M22" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="55" t="n">
-        <v>10200004</v>
+        <v>10200002</v>
       </c>
       <c r="B23" s="55" t="n">
         <v>2</v>
@@ -2051,25 +2045,30 @@
         <v>1</v>
       </c>
       <c r="F23" s="55" t="n">
-        <v>1510004</v>
+        <v>1510002</v>
       </c>
       <c r="G23" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_4</t>
+          <t>Human_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K23" s="55" t="n">
-        <v>10200004</v>
+        <v>10200002</v>
       </c>
       <c r="L23" s="55" t="inlineStr">
         <is>
-          <t>射手上衣</t>
+          <t>大魔法师上衣</t>
+        </is>
+      </c>
+      <c r="M23" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="55" t="n">
-        <v>10200005</v>
+        <v>10200003</v>
       </c>
       <c r="B24" s="55" t="n">
         <v>2</v>
@@ -2081,30 +2080,26 @@
         <v>1</v>
       </c>
       <c r="F24" s="55" t="n">
-        <v>1510005</v>
+        <v>1510003</v>
       </c>
       <c r="G24" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_5</t>
+          <t>Human_Atlas_Clothes_Clothes_3</t>
         </is>
       </c>
       <c r="K24" s="55" t="n">
-        <v>10200005</v>
+        <v>10200003</v>
       </c>
       <c r="L24" s="55" t="inlineStr">
         <is>
-          <t>魔法师上衣</t>
-        </is>
-      </c>
-      <c r="M24" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>冒险者上衣</t>
+        </is>
+      </c>
+      <c r="M24" s="55" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="55" t="n">
-        <v>10200006</v>
+        <v>10200004</v>
       </c>
       <c r="B25" s="55" t="n">
         <v>2</v>
@@ -2116,30 +2111,25 @@
         <v>1</v>
       </c>
       <c r="F25" s="55" t="n">
-        <v>1510006</v>
+        <v>1510004</v>
       </c>
       <c r="G25" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_6</t>
+          <t>Human_Atlas_Clothes_Clothes_4</t>
         </is>
       </c>
       <c r="K25" s="55" t="n">
-        <v>10200006</v>
+        <v>10200004</v>
       </c>
       <c r="L25" s="55" t="inlineStr">
         <is>
-          <t>狩猎者上衣</t>
-        </is>
-      </c>
-      <c r="M25" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>射手上衣</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="55" t="n">
-        <v>10200007</v>
+        <v>10200005</v>
       </c>
       <c r="B26" s="55" t="n">
         <v>2</v>
@@ -2151,19 +2141,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="55" t="n">
-        <v>1510007</v>
+        <v>1510005</v>
       </c>
       <c r="G26" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_7</t>
+          <t>Human_Atlas_Clothes_Clothes_5</t>
         </is>
       </c>
       <c r="K26" s="55" t="n">
-        <v>10200007</v>
+        <v>10200005</v>
       </c>
       <c r="L26" s="55" t="inlineStr">
         <is>
-          <t>精英魔法师上衣</t>
+          <t>魔法师上衣</t>
         </is>
       </c>
       <c r="M26" s="55" t="inlineStr">
@@ -2174,7 +2164,7 @@
     </row>
     <row r="27">
       <c r="A27" s="55" t="n">
-        <v>10200008</v>
+        <v>10200006</v>
       </c>
       <c r="B27" s="55" t="n">
         <v>2</v>
@@ -2186,30 +2176,30 @@
         <v>1</v>
       </c>
       <c r="F27" s="55" t="n">
-        <v>1510008</v>
+        <v>1510006</v>
       </c>
       <c r="G27" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_8</t>
+          <t>Human_Atlas_Clothes_Clothes_6</t>
         </is>
       </c>
       <c r="K27" s="55" t="n">
-        <v>10200008</v>
+        <v>10200006</v>
       </c>
       <c r="L27" s="55" t="inlineStr">
         <is>
-          <t>暗杀者上衣</t>
+          <t>狩猎者上衣</t>
         </is>
       </c>
       <c r="M27" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="55" t="n">
-        <v>10200009</v>
+        <v>10200007</v>
       </c>
       <c r="B28" s="55" t="n">
         <v>2</v>
@@ -2221,30 +2211,30 @@
         <v>1</v>
       </c>
       <c r="F28" s="55" t="n">
-        <v>1510009</v>
+        <v>1510007</v>
       </c>
       <c r="G28" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_9</t>
+          <t>Human_Atlas_Clothes_Clothes_7</t>
         </is>
       </c>
       <c r="K28" s="55" t="n">
-        <v>10200009</v>
+        <v>10200007</v>
       </c>
       <c r="L28" s="55" t="inlineStr">
         <is>
-          <t>竞技者上衣</t>
+          <t>精英魔法师上衣</t>
         </is>
       </c>
       <c r="M28" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="55" t="n">
-        <v>10200010</v>
+        <v>10200008</v>
       </c>
       <c r="B29" s="55" t="n">
         <v>2</v>
@@ -2256,19 +2246,19 @@
         <v>1</v>
       </c>
       <c r="F29" s="55" t="n">
-        <v>1510010</v>
+        <v>1510008</v>
       </c>
       <c r="G29" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_10</t>
+          <t>Human_Atlas_Clothes_Clothes_8</t>
         </is>
       </c>
       <c r="K29" s="55" t="n">
-        <v>10200010</v>
+        <v>10200008</v>
       </c>
       <c r="L29" s="55" t="inlineStr">
         <is>
-          <t>骑士盔甲</t>
+          <t>暗杀者上衣</t>
         </is>
       </c>
       <c r="M29" s="55" t="inlineStr">
@@ -2279,7 +2269,7 @@
     </row>
     <row r="30">
       <c r="A30" s="55" t="n">
-        <v>10200011</v>
+        <v>10200009</v>
       </c>
       <c r="B30" s="55" t="n">
         <v>2</v>
@@ -2291,30 +2281,30 @@
         <v>1</v>
       </c>
       <c r="F30" s="55" t="n">
-        <v>1510011</v>
+        <v>1510009</v>
       </c>
       <c r="G30" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_11</t>
+          <t>Human_Atlas_Clothes_Clothes_9</t>
         </is>
       </c>
       <c r="K30" s="55" t="n">
-        <v>10200011</v>
+        <v>10200009</v>
       </c>
       <c r="L30" s="55" t="inlineStr">
         <is>
-          <t>治疗师长袍</t>
+          <t>竞技者上衣</t>
         </is>
       </c>
       <c r="M30" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="55" t="n">
-        <v>10200012</v>
+        <v>10200010</v>
       </c>
       <c r="B31" s="55" t="n">
         <v>2</v>
@@ -2326,19 +2316,19 @@
         <v>1</v>
       </c>
       <c r="F31" s="55" t="n">
-        <v>1510012</v>
+        <v>1510010</v>
       </c>
       <c r="G31" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_12</t>
+          <t>Human_Atlas_Clothes_Clothes_10</t>
         </is>
       </c>
       <c r="K31" s="55" t="n">
-        <v>10200012</v>
+        <v>10200010</v>
       </c>
       <c r="L31" s="55" t="inlineStr">
         <is>
-          <t>死灵师长袍</t>
+          <t>骑士盔甲</t>
         </is>
       </c>
       <c r="M31" s="55" t="inlineStr">
@@ -2349,7 +2339,7 @@
     </row>
     <row r="32">
       <c r="A32" s="55" t="n">
-        <v>10200013</v>
+        <v>10200011</v>
       </c>
       <c r="B32" s="55" t="n">
         <v>2</v>
@@ -2361,30 +2351,30 @@
         <v>1</v>
       </c>
       <c r="F32" s="55" t="n">
-        <v>1510013</v>
+        <v>1510011</v>
       </c>
       <c r="G32" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_13</t>
+          <t>Human_Atlas_Clothes_Clothes_11</t>
         </is>
       </c>
       <c r="K32" s="55" t="n">
-        <v>10200013</v>
+        <v>10200011</v>
       </c>
       <c r="L32" s="55" t="inlineStr">
         <is>
-          <t>金骑士盔甲</t>
+          <t>治疗师长袍</t>
         </is>
       </c>
       <c r="M32" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="55" t="n">
-        <v>10200014</v>
+        <v>10200012</v>
       </c>
       <c r="B33" s="55" t="n">
         <v>2</v>
@@ -2396,30 +2386,30 @@
         <v>1</v>
       </c>
       <c r="F33" s="55" t="n">
-        <v>1510014</v>
+        <v>1510012</v>
       </c>
       <c r="G33" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_14</t>
+          <t>Human_Atlas_Clothes_Clothes_12</t>
         </is>
       </c>
       <c r="K33" s="55" t="n">
-        <v>10200014</v>
+        <v>10200012</v>
       </c>
       <c r="L33" s="55" t="inlineStr">
         <is>
-          <t>勇者上衣</t>
+          <t>死灵师长袍</t>
         </is>
       </c>
       <c r="M33" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="55" t="n">
-        <v>10200015</v>
+        <v>10200013</v>
       </c>
       <c r="B34" s="55" t="n">
         <v>2</v>
@@ -2431,19 +2421,19 @@
         <v>1</v>
       </c>
       <c r="F34" s="55" t="n">
-        <v>1510015</v>
+        <v>1510013</v>
       </c>
       <c r="G34" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_15</t>
+          <t>Human_Atlas_Clothes_Clothes_13</t>
         </is>
       </c>
       <c r="K34" s="55" t="n">
-        <v>10200015</v>
+        <v>10200013</v>
       </c>
       <c r="L34" s="55" t="inlineStr">
         <is>
-          <t>魔力法师上衣</t>
+          <t>金骑士盔甲</t>
         </is>
       </c>
       <c r="M34" s="55" t="inlineStr">
@@ -2454,7 +2444,7 @@
     </row>
     <row r="35">
       <c r="A35" s="55" t="n">
-        <v>10200016</v>
+        <v>10200014</v>
       </c>
       <c r="B35" s="55" t="n">
         <v>2</v>
@@ -2466,19 +2456,19 @@
         <v>1</v>
       </c>
       <c r="F35" s="55" t="n">
-        <v>1510016</v>
+        <v>1510014</v>
       </c>
       <c r="G35" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_16</t>
+          <t>Human_Atlas_Clothes_Clothes_14</t>
         </is>
       </c>
       <c r="K35" s="55" t="n">
-        <v>10200016</v>
+        <v>10200014</v>
       </c>
       <c r="L35" s="55" t="inlineStr">
         <is>
-          <t>暗黑骑士盔甲</t>
+          <t>勇者上衣</t>
         </is>
       </c>
       <c r="M35" s="55" t="inlineStr">
@@ -2489,7 +2479,7 @@
     </row>
     <row r="36">
       <c r="A36" s="55" t="n">
-        <v>10200017</v>
+        <v>10200015</v>
       </c>
       <c r="B36" s="55" t="n">
         <v>2</v>
@@ -2501,33 +2491,33 @@
         <v>1</v>
       </c>
       <c r="F36" s="55" t="n">
-        <v>1510017</v>
+        <v>1510015</v>
       </c>
       <c r="G36" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_17</t>
+          <t>Human_Atlas_Clothes_Clothes_15</t>
         </is>
       </c>
       <c r="K36" s="55" t="n">
-        <v>10200017</v>
+        <v>10200015</v>
       </c>
       <c r="L36" s="55" t="inlineStr">
         <is>
-          <t>银色骑士盔甲</t>
+          <t>魔力法师上衣</t>
         </is>
       </c>
       <c r="M36" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="55" t="n">
-        <v>10300001</v>
+        <v>10200016</v>
       </c>
       <c r="B37" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" s="55" t="n">
         <v>1</v>
@@ -2536,33 +2526,33 @@
         <v>1</v>
       </c>
       <c r="F37" s="55" t="n">
-        <v>1520001</v>
+        <v>1510016</v>
       </c>
       <c r="G37" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_1</t>
+          <t>Human_Atlas_Clothes_Clothes_16</t>
         </is>
       </c>
       <c r="K37" s="55" t="n">
-        <v>10300001</v>
+        <v>10200016</v>
       </c>
       <c r="L37" s="55" t="inlineStr">
         <is>
-          <t>钢盔甲裤--------------------------</t>
+          <t>暗黑骑士盔甲</t>
         </is>
       </c>
       <c r="M37" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="55" t="n">
-        <v>10300002</v>
+        <v>10200017</v>
       </c>
       <c r="B38" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" s="55" t="n">
         <v>1</v>
@@ -2571,30 +2561,30 @@
         <v>1</v>
       </c>
       <c r="F38" s="55" t="n">
-        <v>1520002</v>
+        <v>1510017</v>
       </c>
       <c r="G38" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_2</t>
+          <t>Human_Atlas_Clothes_Clothes_17</t>
         </is>
       </c>
       <c r="K38" s="55" t="n">
-        <v>10300002</v>
+        <v>10200017</v>
       </c>
       <c r="L38" s="55" t="inlineStr">
         <is>
-          <t>大魔法师裤</t>
+          <t>银色骑士盔甲</t>
         </is>
       </c>
       <c r="M38" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="55" t="n">
-        <v>10300003</v>
+        <v>10300001</v>
       </c>
       <c r="B39" s="55" t="n">
         <v>3</v>
@@ -2606,26 +2596,30 @@
         <v>1</v>
       </c>
       <c r="F39" s="55" t="n">
-        <v>1520003</v>
+        <v>1520001</v>
       </c>
       <c r="G39" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_3</t>
+          <t>Human_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K39" s="55" t="n">
-        <v>10300003</v>
+        <v>10300001</v>
       </c>
       <c r="L39" s="55" t="inlineStr">
         <is>
-          <t>冒险者裤子</t>
-        </is>
-      </c>
-      <c r="M39" s="55" t="inlineStr"/>
+          <t>钢盔甲裤--------------------------</t>
+        </is>
+      </c>
+      <c r="M39" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="55" t="n">
-        <v>10300004</v>
+        <v>10300002</v>
       </c>
       <c r="B40" s="55" t="n">
         <v>3</v>
@@ -2637,25 +2631,30 @@
         <v>1</v>
       </c>
       <c r="F40" s="55" t="n">
-        <v>1520004</v>
+        <v>1520002</v>
       </c>
       <c r="G40" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_4</t>
+          <t>Human_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K40" s="55" t="n">
-        <v>10300004</v>
+        <v>10300002</v>
       </c>
       <c r="L40" s="55" t="inlineStr">
         <is>
-          <t>射手裤子</t>
+          <t>大魔法师裤</t>
+        </is>
+      </c>
+      <c r="M40" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="55" t="n">
-        <v>10300005</v>
+        <v>10300003</v>
       </c>
       <c r="B41" s="55" t="n">
         <v>3</v>
@@ -2667,30 +2666,26 @@
         <v>1</v>
       </c>
       <c r="F41" s="55" t="n">
-        <v>1520005</v>
+        <v>1520003</v>
       </c>
       <c r="G41" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_5</t>
+          <t>Human_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K41" s="55" t="n">
-        <v>10300005</v>
+        <v>10300003</v>
       </c>
       <c r="L41" s="55" t="inlineStr">
         <is>
-          <t>魔法师裤</t>
-        </is>
-      </c>
-      <c r="M41" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>冒险者裤子</t>
+        </is>
+      </c>
+      <c r="M41" s="55" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="55" t="n">
-        <v>10300006</v>
+        <v>10300004</v>
       </c>
       <c r="B42" s="55" t="n">
         <v>3</v>
@@ -2702,30 +2697,25 @@
         <v>1</v>
       </c>
       <c r="F42" s="55" t="n">
-        <v>1520006</v>
+        <v>1520004</v>
       </c>
       <c r="G42" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_6</t>
+          <t>Human_Atlas_Pants_Pants_4</t>
         </is>
       </c>
       <c r="K42" s="55" t="n">
-        <v>10300006</v>
+        <v>10300004</v>
       </c>
       <c r="L42" s="55" t="inlineStr">
         <is>
-          <t>狩猎者裤</t>
-        </is>
-      </c>
-      <c r="M42" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>射手裤子</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="55" t="n">
-        <v>10300007</v>
+        <v>10300005</v>
       </c>
       <c r="B43" s="55" t="n">
         <v>3</v>
@@ -2737,19 +2727,19 @@
         <v>1</v>
       </c>
       <c r="F43" s="55" t="n">
-        <v>1520007</v>
+        <v>1520005</v>
       </c>
       <c r="G43" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_7</t>
+          <t>Human_Atlas_Pants_Pants_5</t>
         </is>
       </c>
       <c r="K43" s="55" t="n">
-        <v>10300007</v>
+        <v>10300005</v>
       </c>
       <c r="L43" s="55" t="inlineStr">
         <is>
-          <t>精英魔法师裤</t>
+          <t>魔法师裤</t>
         </is>
       </c>
       <c r="M43" s="55" t="inlineStr">
@@ -2760,7 +2750,7 @@
     </row>
     <row r="44">
       <c r="A44" s="55" t="n">
-        <v>10300008</v>
+        <v>10300006</v>
       </c>
       <c r="B44" s="55" t="n">
         <v>3</v>
@@ -2772,30 +2762,30 @@
         <v>1</v>
       </c>
       <c r="F44" s="55" t="n">
-        <v>1520008</v>
+        <v>1520006</v>
       </c>
       <c r="G44" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_8</t>
+          <t>Human_Atlas_Pants_Pants_6</t>
         </is>
       </c>
       <c r="K44" s="55" t="n">
-        <v>10300008</v>
+        <v>10300006</v>
       </c>
       <c r="L44" s="55" t="inlineStr">
         <is>
-          <t>暗杀者裤</t>
+          <t>狩猎者裤</t>
         </is>
       </c>
       <c r="M44" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="55" t="n">
-        <v>10300009</v>
+        <v>10300007</v>
       </c>
       <c r="B45" s="55" t="n">
         <v>3</v>
@@ -2807,30 +2797,30 @@
         <v>1</v>
       </c>
       <c r="F45" s="55" t="n">
-        <v>1520009</v>
+        <v>1520007</v>
       </c>
       <c r="G45" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_9</t>
+          <t>Human_Atlas_Pants_Pants_7</t>
         </is>
       </c>
       <c r="K45" s="55" t="n">
-        <v>10300009</v>
+        <v>10300007</v>
       </c>
       <c r="L45" s="55" t="inlineStr">
         <is>
-          <t>竞技者裤</t>
+          <t>精英魔法师裤</t>
         </is>
       </c>
       <c r="M45" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="55" t="n">
-        <v>10300010</v>
+        <v>10300008</v>
       </c>
       <c r="B46" s="55" t="n">
         <v>3</v>
@@ -2842,19 +2832,19 @@
         <v>1</v>
       </c>
       <c r="F46" s="55" t="n">
-        <v>1520010</v>
+        <v>1520008</v>
       </c>
       <c r="G46" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_10</t>
+          <t>Human_Atlas_Pants_Pants_8</t>
         </is>
       </c>
       <c r="K46" s="55" t="n">
-        <v>10300010</v>
+        <v>10300008</v>
       </c>
       <c r="L46" s="55" t="inlineStr">
         <is>
-          <t>骑士裤</t>
+          <t>暗杀者裤</t>
         </is>
       </c>
       <c r="M46" s="55" t="inlineStr">
@@ -2865,7 +2855,7 @@
     </row>
     <row r="47">
       <c r="A47" s="55" t="n">
-        <v>10300011</v>
+        <v>10300009</v>
       </c>
       <c r="B47" s="55" t="n">
         <v>3</v>
@@ -2877,30 +2867,30 @@
         <v>1</v>
       </c>
       <c r="F47" s="55" t="n">
-        <v>1520011</v>
+        <v>1520009</v>
       </c>
       <c r="G47" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_11</t>
+          <t>Human_Atlas_Pants_Pants_9</t>
         </is>
       </c>
       <c r="K47" s="55" t="n">
-        <v>10300011</v>
+        <v>10300009</v>
       </c>
       <c r="L47" s="55" t="inlineStr">
         <is>
-          <t>治疗师裤</t>
+          <t>竞技者裤</t>
         </is>
       </c>
       <c r="M47" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="55" t="n">
-        <v>10300012</v>
+        <v>10300010</v>
       </c>
       <c r="B48" s="55" t="n">
         <v>3</v>
@@ -2912,19 +2902,19 @@
         <v>1</v>
       </c>
       <c r="F48" s="55" t="n">
-        <v>1520012</v>
+        <v>1520010</v>
       </c>
       <c r="G48" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_12</t>
+          <t>Human_Atlas_Pants_Pants_10</t>
         </is>
       </c>
       <c r="K48" s="55" t="n">
-        <v>10300012</v>
+        <v>10300010</v>
       </c>
       <c r="L48" s="55" t="inlineStr">
         <is>
-          <t>死灵师裤</t>
+          <t>骑士裤</t>
         </is>
       </c>
       <c r="M48" s="55" t="inlineStr">
@@ -2935,7 +2925,7 @@
     </row>
     <row r="49">
       <c r="A49" s="55" t="n">
-        <v>10300013</v>
+        <v>10300011</v>
       </c>
       <c r="B49" s="55" t="n">
         <v>3</v>
@@ -2947,30 +2937,30 @@
         <v>1</v>
       </c>
       <c r="F49" s="55" t="n">
-        <v>1520013</v>
+        <v>1520011</v>
       </c>
       <c r="G49" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_13</t>
+          <t>Human_Atlas_Pants_Pants_11</t>
         </is>
       </c>
       <c r="K49" s="55" t="n">
-        <v>10300013</v>
+        <v>10300011</v>
       </c>
       <c r="L49" s="55" t="inlineStr">
         <is>
-          <t>金骑士裤</t>
+          <t>治疗师裤</t>
         </is>
       </c>
       <c r="M49" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="55" t="n">
-        <v>10300014</v>
+        <v>10300012</v>
       </c>
       <c r="B50" s="55" t="n">
         <v>3</v>
@@ -2982,30 +2972,30 @@
         <v>1</v>
       </c>
       <c r="F50" s="55" t="n">
-        <v>1520014</v>
+        <v>1520012</v>
       </c>
       <c r="G50" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_14</t>
+          <t>Human_Atlas_Pants_Pants_12</t>
         </is>
       </c>
       <c r="K50" s="55" t="n">
-        <v>10300014</v>
+        <v>10300012</v>
       </c>
       <c r="L50" s="55" t="inlineStr">
         <is>
-          <t>勇者裤</t>
+          <t>死灵师裤</t>
         </is>
       </c>
       <c r="M50" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="55" t="n">
-        <v>10300015</v>
+        <v>10300013</v>
       </c>
       <c r="B51" s="55" t="n">
         <v>3</v>
@@ -3017,19 +3007,19 @@
         <v>1</v>
       </c>
       <c r="F51" s="55" t="n">
-        <v>1520015</v>
+        <v>1520013</v>
       </c>
       <c r="G51" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_15</t>
+          <t>Human_Atlas_Pants_Pants_13</t>
         </is>
       </c>
       <c r="K51" s="55" t="n">
-        <v>10300015</v>
+        <v>10300013</v>
       </c>
       <c r="L51" s="55" t="inlineStr">
         <is>
-          <t>魔力法师裤</t>
+          <t>金骑士裤</t>
         </is>
       </c>
       <c r="M51" s="55" t="inlineStr">
@@ -3040,7 +3030,7 @@
     </row>
     <row r="52">
       <c r="A52" s="55" t="n">
-        <v>10300016</v>
+        <v>10300014</v>
       </c>
       <c r="B52" s="55" t="n">
         <v>3</v>
@@ -3052,19 +3042,19 @@
         <v>1</v>
       </c>
       <c r="F52" s="55" t="n">
-        <v>1520016</v>
+        <v>1520014</v>
       </c>
       <c r="G52" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_16</t>
+          <t>Human_Atlas_Pants_Pants_14</t>
         </is>
       </c>
       <c r="K52" s="55" t="n">
-        <v>10300016</v>
+        <v>10300014</v>
       </c>
       <c r="L52" s="55" t="inlineStr">
         <is>
-          <t>暗黑骑士裤</t>
+          <t>勇者裤</t>
         </is>
       </c>
       <c r="M52" s="55" t="inlineStr">
@@ -3075,7 +3065,7 @@
     </row>
     <row r="53">
       <c r="A53" s="55" t="n">
-        <v>10300017</v>
+        <v>10300015</v>
       </c>
       <c r="B53" s="55" t="n">
         <v>3</v>
@@ -3087,36 +3077,33 @@
         <v>1</v>
       </c>
       <c r="F53" s="55" t="n">
-        <v>1520017</v>
+        <v>1520015</v>
       </c>
       <c r="G53" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_17</t>
+          <t>Human_Atlas_Pants_Pants_15</t>
         </is>
       </c>
       <c r="K53" s="55" t="n">
-        <v>10300017</v>
+        <v>10300015</v>
       </c>
       <c r="L53" s="55" t="inlineStr">
         <is>
-          <t>银色骑士裤</t>
+          <t>魔力法师裤</t>
         </is>
       </c>
       <c r="M53" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="55" t="n">
-        <v>11000001</v>
+        <v>10300016</v>
       </c>
       <c r="B54" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C54" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" s="55" t="n">
         <v>1</v>
@@ -3125,36 +3112,33 @@
         <v>1</v>
       </c>
       <c r="F54" s="55" t="n">
-        <v>1900001</v>
+        <v>1520016</v>
       </c>
       <c r="G54" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_1</t>
+          <t>Human_Atlas_Pants_Pants_16</t>
         </is>
       </c>
       <c r="K54" s="55" t="n">
-        <v>11000001</v>
+        <v>10300016</v>
       </c>
       <c r="L54" s="55" t="inlineStr">
         <is>
-          <t>钢剑----------------------------</t>
+          <t>暗黑骑士裤</t>
         </is>
       </c>
       <c r="M54" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="55" t="n">
-        <v>11000002</v>
+        <v>10300017</v>
       </c>
       <c r="B55" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C55" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" s="55" t="n">
         <v>1</v>
@@ -3163,32 +3147,36 @@
         <v>1</v>
       </c>
       <c r="F55" s="55" t="n">
-        <v>1900002</v>
+        <v>1520017</v>
       </c>
       <c r="G55" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_2</t>
+          <t>Human_Atlas_Pants_Pants_17</t>
         </is>
       </c>
       <c r="K55" s="55" t="n">
-        <v>11000002</v>
+        <v>10300017</v>
       </c>
       <c r="L55" s="55" t="inlineStr">
         <is>
-          <t>铁剑</t>
-        </is>
-      </c>
-      <c r="M55" s="55" t="inlineStr"/>
+          <t>银色骑士裤</t>
+        </is>
+      </c>
+      <c r="M55" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="55" t="n">
-        <v>11000003</v>
+        <v>11000001</v>
       </c>
       <c r="B56" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C56" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" s="55" t="n">
         <v>1</v>
@@ -3197,32 +3185,36 @@
         <v>1</v>
       </c>
       <c r="F56" s="55" t="n">
-        <v>1900003</v>
+        <v>1900001</v>
       </c>
       <c r="G56" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_3</t>
+          <t>Human_Atlas_Weapon_Weapon_L_1</t>
         </is>
       </c>
       <c r="K56" s="55" t="n">
-        <v>11000003</v>
+        <v>11000001</v>
       </c>
       <c r="L56" s="55" t="inlineStr">
         <is>
-          <t>火法杖</t>
-        </is>
-      </c>
-      <c r="M56" s="55" t="inlineStr"/>
+          <t>钢剑----------------------------</t>
+        </is>
+      </c>
+      <c r="M56" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="55" t="n">
-        <v>11000004</v>
+        <v>11000002</v>
       </c>
       <c r="B57" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C57" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="55" t="n">
         <v>1</v>
@@ -3231,32 +3223,32 @@
         <v>1</v>
       </c>
       <c r="F57" s="55" t="n">
-        <v>1900004</v>
+        <v>1900002</v>
       </c>
       <c r="G57" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_4</t>
+          <t>Human_Atlas_Weapon_Weapon_L_2</t>
         </is>
       </c>
       <c r="K57" s="55" t="n">
-        <v>11000004</v>
+        <v>11000002</v>
       </c>
       <c r="L57" s="55" t="inlineStr">
         <is>
-          <t>冰法杖</t>
+          <t>铁剑</t>
         </is>
       </c>
       <c r="M57" s="55" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="55" t="n">
-        <v>11000005</v>
+        <v>11000003</v>
       </c>
       <c r="B58" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C58" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" s="55" t="n">
         <v>1</v>
@@ -3265,32 +3257,32 @@
         <v>1</v>
       </c>
       <c r="F58" s="55" t="n">
-        <v>1900005</v>
+        <v>1900003</v>
       </c>
       <c r="G58" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_5</t>
+          <t>Human_Atlas_Weapon_Weapon_L_3</t>
         </is>
       </c>
       <c r="K58" s="55" t="n">
-        <v>11000005</v>
+        <v>11000003</v>
       </c>
       <c r="L58" s="55" t="inlineStr">
         <is>
-          <t>残破剑</t>
+          <t>火法杖</t>
         </is>
       </c>
       <c r="M58" s="55" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="55" t="n">
-        <v>11000006</v>
+        <v>11000004</v>
       </c>
       <c r="B59" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C59" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" s="55" t="n">
         <v>1</v>
@@ -3299,32 +3291,32 @@
         <v>1</v>
       </c>
       <c r="F59" s="55" t="n">
-        <v>1900006</v>
+        <v>1900004</v>
       </c>
       <c r="G59" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_6</t>
+          <t>Human_Atlas_Weapon_Weapon_L_4</t>
         </is>
       </c>
       <c r="K59" s="55" t="n">
-        <v>11000006</v>
+        <v>11000004</v>
       </c>
       <c r="L59" s="55" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>冰法杖</t>
         </is>
       </c>
       <c r="M59" s="55" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="55" t="n">
-        <v>11000007</v>
+        <v>11000005</v>
       </c>
       <c r="B60" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C60" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" s="55" t="n">
         <v>1</v>
@@ -3333,36 +3325,32 @@
         <v>1</v>
       </c>
       <c r="F60" s="55" t="n">
-        <v>1900007</v>
+        <v>1900005</v>
       </c>
       <c r="G60" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_7</t>
+          <t>Human_Atlas_Weapon_Weapon_L_5</t>
         </is>
       </c>
       <c r="K60" s="55" t="n">
-        <v>11000007</v>
+        <v>11000005</v>
       </c>
       <c r="L60" s="55" t="inlineStr">
         <is>
-          <t>绿宝石法杖</t>
-        </is>
-      </c>
-      <c r="M60" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>残破剑</t>
+        </is>
+      </c>
+      <c r="M60" s="55" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="55" t="n">
-        <v>11000008</v>
+        <v>11000006</v>
       </c>
       <c r="B61" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C61" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" s="55" t="n">
         <v>1</v>
@@ -3371,30 +3359,26 @@
         <v>1</v>
       </c>
       <c r="F61" s="55" t="n">
-        <v>1900008</v>
+        <v>1900006</v>
       </c>
       <c r="G61" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_8</t>
+          <t>Human_Atlas_Weapon_Weapon_L_6</t>
         </is>
       </c>
       <c r="K61" s="55" t="n">
-        <v>11000008</v>
+        <v>11000006</v>
       </c>
       <c r="L61" s="55" t="inlineStr">
         <is>
-          <t>魔力法杖</t>
-        </is>
-      </c>
-      <c r="M61" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>短刀</t>
+        </is>
+      </c>
+      <c r="M61" s="55" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="55" t="n">
-        <v>11000009</v>
+        <v>11000007</v>
       </c>
       <c r="B62" s="55" t="n">
         <v>10</v>
@@ -3409,30 +3393,30 @@
         <v>1</v>
       </c>
       <c r="F62" s="55" t="n">
-        <v>1900009</v>
+        <v>1900007</v>
       </c>
       <c r="G62" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_9</t>
+          <t>Human_Atlas_Weapon_Weapon_L_7</t>
         </is>
       </c>
       <c r="K62" s="55" t="n">
-        <v>11000009</v>
+        <v>11000007</v>
       </c>
       <c r="L62" s="55" t="inlineStr">
         <is>
-          <t>星之法杖</t>
+          <t>绿宝石法杖</t>
         </is>
       </c>
       <c r="M62" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="55" t="n">
-        <v>11000010</v>
+        <v>11000008</v>
       </c>
       <c r="B63" s="55" t="n">
         <v>10</v>
@@ -3447,26 +3431,30 @@
         <v>1</v>
       </c>
       <c r="F63" s="55" t="n">
-        <v>1900010</v>
+        <v>1900008</v>
       </c>
       <c r="G63" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_10</t>
+          <t>Human_Atlas_Weapon_Weapon_L_8</t>
         </is>
       </c>
       <c r="K63" s="55" t="n">
-        <v>11000010</v>
+        <v>11000008</v>
       </c>
       <c r="L63" s="55" t="inlineStr">
         <is>
-          <t>冰法杖</t>
-        </is>
-      </c>
-      <c r="M63" s="55" t="inlineStr"/>
+          <t>魔力法杖</t>
+        </is>
+      </c>
+      <c r="M63" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="55" t="n">
-        <v>11000011</v>
+        <v>11000009</v>
       </c>
       <c r="B64" s="55" t="n">
         <v>10</v>
@@ -3481,32 +3469,36 @@
         <v>1</v>
       </c>
       <c r="F64" s="55" t="n">
-        <v>1900011</v>
+        <v>1900009</v>
       </c>
       <c r="G64" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_11</t>
+          <t>Human_Atlas_Weapon_Weapon_L_9</t>
         </is>
       </c>
       <c r="K64" s="55" t="n">
-        <v>11000011</v>
+        <v>11000009</v>
       </c>
       <c r="L64" s="55" t="inlineStr">
         <is>
-          <t>电法杖</t>
-        </is>
-      </c>
-      <c r="M64" s="55" t="inlineStr"/>
+          <t>星之法杖</t>
+        </is>
+      </c>
+      <c r="M64" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="55" t="n">
-        <v>11000012</v>
+        <v>11000010</v>
       </c>
       <c r="B65" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C65" s="55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" s="55" t="n">
         <v>1</v>
@@ -3515,30 +3507,26 @@
         <v>1</v>
       </c>
       <c r="F65" s="55" t="n">
-        <v>1900012</v>
+        <v>1900010</v>
       </c>
       <c r="G65" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_12</t>
+          <t>Human_Atlas_Weapon_Weapon_L_10</t>
         </is>
       </c>
       <c r="K65" s="55" t="n">
-        <v>11000012</v>
+        <v>11000010</v>
       </c>
       <c r="L65" s="55" t="inlineStr">
         <is>
-          <t>大剑</t>
-        </is>
-      </c>
-      <c r="M65" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
-        </is>
-      </c>
+          <t>冰法杖</t>
+        </is>
+      </c>
+      <c r="M65" s="55" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="55" t="n">
-        <v>11000013</v>
+        <v>11000011</v>
       </c>
       <c r="B66" s="55" t="n">
         <v>10</v>
@@ -3553,74 +3541,70 @@
         <v>1</v>
       </c>
       <c r="F66" s="55" t="n">
-        <v>1900013</v>
+        <v>1900011</v>
       </c>
       <c r="G66" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_13</t>
+          <t>Human_Atlas_Weapon_Weapon_L_11</t>
         </is>
       </c>
       <c r="K66" s="55" t="n">
-        <v>11000013</v>
+        <v>11000011</v>
       </c>
       <c r="L66" s="55" t="inlineStr">
         <is>
-          <t>死灵法杖</t>
-        </is>
-      </c>
-      <c r="M66" s="55" t="inlineStr">
+          <t>电法杖</t>
+        </is>
+      </c>
+      <c r="M66" s="55" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="55" t="n">
+        <v>11000012</v>
+      </c>
+      <c r="B67" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C67" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="55" t="n">
+        <v>1900012</v>
+      </c>
+      <c r="G67" s="55" t="inlineStr">
+        <is>
+          <t>Human_Atlas_Weapon_Weapon_L_12</t>
+        </is>
+      </c>
+      <c r="K67" s="55" t="n">
+        <v>11000012</v>
+      </c>
+      <c r="L67" s="55" t="inlineStr">
+        <is>
+          <t>大剑</t>
+        </is>
+      </c>
+      <c r="M67" s="55" t="inlineStr">
         <is>
           <t>3,4,5,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>11000015</v>
-      </c>
-      <c r="B67" t="n">
-        <v>10</v>
-      </c>
-      <c r="C67" t="n">
-        <v>6</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1900015</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Human_Atlas_Weapon_Weapon_L_15</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>11000015</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>钢铁盾</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="55" t="n">
-        <v>11010001</v>
+        <v>11000013</v>
       </c>
       <c r="B68" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C68" s="55" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D68" s="55" t="n">
         <v>1</v>
@@ -3629,37 +3613,36 @@
         <v>1</v>
       </c>
       <c r="F68" s="55" t="n">
-        <v>1910001</v>
+        <v>1900013</v>
       </c>
       <c r="G68" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_R_1</t>
-        </is>
-      </c>
-      <c r="I68" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Human_Atlas_Other_Arrow_1&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180</t>
+          <t>Human_Atlas_Weapon_Weapon_L_13</t>
         </is>
       </c>
       <c r="K68" s="55" t="n">
-        <v>11010001</v>
+        <v>11000013</v>
       </c>
       <c r="L68" s="55" t="inlineStr">
         <is>
-          <t>木弓</t>
-        </is>
-      </c>
-      <c r="M68" s="55" t="inlineStr"/>
+          <t>死灵法杖</t>
+        </is>
+      </c>
+      <c r="M68" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="55" t="n">
-        <v>11010002</v>
+        <v>11000015</v>
       </c>
       <c r="B69" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C69" s="55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" s="55" t="n">
         <v>1</v>
@@ -3668,24 +3651,19 @@
         <v>1</v>
       </c>
       <c r="F69" s="55" t="n">
-        <v>1910002</v>
+        <v>1900015</v>
       </c>
       <c r="G69" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_R_2</t>
-        </is>
-      </c>
-      <c r="I69" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Human_Atlas_Other_Arrow_2&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
+          <t>Human_Atlas_Weapon_Weapon_L_15</t>
         </is>
       </c>
       <c r="K69" s="55" t="n">
-        <v>11010002</v>
+        <v>11000015</v>
       </c>
       <c r="L69" s="55" t="inlineStr">
         <is>
-          <t>钢弓</t>
+          <t>钢铁盾</t>
         </is>
       </c>
       <c r="M69" s="55" t="inlineStr">
@@ -3696,7 +3674,7 @@
     </row>
     <row r="70">
       <c r="A70" s="55" t="n">
-        <v>11010003</v>
+        <v>11010001</v>
       </c>
       <c r="B70" s="55" t="n">
         <v>10</v>
@@ -3711,41 +3689,37 @@
         <v>1</v>
       </c>
       <c r="F70" s="55" t="n">
-        <v>1910003</v>
+        <v>1910001</v>
       </c>
       <c r="G70" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_R_3</t>
+          <t>Human_Atlas_Weapon_Weapon_R_1</t>
         </is>
       </c>
       <c r="I70" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Human_Atlas_Other_Arrow_3&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
+          <t>ShowSprite:Human_Atlas_Other_Arrow_1&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180</t>
         </is>
       </c>
       <c r="K70" s="55" t="n">
-        <v>11010003</v>
+        <v>11010001</v>
       </c>
       <c r="L70" s="55" t="inlineStr">
         <is>
-          <t>红木弓</t>
-        </is>
-      </c>
-      <c r="M70" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>木弓</t>
+        </is>
+      </c>
+      <c r="M70" s="55" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="55" t="n">
-        <v>11020021</v>
+        <v>11010002</v>
       </c>
       <c r="B71" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C71" s="55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D71" s="55" t="n">
         <v>1</v>
@@ -3754,19 +3728,24 @@
         <v>1</v>
       </c>
       <c r="F71" s="55" t="n">
-        <v>1920021</v>
+        <v>1910002</v>
       </c>
       <c r="G71" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_LR_21</t>
+          <t>Human_Atlas_Weapon_Weapon_R_2</t>
+        </is>
+      </c>
+      <c r="I71" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Human_Atlas_Other_Arrow_2&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
         </is>
       </c>
       <c r="K71" s="55" t="n">
-        <v>11020021</v>
+        <v>11010002</v>
       </c>
       <c r="L71" s="55" t="inlineStr">
         <is>
-          <t>冒险者盾剑</t>
+          <t>钢弓</t>
         </is>
       </c>
       <c r="M71" s="55" t="inlineStr">
@@ -3777,13 +3756,13 @@
     </row>
     <row r="72">
       <c r="A72" s="55" t="n">
-        <v>11020022</v>
+        <v>11010003</v>
       </c>
       <c r="B72" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C72" s="55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D72" s="55" t="n">
         <v>1</v>
@@ -3792,36 +3771,41 @@
         <v>1</v>
       </c>
       <c r="F72" s="55" t="n">
-        <v>1920022</v>
+        <v>1910003</v>
       </c>
       <c r="G72" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_LR_22</t>
+          <t>Human_Atlas_Weapon_Weapon_R_3</t>
+        </is>
+      </c>
+      <c r="I72" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Human_Atlas_Other_Arrow_3&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
         </is>
       </c>
       <c r="K72" s="55" t="n">
-        <v>11020022</v>
+        <v>11010003</v>
       </c>
       <c r="L72" s="55" t="inlineStr">
         <is>
-          <t>勇者盾剑</t>
+          <t>红木弓</t>
         </is>
       </c>
       <c r="M72" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="55" t="n">
-        <v>11020014</v>
+        <v>11020021</v>
       </c>
       <c r="B73" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C73" s="55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D73" s="55" t="n">
         <v>1</v>
@@ -3830,19 +3814,19 @@
         <v>1</v>
       </c>
       <c r="F73" s="55" t="n">
-        <v>1920014</v>
+        <v>1920021</v>
       </c>
       <c r="G73" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_LR_14</t>
+          <t>Human_Atlas_Weapon_Weapon_LR_21</t>
         </is>
       </c>
       <c r="K73" s="55" t="n">
-        <v>11020014</v>
+        <v>11020021</v>
       </c>
       <c r="L73" s="55" t="inlineStr">
         <is>
-          <t>精致短刀</t>
+          <t>冒险者盾剑</t>
         </is>
       </c>
       <c r="M73" s="55" t="inlineStr">
@@ -3853,61 +3837,72 @@
     </row>
     <row r="74">
       <c r="A74" s="55" t="n">
-        <v>20100001</v>
+        <v>11020022</v>
       </c>
       <c r="B74" s="55" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C74" s="55" t="n">
+        <v>4</v>
       </c>
       <c r="D74" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="55" t="n">
-        <v>2500001</v>
+        <v>1920022</v>
       </c>
       <c r="G74" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_1</t>
+          <t>Human_Atlas_Weapon_Weapon_LR_22</t>
         </is>
       </c>
       <c r="K74" s="55" t="n">
-        <v>20100001</v>
+        <v>11020022</v>
       </c>
       <c r="L74" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-皇冠-------------------</t>
+          <t>勇者盾剑</t>
+        </is>
+      </c>
+      <c r="M74" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="55" t="n">
-        <v>20100002</v>
+        <v>11020014</v>
       </c>
       <c r="B75" s="55" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C75" s="55" t="n">
+        <v>3</v>
       </c>
       <c r="D75" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="55" t="n">
-        <v>2500002</v>
+        <v>1920014</v>
       </c>
       <c r="G75" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_2</t>
+          <t>Human_Atlas_Weapon_Weapon_LR_14</t>
         </is>
       </c>
       <c r="K75" s="55" t="n">
-        <v>20100002</v>
+        <v>11020014</v>
       </c>
       <c r="L75" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-铁制头盔</t>
+          <t>精致短刀</t>
         </is>
       </c>
       <c r="M75" s="55" t="inlineStr">
@@ -3918,7 +3913,7 @@
     </row>
     <row r="76">
       <c r="A76" s="55" t="n">
-        <v>20100003</v>
+        <v>20100001</v>
       </c>
       <c r="B76" s="55" t="n">
         <v>1</v>
@@ -3930,30 +3925,25 @@
         <v>2</v>
       </c>
       <c r="F76" s="55" t="n">
-        <v>2500003</v>
+        <v>2500001</v>
       </c>
       <c r="G76" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_3</t>
+          <t>Skeleton_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K76" s="55" t="n">
-        <v>20100003</v>
+        <v>20100001</v>
       </c>
       <c r="L76" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-异域头巾</t>
-        </is>
-      </c>
-      <c r="M76" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>骷髅-帽子-皇冠-------------------</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="55" t="n">
-        <v>20100004</v>
+        <v>20100002</v>
       </c>
       <c r="B77" s="55" t="n">
         <v>1</v>
@@ -3965,19 +3955,19 @@
         <v>2</v>
       </c>
       <c r="F77" s="55" t="n">
-        <v>2500004</v>
+        <v>2500002</v>
       </c>
       <c r="G77" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_4</t>
+          <t>Skeleton_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K77" s="55" t="n">
-        <v>20100004</v>
+        <v>20100002</v>
       </c>
       <c r="L77" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-魔力帽</t>
+          <t>骷髅-帽子-铁制头盔</t>
         </is>
       </c>
       <c r="M77" s="55" t="inlineStr">
@@ -3988,7 +3978,7 @@
     </row>
     <row r="78">
       <c r="A78" s="55" t="n">
-        <v>20100005</v>
+        <v>20100003</v>
       </c>
       <c r="B78" s="55" t="n">
         <v>1</v>
@@ -4000,30 +3990,30 @@
         <v>2</v>
       </c>
       <c r="F78" s="55" t="n">
-        <v>2500005</v>
+        <v>2500003</v>
       </c>
       <c r="G78" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_5</t>
+          <t>Skeleton_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K78" s="55" t="n">
-        <v>20100005</v>
+        <v>20100003</v>
       </c>
       <c r="L78" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-草帽</t>
+          <t>骷髅-帽子-异域头巾</t>
         </is>
       </c>
       <c r="M78" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="55" t="n">
-        <v>20100006</v>
+        <v>20100004</v>
       </c>
       <c r="B79" s="55" t="n">
         <v>1</v>
@@ -4035,30 +4025,30 @@
         <v>2</v>
       </c>
       <c r="F79" s="55" t="n">
-        <v>2500006</v>
+        <v>2500004</v>
       </c>
       <c r="G79" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_6</t>
+          <t>Skeleton_Atlas_Hat_Hat_4</t>
         </is>
       </c>
       <c r="K79" s="55" t="n">
-        <v>20100006</v>
+        <v>20100004</v>
       </c>
       <c r="L79" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-恶魔头颅</t>
+          <t>骷髅-帽子-魔力帽</t>
         </is>
       </c>
       <c r="M79" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="55" t="n">
-        <v>20100007</v>
+        <v>20100005</v>
       </c>
       <c r="B80" s="55" t="n">
         <v>1</v>
@@ -4070,19 +4060,19 @@
         <v>2</v>
       </c>
       <c r="F80" s="55" t="n">
-        <v>2500007</v>
+        <v>2500005</v>
       </c>
       <c r="G80" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_7</t>
+          <t>Skeleton_Atlas_Hat_Hat_5</t>
         </is>
       </c>
       <c r="K80" s="55" t="n">
-        <v>20100007</v>
+        <v>20100005</v>
       </c>
       <c r="L80" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-魔王之角</t>
+          <t>骷髅-帽子-草帽</t>
         </is>
       </c>
       <c r="M80" s="55" t="inlineStr">
@@ -4093,10 +4083,10 @@
     </row>
     <row r="81">
       <c r="A81" s="55" t="n">
-        <v>20200001</v>
+        <v>20100006</v>
       </c>
       <c r="B81" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" s="55" t="n">
         <v>1</v>
@@ -4105,28 +4095,33 @@
         <v>2</v>
       </c>
       <c r="F81" s="55" t="n">
-        <v>2510001</v>
+        <v>2500006</v>
       </c>
       <c r="G81" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_1</t>
+          <t>Skeleton_Atlas_Hat_Hat_6</t>
         </is>
       </c>
       <c r="K81" s="55" t="n">
-        <v>20200001</v>
+        <v>20100006</v>
       </c>
       <c r="L81" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-肩甲1</t>
+          <t>骷髅-帽子-恶魔头颅</t>
+        </is>
+      </c>
+      <c r="M81" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="55" t="n">
-        <v>20200002</v>
+        <v>20100007</v>
       </c>
       <c r="B82" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" s="55" t="n">
         <v>1</v>
@@ -4135,25 +4130,30 @@
         <v>2</v>
       </c>
       <c r="F82" s="55" t="n">
-        <v>2510002</v>
+        <v>2500007</v>
       </c>
       <c r="G82" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_2</t>
+          <t>Skeleton_Atlas_Hat_Hat_7</t>
         </is>
       </c>
       <c r="K82" s="55" t="n">
-        <v>20200002</v>
+        <v>20100007</v>
       </c>
       <c r="L82" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-肩甲2</t>
+          <t>骷髅-帽子-魔王之角</t>
+        </is>
+      </c>
+      <c r="M82" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="55" t="n">
-        <v>20200003</v>
+        <v>20200001</v>
       </c>
       <c r="B83" s="55" t="n">
         <v>2</v>
@@ -4165,25 +4165,25 @@
         <v>2</v>
       </c>
       <c r="F83" s="55" t="n">
-        <v>2510003</v>
+        <v>2510001</v>
       </c>
       <c r="G83" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_3</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K83" s="55" t="n">
-        <v>20200003</v>
+        <v>20200001</v>
       </c>
       <c r="L83" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂的肩甲</t>
+          <t>骷髅-衣服-肩甲1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="55" t="n">
-        <v>20200004</v>
+        <v>20200002</v>
       </c>
       <c r="B84" s="55" t="n">
         <v>2</v>
@@ -4195,30 +4195,25 @@
         <v>2</v>
       </c>
       <c r="F84" s="55" t="n">
-        <v>2510004</v>
+        <v>2510002</v>
       </c>
       <c r="G84" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_4</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K84" s="55" t="n">
-        <v>20200004</v>
+        <v>20200002</v>
       </c>
       <c r="L84" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-丝绸披肩</t>
-        </is>
-      </c>
-      <c r="M84" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>骷髅-衣服-肩甲2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="55" t="n">
-        <v>20200005</v>
+        <v>20200003</v>
       </c>
       <c r="B85" s="55" t="n">
         <v>2</v>
@@ -4230,30 +4225,25 @@
         <v>2</v>
       </c>
       <c r="F85" s="55" t="n">
-        <v>2510005</v>
+        <v>2510003</v>
       </c>
       <c r="G85" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_5</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_3</t>
         </is>
       </c>
       <c r="K85" s="55" t="n">
-        <v>20200005</v>
+        <v>20200003</v>
       </c>
       <c r="L85" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-魔法披肩</t>
-        </is>
-      </c>
-      <c r="M85" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>骷髅-衣服-破烂的肩甲</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="55" t="n">
-        <v>20200006</v>
+        <v>20200004</v>
       </c>
       <c r="B86" s="55" t="n">
         <v>2</v>
@@ -4265,25 +4255,30 @@
         <v>2</v>
       </c>
       <c r="F86" s="55" t="n">
-        <v>2510006</v>
+        <v>2510004</v>
       </c>
       <c r="G86" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_6</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_4</t>
         </is>
       </c>
       <c r="K86" s="55" t="n">
-        <v>20200006</v>
+        <v>20200004</v>
       </c>
       <c r="L86" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-麻布衣</t>
+          <t>骷髅-衣服-丝绸披肩</t>
+        </is>
+      </c>
+      <c r="M86" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="55" t="n">
-        <v>20200007</v>
+        <v>20200005</v>
       </c>
       <c r="B87" s="55" t="n">
         <v>2</v>
@@ -4295,30 +4290,30 @@
         <v>2</v>
       </c>
       <c r="F87" s="55" t="n">
-        <v>2510007</v>
+        <v>2510005</v>
       </c>
       <c r="G87" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_7</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_5</t>
         </is>
       </c>
       <c r="K87" s="55" t="n">
-        <v>20200007</v>
+        <v>20200005</v>
       </c>
       <c r="L87" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-蔚蓝铠甲</t>
+          <t>骷髅-衣服-魔法披肩</t>
         </is>
       </c>
       <c r="M87" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="55" t="n">
-        <v>20200008</v>
+        <v>20200006</v>
       </c>
       <c r="B88" s="55" t="n">
         <v>2</v>
@@ -4330,25 +4325,25 @@
         <v>2</v>
       </c>
       <c r="F88" s="55" t="n">
-        <v>2510008</v>
+        <v>2510006</v>
       </c>
       <c r="G88" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_8</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_6</t>
         </is>
       </c>
       <c r="K88" s="55" t="n">
-        <v>20200008</v>
+        <v>20200006</v>
       </c>
       <c r="L88" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂法衣</t>
+          <t>骷髅-衣服-麻布衣</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="55" t="n">
-        <v>20200009</v>
+        <v>20200007</v>
       </c>
       <c r="B89" s="55" t="n">
         <v>2</v>
@@ -4360,19 +4355,19 @@
         <v>2</v>
       </c>
       <c r="F89" s="55" t="n">
-        <v>2510009</v>
+        <v>2510007</v>
       </c>
       <c r="G89" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_9</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_7</t>
         </is>
       </c>
       <c r="K89" s="55" t="n">
-        <v>20200009</v>
+        <v>20200007</v>
       </c>
       <c r="L89" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-琥珀铠甲</t>
+          <t>骷髅-衣服-蔚蓝铠甲</t>
         </is>
       </c>
       <c r="M89" s="55" t="inlineStr">
@@ -4383,7 +4378,7 @@
     </row>
     <row r="90">
       <c r="A90" s="55" t="n">
-        <v>20200010</v>
+        <v>20200008</v>
       </c>
       <c r="B90" s="55" t="n">
         <v>2</v>
@@ -4395,30 +4390,25 @@
         <v>2</v>
       </c>
       <c r="F90" s="55" t="n">
-        <v>2510010</v>
+        <v>2510008</v>
       </c>
       <c r="G90" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_10</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_8</t>
         </is>
       </c>
       <c r="K90" s="55" t="n">
-        <v>20200010</v>
+        <v>20200008</v>
       </c>
       <c r="L90" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-远古铠甲</t>
-        </is>
-      </c>
-      <c r="M90" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>骷髅-衣服-破烂法衣</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="55" t="n">
-        <v>20200011</v>
+        <v>20200009</v>
       </c>
       <c r="B91" s="55" t="n">
         <v>2</v>
@@ -4430,19 +4420,19 @@
         <v>2</v>
       </c>
       <c r="F91" s="55" t="n">
-        <v>2510011</v>
+        <v>2510009</v>
       </c>
       <c r="G91" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_11</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_9</t>
         </is>
       </c>
       <c r="K91" s="55" t="n">
-        <v>20200011</v>
+        <v>20200009</v>
       </c>
       <c r="L91" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-深红战衣</t>
+          <t>骷髅-衣服-琥珀铠甲</t>
         </is>
       </c>
       <c r="M91" s="55" t="inlineStr">
@@ -4453,10 +4443,10 @@
     </row>
     <row r="92">
       <c r="A92" s="55" t="n">
-        <v>20300001</v>
+        <v>20200010</v>
       </c>
       <c r="B92" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D92" s="55" t="n">
         <v>1</v>
@@ -4465,28 +4455,33 @@
         <v>2</v>
       </c>
       <c r="F92" s="55" t="n">
-        <v>2520001</v>
+        <v>2510010</v>
       </c>
       <c r="G92" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_1</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_10</t>
         </is>
       </c>
       <c r="K92" s="55" t="n">
-        <v>20300001</v>
+        <v>20200010</v>
       </c>
       <c r="L92" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂腰带</t>
+          <t>骷髅-衣服-远古铠甲</t>
+        </is>
+      </c>
+      <c r="M92" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="55" t="n">
-        <v>20300003</v>
+        <v>20200011</v>
       </c>
       <c r="B93" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D93" s="55" t="n">
         <v>1</v>
@@ -4495,25 +4490,30 @@
         <v>2</v>
       </c>
       <c r="F93" s="55" t="n">
-        <v>2520003</v>
+        <v>2510011</v>
       </c>
       <c r="G93" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_3</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_11</t>
         </is>
       </c>
       <c r="K93" s="55" t="n">
-        <v>20300003</v>
+        <v>20200011</v>
       </c>
       <c r="L93" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂法裤</t>
+          <t>骷髅-衣服-深红战衣</t>
+        </is>
+      </c>
+      <c r="M93" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="55" t="n">
-        <v>20300007</v>
+        <v>20300001</v>
       </c>
       <c r="B94" s="55" t="n">
         <v>3</v>
@@ -4525,30 +4525,25 @@
         <v>2</v>
       </c>
       <c r="F94" s="55" t="n">
-        <v>2520007</v>
+        <v>2520001</v>
       </c>
       <c r="G94" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_7</t>
+          <t>Skeleton_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K94" s="55" t="n">
-        <v>20300007</v>
+        <v>20300001</v>
       </c>
       <c r="L94" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-蔚蓝腰带</t>
-        </is>
-      </c>
-      <c r="M94" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-衣服-破烂腰带</t>
         </is>
       </c>
     </row>
     <row r="95" ht="12" customHeight="1" s="56">
       <c r="A95" s="55" t="n">
-        <v>20300009</v>
+        <v>20300003</v>
       </c>
       <c r="B95" s="55" t="n">
         <v>3</v>
@@ -4560,30 +4555,25 @@
         <v>2</v>
       </c>
       <c r="F95" s="55" t="n">
-        <v>2520009</v>
+        <v>2520003</v>
       </c>
       <c r="G95" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_9</t>
+          <t>Skeleton_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K95" s="55" t="n">
-        <v>20300009</v>
+        <v>20300003</v>
       </c>
       <c r="L95" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-琥珀腰带</t>
-        </is>
-      </c>
-      <c r="M95" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-衣服-破烂法裤</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="55" t="n">
-        <v>20300011</v>
+        <v>20300007</v>
       </c>
       <c r="B96" s="55" t="n">
         <v>3</v>
@@ -4595,19 +4585,19 @@
         <v>2</v>
       </c>
       <c r="F96" s="55" t="n">
-        <v>2520011</v>
+        <v>2520007</v>
       </c>
       <c r="G96" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_11</t>
+          <t>Skeleton_Atlas_Pants_Pants_7</t>
         </is>
       </c>
       <c r="K96" s="55" t="n">
-        <v>20300011</v>
+        <v>20300007</v>
       </c>
       <c r="L96" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-深红腰带</t>
+          <t>骷髅-衣服-蔚蓝腰带</t>
         </is>
       </c>
       <c r="M96" s="55" t="inlineStr">
@@ -4618,13 +4608,10 @@
     </row>
     <row r="97">
       <c r="A97" s="55" t="n">
-        <v>21000001</v>
+        <v>20300009</v>
       </c>
       <c r="B97" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C97" s="55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D97" s="55" t="n">
         <v>1</v>
@@ -4633,39 +4620,33 @@
         <v>2</v>
       </c>
       <c r="F97" s="55" t="n">
-        <v>2900001</v>
+        <v>2520009</v>
       </c>
       <c r="G97" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_1</t>
-        </is>
-      </c>
-      <c r="H97" s="55" t="n">
-        <v>45</v>
-      </c>
-      <c r="I97" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>Skeleton_Atlas_Pants_Pants_9</t>
         </is>
       </c>
       <c r="K97" s="55" t="n">
-        <v>21000001</v>
+        <v>20300009</v>
       </c>
       <c r="L97" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-骨头</t>
+          <t>骷髅-衣服-琥珀腰带</t>
+        </is>
+      </c>
+      <c r="M97" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="55" t="n">
-        <v>21000002</v>
+        <v>20300011</v>
       </c>
       <c r="B98" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C98" s="55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D98" s="55" t="n">
         <v>1</v>
@@ -4674,38 +4655,30 @@
         <v>2</v>
       </c>
       <c r="F98" s="55" t="n">
-        <v>2900002</v>
+        <v>2520011</v>
       </c>
       <c r="G98" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_2</t>
-        </is>
-      </c>
-      <c r="H98" s="55" t="n">
-        <v>45</v>
-      </c>
-      <c r="I98" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>Skeleton_Atlas_Pants_Pants_11</t>
         </is>
       </c>
       <c r="K98" s="55" t="n">
-        <v>21000002</v>
+        <v>20300011</v>
       </c>
       <c r="L98" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-鸡腿</t>
+          <t>骷髅-衣服-深红腰带</t>
         </is>
       </c>
       <c r="M98" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="55" t="n">
-        <v>21000003</v>
+        <v>21000001</v>
       </c>
       <c r="B99" s="55" t="n">
         <v>10</v>
@@ -4720,30 +4693,33 @@
         <v>2</v>
       </c>
       <c r="F99" s="55" t="n">
-        <v>2900003</v>
+        <v>2900001</v>
       </c>
       <c r="G99" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_3</t>
-        </is>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_1</t>
+        </is>
+      </c>
+      <c r="H99" s="55" t="n">
+        <v>45</v>
       </c>
       <c r="I99" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K99" s="55" t="n">
-        <v>21000003</v>
+        <v>21000001</v>
       </c>
       <c r="L99" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-无用之书</t>
+          <t>骷髅-武器-骨头</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="55" t="n">
-        <v>21000004</v>
+        <v>21000002</v>
       </c>
       <c r="B100" s="55" t="n">
         <v>10</v>
@@ -4758,30 +4734,38 @@
         <v>2</v>
       </c>
       <c r="F100" s="55" t="n">
-        <v>2900004</v>
+        <v>2900002</v>
       </c>
       <c r="G100" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_4</t>
-        </is>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_2</t>
+        </is>
+      </c>
+      <c r="H100" s="55" t="n">
+        <v>45</v>
       </c>
       <c r="I100" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_4&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K100" s="55" t="n">
-        <v>21000004</v>
+        <v>21000002</v>
       </c>
       <c r="L100" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-木制圆盾</t>
+          <t>骷髅-武器-鸡腿</t>
+        </is>
+      </c>
+      <c r="M100" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="55" t="n">
-        <v>21000005</v>
+        <v>21000003</v>
       </c>
       <c r="B101" s="55" t="n">
         <v>10</v>
@@ -4796,35 +4780,30 @@
         <v>2</v>
       </c>
       <c r="F101" s="55" t="n">
-        <v>2900005</v>
+        <v>2900003</v>
       </c>
       <c r="G101" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_5</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_3</t>
         </is>
       </c>
       <c r="I101" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_5&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K101" s="55" t="n">
-        <v>21000005</v>
+        <v>21000003</v>
       </c>
       <c r="L101" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-飞镖</t>
-        </is>
-      </c>
-      <c r="M101" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>骷髅-武器-无用之书</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="55" t="n">
-        <v>21000006</v>
+        <v>21000004</v>
       </c>
       <c r="B102" s="55" t="n">
         <v>10</v>
@@ -4839,35 +4818,30 @@
         <v>2</v>
       </c>
       <c r="F102" s="55" t="n">
-        <v>2900006</v>
+        <v>2900004</v>
       </c>
       <c r="G102" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_6</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_4</t>
         </is>
       </c>
       <c r="I102" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_6&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_4&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K102" s="55" t="n">
-        <v>21000006</v>
+        <v>21000004</v>
       </c>
       <c r="L102" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-骷髅头</t>
-        </is>
-      </c>
-      <c r="M102" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-武器-木制圆盾</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="55" t="n">
-        <v>21000007</v>
+        <v>21000005</v>
       </c>
       <c r="B103" s="55" t="n">
         <v>10</v>
@@ -4882,24 +4856,24 @@
         <v>2</v>
       </c>
       <c r="F103" s="55" t="n">
-        <v>2900007</v>
+        <v>2900005</v>
       </c>
       <c r="G103" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_7</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_5</t>
         </is>
       </c>
       <c r="I103" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_7&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_5&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K103" s="55" t="n">
-        <v>21000007</v>
+        <v>21000005</v>
       </c>
       <c r="L103" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-欧里给</t>
+          <t>骷髅-武器-飞镖</t>
         </is>
       </c>
       <c r="M103" s="55" t="inlineStr">
@@ -4910,7 +4884,7 @@
     </row>
     <row r="104">
       <c r="A104" s="55" t="n">
-        <v>21000008</v>
+        <v>21000006</v>
       </c>
       <c r="B104" s="55" t="n">
         <v>10</v>
@@ -4925,35 +4899,35 @@
         <v>2</v>
       </c>
       <c r="F104" s="55" t="n">
-        <v>2900008</v>
+        <v>2900006</v>
       </c>
       <c r="G104" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_8</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_6</t>
         </is>
       </c>
       <c r="I104" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_8&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_6&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K104" s="55" t="n">
-        <v>21000008</v>
+        <v>21000006</v>
       </c>
       <c r="L104" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-苹果</t>
+          <t>骷髅-武器-骷髅头</t>
         </is>
       </c>
       <c r="M104" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="55" t="n">
-        <v>21000009</v>
+        <v>21000007</v>
       </c>
       <c r="B105" s="55" t="n">
         <v>10</v>
@@ -4968,35 +4942,35 @@
         <v>2</v>
       </c>
       <c r="F105" s="55" t="n">
-        <v>2900009</v>
+        <v>2900007</v>
       </c>
       <c r="G105" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_9</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_7</t>
         </is>
       </c>
       <c r="I105" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_9&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_7&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K105" s="55" t="n">
-        <v>21000009</v>
+        <v>21000007</v>
       </c>
       <c r="L105" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-28年拉菲</t>
+          <t>骷髅-武器-欧里给</t>
         </is>
       </c>
       <c r="M105" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="55" t="n">
-        <v>21000010</v>
+        <v>21000008</v>
       </c>
       <c r="B106" s="55" t="n">
         <v>10</v>
@@ -5011,41 +4985,41 @@
         <v>2</v>
       </c>
       <c r="F106" s="55" t="n">
-        <v>2900010</v>
+        <v>2900008</v>
       </c>
       <c r="G106" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_10</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_8</t>
         </is>
       </c>
       <c r="I106" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_10&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_8&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K106" s="55" t="n">
-        <v>21000010</v>
+        <v>21000008</v>
       </c>
       <c r="L106" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-金币</t>
+          <t>骷髅-武器-苹果</t>
         </is>
       </c>
       <c r="M106" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="55" t="n">
-        <v>21010001</v>
+        <v>21000009</v>
       </c>
       <c r="B107" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C107" s="55" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D107" s="55" t="n">
         <v>1</v>
@@ -5054,39 +5028,41 @@
         <v>2</v>
       </c>
       <c r="F107" s="55" t="n">
-        <v>2910001</v>
+        <v>2900009</v>
       </c>
       <c r="G107" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_1</t>
-        </is>
-      </c>
-      <c r="H107" s="55" t="n">
-        <v>-45</v>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_9</t>
+        </is>
+      </c>
+      <c r="I107" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_9&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+        </is>
       </c>
       <c r="K107" s="55" t="n">
-        <v>21010001</v>
+        <v>21000009</v>
       </c>
       <c r="L107" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-铁剑</t>
+          <t>骷髅-武器-28年拉菲</t>
         </is>
       </c>
       <c r="M107" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="55" t="n">
-        <v>21010002</v>
+        <v>21000010</v>
       </c>
       <c r="B108" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C108" s="55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D108" s="55" t="n">
         <v>1</v>
@@ -5095,34 +5071,41 @@
         <v>2</v>
       </c>
       <c r="F108" s="55" t="n">
-        <v>2910002</v>
+        <v>2900010</v>
       </c>
       <c r="G108" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_2</t>
-        </is>
-      </c>
-      <c r="H108" s="55" t="n">
-        <v>-45</v>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_10</t>
+        </is>
+      </c>
+      <c r="I108" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_10&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+        </is>
       </c>
       <c r="K108" s="55" t="n">
-        <v>21010002</v>
+        <v>21000010</v>
       </c>
       <c r="L108" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-火法杖</t>
+          <t>骷髅-武器-金币</t>
+        </is>
+      </c>
+      <c r="M108" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="55" t="n">
-        <v>21010003</v>
+        <v>21010001</v>
       </c>
       <c r="B109" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C109" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" s="55" t="n">
         <v>1</v>
@@ -5131,34 +5114,39 @@
         <v>2</v>
       </c>
       <c r="F109" s="55" t="n">
-        <v>2910003</v>
+        <v>2910001</v>
       </c>
       <c r="G109" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_3</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_1</t>
         </is>
       </c>
       <c r="H109" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K109" s="55" t="n">
-        <v>21010003</v>
+        <v>21010001</v>
       </c>
       <c r="L109" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-冰法杖</t>
+          <t>骷髅-武器-铁剑</t>
+        </is>
+      </c>
+      <c r="M109" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="55" t="n">
-        <v>21010004</v>
+        <v>21010002</v>
       </c>
       <c r="B110" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C110" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110" s="55" t="n">
         <v>1</v>
@@ -5167,34 +5155,34 @@
         <v>2</v>
       </c>
       <c r="F110" s="55" t="n">
-        <v>2910004</v>
+        <v>2910002</v>
       </c>
       <c r="G110" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_4</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_2</t>
         </is>
       </c>
       <c r="H110" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K110" s="55" t="n">
-        <v>21010004</v>
+        <v>21010002</v>
       </c>
       <c r="L110" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-残破剑</t>
+          <t>骷髅-武器-火法杖</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="55" t="n">
-        <v>21010005</v>
+        <v>21010003</v>
       </c>
       <c r="B111" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C111" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" s="55" t="n">
         <v>1</v>
@@ -5203,25 +5191,28 @@
         <v>2</v>
       </c>
       <c r="F111" s="55" t="n">
-        <v>2910005</v>
+        <v>2910003</v>
       </c>
       <c r="G111" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_5</t>
-        </is>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_3</t>
+        </is>
+      </c>
+      <c r="H111" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K111" s="55" t="n">
-        <v>21010005</v>
+        <v>21010003</v>
       </c>
       <c r="L111" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-短刀</t>
+          <t>骷髅-武器-冰法杖</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="55" t="n">
-        <v>21010006</v>
+        <v>21010004</v>
       </c>
       <c r="B112" s="55" t="n">
         <v>10</v>
@@ -5236,30 +5227,28 @@
         <v>2</v>
       </c>
       <c r="F112" s="55" t="n">
-        <v>2910006</v>
+        <v>2910004</v>
       </c>
       <c r="G112" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_6</t>
-        </is>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_4</t>
+        </is>
+      </c>
+      <c r="H112" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K112" s="55" t="n">
-        <v>21010006</v>
+        <v>21010004</v>
       </c>
       <c r="L112" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-骷髅剑</t>
-        </is>
-      </c>
-      <c r="M112" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-武器-残破剑</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="55" t="n">
-        <v>21010007</v>
+        <v>21010005</v>
       </c>
       <c r="B113" s="55" t="n">
         <v>10</v>
@@ -5274,30 +5263,25 @@
         <v>2</v>
       </c>
       <c r="F113" s="55" t="n">
-        <v>2910007</v>
+        <v>2910005</v>
       </c>
       <c r="G113" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_7</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_5</t>
         </is>
       </c>
       <c r="K113" s="55" t="n">
-        <v>21010007</v>
+        <v>21010005</v>
       </c>
       <c r="L113" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-金色刺剑</t>
-        </is>
-      </c>
-      <c r="M113" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-武器-短刀</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="55" t="n">
-        <v>21010008</v>
+        <v>21010006</v>
       </c>
       <c r="B114" s="55" t="n">
         <v>10</v>
@@ -5312,25 +5296,30 @@
         <v>2</v>
       </c>
       <c r="F114" s="55" t="n">
-        <v>2910008</v>
+        <v>2910006</v>
       </c>
       <c r="G114" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_8</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_6</t>
         </is>
       </c>
       <c r="K114" s="55" t="n">
-        <v>21010008</v>
+        <v>21010006</v>
       </c>
       <c r="L114" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-铲子</t>
+          <t>骷髅-武器-骷髅剑</t>
+        </is>
+      </c>
+      <c r="M114" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="55" t="n">
-        <v>21010009</v>
+        <v>21010007</v>
       </c>
       <c r="B115" s="55" t="n">
         <v>10</v>
@@ -5345,19 +5334,19 @@
         <v>2</v>
       </c>
       <c r="F115" s="55" t="n">
-        <v>2910009</v>
+        <v>2910007</v>
       </c>
       <c r="G115" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_9</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_7</t>
         </is>
       </c>
       <c r="K115" s="55" t="n">
-        <v>21010009</v>
+        <v>21010007</v>
       </c>
       <c r="L115" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-冰之哀伤</t>
+          <t>骷髅-武器-金色刺剑</t>
         </is>
       </c>
       <c r="M115" s="55" t="inlineStr">
@@ -5368,7 +5357,7 @@
     </row>
     <row r="116">
       <c r="A116" s="55" t="n">
-        <v>21010010</v>
+        <v>21010008</v>
       </c>
       <c r="B116" s="55" t="n">
         <v>10</v>
@@ -5383,36 +5372,31 @@
         <v>2</v>
       </c>
       <c r="F116" s="55" t="n">
-        <v>2910010</v>
+        <v>2910008</v>
       </c>
       <c r="G116" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_10</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_8</t>
         </is>
       </c>
       <c r="K116" s="55" t="n">
-        <v>21010010</v>
+        <v>21010008</v>
       </c>
       <c r="L116" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-火之高兴</t>
-        </is>
-      </c>
-      <c r="M116" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-武器-铲子</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="55" t="n">
-        <v>21010011</v>
+        <v>21010009</v>
       </c>
       <c r="B117" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C117" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" s="55" t="n">
         <v>1</v>
@@ -5421,39 +5405,36 @@
         <v>2</v>
       </c>
       <c r="F117" s="55" t="n">
-        <v>2910011</v>
+        <v>2910009</v>
       </c>
       <c r="G117" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_11</t>
-        </is>
-      </c>
-      <c r="H117" s="55" t="n">
-        <v>-45</v>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_9</t>
+        </is>
       </c>
       <c r="K117" s="55" t="n">
-        <v>21010011</v>
+        <v>21010009</v>
       </c>
       <c r="L117" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-绿宝石法杖</t>
+          <t>骷髅-武器-冰之哀伤</t>
         </is>
       </c>
       <c r="M117" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="55" t="n">
-        <v>21010012</v>
+        <v>21010010</v>
       </c>
       <c r="B118" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C118" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" s="55" t="n">
         <v>1</v>
@@ -5462,33 +5443,30 @@
         <v>2</v>
       </c>
       <c r="F118" s="55" t="n">
-        <v>2910012</v>
+        <v>2910010</v>
       </c>
       <c r="G118" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_12</t>
-        </is>
-      </c>
-      <c r="H118" s="55" t="n">
-        <v>-45</v>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_10</t>
+        </is>
       </c>
       <c r="K118" s="55" t="n">
-        <v>21010012</v>
+        <v>21010010</v>
       </c>
       <c r="L118" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-魔力法杖</t>
+          <t>骷髅-武器-火之高兴</t>
         </is>
       </c>
       <c r="M118" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="55" t="n">
-        <v>21010013</v>
+        <v>21010011</v>
       </c>
       <c r="B119" s="55" t="n">
         <v>10</v>
@@ -5503,19 +5481,22 @@
         <v>2</v>
       </c>
       <c r="F119" s="55" t="n">
-        <v>2910013</v>
+        <v>2910011</v>
       </c>
       <c r="G119" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_13</t>
-        </is>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_11</t>
+        </is>
+      </c>
+      <c r="H119" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K119" s="55" t="n">
-        <v>21010013</v>
+        <v>21010011</v>
       </c>
       <c r="L119" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-扫帚</t>
+          <t>骷髅-武器-绿宝石法杖</t>
         </is>
       </c>
       <c r="M119" s="55" t="inlineStr">
@@ -5526,7 +5507,7 @@
     </row>
     <row r="120">
       <c r="A120" s="55" t="n">
-        <v>21010014</v>
+        <v>21010012</v>
       </c>
       <c r="B120" s="55" t="n">
         <v>10</v>
@@ -5541,30 +5522,33 @@
         <v>2</v>
       </c>
       <c r="F120" s="55" t="n">
-        <v>2910014</v>
+        <v>2910012</v>
       </c>
       <c r="G120" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_14</t>
-        </is>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_12</t>
+        </is>
+      </c>
+      <c r="H120" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K120" s="55" t="n">
-        <v>21010014</v>
+        <v>21010012</v>
       </c>
       <c r="L120" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-星之法杖</t>
+          <t>骷髅-武器-魔力法杖</t>
         </is>
       </c>
       <c r="M120" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="55" t="n">
-        <v>21010015</v>
+        <v>21010013</v>
       </c>
       <c r="B121" s="55" t="n">
         <v>10</v>
@@ -5579,30 +5563,30 @@
         <v>2</v>
       </c>
       <c r="F121" s="55" t="n">
-        <v>2910015</v>
+        <v>2910013</v>
       </c>
       <c r="G121" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_15</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_13</t>
         </is>
       </c>
       <c r="K121" s="55" t="n">
-        <v>21010015</v>
+        <v>21010013</v>
       </c>
       <c r="L121" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-百变法杖</t>
+          <t>骷髅-武器-扫帚</t>
         </is>
       </c>
       <c r="M121" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="55" t="n">
-        <v>21010016</v>
+        <v>21010014</v>
       </c>
       <c r="B122" s="55" t="n">
         <v>10</v>
@@ -5617,19 +5601,19 @@
         <v>2</v>
       </c>
       <c r="F122" s="55" t="n">
-        <v>2910016</v>
+        <v>2910014</v>
       </c>
       <c r="G122" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_16</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_14</t>
         </is>
       </c>
       <c r="K122" s="55" t="n">
-        <v>21010016</v>
+        <v>21010014</v>
       </c>
       <c r="L122" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-琥珀法杖</t>
+          <t>骷髅-武器-星之法杖</t>
         </is>
       </c>
       <c r="M122" s="55" t="inlineStr">
@@ -5640,7 +5624,7 @@
     </row>
     <row r="123">
       <c r="A123" s="55" t="n">
-        <v>21010017</v>
+        <v>21010015</v>
       </c>
       <c r="B123" s="55" t="n">
         <v>10</v>
@@ -5655,19 +5639,19 @@
         <v>2</v>
       </c>
       <c r="F123" s="55" t="n">
-        <v>2910017</v>
+        <v>2910015</v>
       </c>
       <c r="G123" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_17</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_15</t>
         </is>
       </c>
       <c r="K123" s="55" t="n">
-        <v>21010017</v>
+        <v>21010015</v>
       </c>
       <c r="L123" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-爱之天使</t>
+          <t>骷髅-武器-百变法杖</t>
         </is>
       </c>
       <c r="M123" s="55" t="inlineStr">
@@ -5678,7 +5662,7 @@
     </row>
     <row r="124">
       <c r="A124" s="55" t="n">
-        <v>21010018</v>
+        <v>21010016</v>
       </c>
       <c r="B124" s="55" t="n">
         <v>10</v>
@@ -5693,19 +5677,19 @@
         <v>2</v>
       </c>
       <c r="F124" s="55" t="n">
-        <v>2910018</v>
+        <v>2910016</v>
       </c>
       <c r="G124" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_18</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_16</t>
         </is>
       </c>
       <c r="K124" s="55" t="n">
-        <v>21010018</v>
+        <v>21010016</v>
       </c>
       <c r="L124" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-星域之杖</t>
+          <t>骷髅-武器-琥珀法杖</t>
         </is>
       </c>
       <c r="M124" s="55" t="inlineStr">
@@ -5716,7 +5700,7 @@
     </row>
     <row r="125">
       <c r="A125" s="55" t="n">
-        <v>21010019</v>
+        <v>21010017</v>
       </c>
       <c r="B125" s="55" t="n">
         <v>10</v>
@@ -5731,30 +5715,30 @@
         <v>2</v>
       </c>
       <c r="F125" s="55" t="n">
-        <v>2910019</v>
+        <v>2910017</v>
       </c>
       <c r="G125" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_19</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_17</t>
         </is>
       </c>
       <c r="K125" s="55" t="n">
-        <v>21010019</v>
+        <v>21010017</v>
       </c>
       <c r="L125" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-结晶法杖</t>
+          <t>骷髅-武器-爱之天使</t>
         </is>
       </c>
       <c r="M125" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="55" t="n">
-        <v>21010020</v>
+        <v>21010018</v>
       </c>
       <c r="B126" s="55" t="n">
         <v>10</v>
@@ -5769,54 +5753,57 @@
         <v>2</v>
       </c>
       <c r="F126" s="55" t="n">
-        <v>2910020</v>
+        <v>2910018</v>
       </c>
       <c r="G126" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_20</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_18</t>
         </is>
       </c>
       <c r="K126" s="55" t="n">
-        <v>21010020</v>
+        <v>21010018</v>
       </c>
       <c r="L126" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-黑暗法杖</t>
+          <t>骷髅-武器-星域之杖</t>
         </is>
       </c>
       <c r="M126" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="55" t="n">
-        <v>30100001</v>
+        <v>21010019</v>
       </c>
       <c r="B127" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C127" s="55" t="n">
         <v>1</v>
       </c>
       <c r="D127" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E127" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F127" s="55" t="n">
-        <v>3020001</v>
+        <v>2910019</v>
       </c>
       <c r="G127" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_1</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_19</t>
         </is>
       </c>
       <c r="K127" s="55" t="n">
-        <v>30100001</v>
+        <v>21010019</v>
       </c>
       <c r="L127" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-1</t>
+          <t>骷髅-武器-结晶法杖</t>
         </is>
       </c>
       <c r="M127" s="55" t="inlineStr">
@@ -5827,37 +5814,45 @@
     </row>
     <row r="128">
       <c r="A128" s="55" t="n">
-        <v>30100002</v>
+        <v>21010020</v>
       </c>
       <c r="B128" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C128" s="55" t="n">
         <v>1</v>
       </c>
       <c r="D128" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E128" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F128" s="55" t="n">
-        <v>3020002</v>
+        <v>2910020</v>
       </c>
       <c r="G128" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_2</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_20</t>
         </is>
       </c>
       <c r="K128" s="55" t="n">
-        <v>30100002</v>
+        <v>21010020</v>
       </c>
       <c r="L128" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-2</t>
+          <t>骷髅-武器-黑暗法杖</t>
+        </is>
+      </c>
+      <c r="M128" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="55" t="n">
-        <v>30100003</v>
+        <v>30100001</v>
       </c>
       <c r="B129" s="55" t="n">
         <v>1</v>
@@ -5869,30 +5864,30 @@
         <v>3</v>
       </c>
       <c r="F129" s="55" t="n">
-        <v>3020003</v>
+        <v>3020001</v>
       </c>
       <c r="G129" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_3</t>
+          <t>Slime_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K129" s="55" t="n">
-        <v>30100003</v>
+        <v>30100001</v>
       </c>
       <c r="L129" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-3</t>
+          <t>史莱姆-帽子-1</t>
         </is>
       </c>
       <c r="M129" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="55" t="n">
-        <v>30100004</v>
+        <v>30100002</v>
       </c>
       <c r="B130" s="55" t="n">
         <v>1</v>
@@ -5904,30 +5899,25 @@
         <v>3</v>
       </c>
       <c r="F130" s="55" t="n">
-        <v>3020004</v>
+        <v>3020002</v>
       </c>
       <c r="G130" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_4</t>
+          <t>Slime_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K130" s="55" t="n">
-        <v>30100004</v>
+        <v>30100002</v>
       </c>
       <c r="L130" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-4</t>
-        </is>
-      </c>
-      <c r="M130" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>史莱姆-帽子-2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="55" t="n">
-        <v>30100005</v>
+        <v>30100003</v>
       </c>
       <c r="B131" s="55" t="n">
         <v>1</v>
@@ -5939,19 +5929,19 @@
         <v>3</v>
       </c>
       <c r="F131" s="55" t="n">
-        <v>3020005</v>
+        <v>3020003</v>
       </c>
       <c r="G131" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_5</t>
+          <t>Slime_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K131" s="55" t="n">
-        <v>30100005</v>
+        <v>30100003</v>
       </c>
       <c r="L131" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-5</t>
+          <t>史莱姆-帽子-3</t>
         </is>
       </c>
       <c r="M131" s="55" t="inlineStr">
@@ -5962,7 +5952,7 @@
     </row>
     <row r="132" ht="15" customHeight="1" s="56">
       <c r="A132" s="55" t="n">
-        <v>30100006</v>
+        <v>30100004</v>
       </c>
       <c r="B132" s="55" t="n">
         <v>1</v>
@@ -5974,30 +5964,30 @@
         <v>3</v>
       </c>
       <c r="F132" s="55" t="n">
-        <v>3020006</v>
+        <v>3020004</v>
       </c>
       <c r="G132" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_6</t>
+          <t>Slime_Atlas_Hat_Hat_4</t>
         </is>
       </c>
       <c r="K132" s="55" t="n">
-        <v>30100006</v>
+        <v>30100004</v>
       </c>
       <c r="L132" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-6</t>
+          <t>史莱姆-帽子-4</t>
         </is>
       </c>
       <c r="M132" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="56">
       <c r="A133" s="55" t="n">
-        <v>30100007</v>
+        <v>30100005</v>
       </c>
       <c r="B133" s="55" t="n">
         <v>1</v>
@@ -6009,25 +5999,30 @@
         <v>3</v>
       </c>
       <c r="F133" s="55" t="n">
-        <v>3020007</v>
+        <v>3020005</v>
       </c>
       <c r="G133" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_7</t>
+          <t>Slime_Atlas_Hat_Hat_5</t>
         </is>
       </c>
       <c r="K133" s="55" t="n">
-        <v>30100007</v>
+        <v>30100005</v>
       </c>
       <c r="L133" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-7</t>
+          <t>史莱姆-帽子-5</t>
+        </is>
+      </c>
+      <c r="M133" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="56">
       <c r="A134" s="55" t="n">
-        <v>30100008</v>
+        <v>30100006</v>
       </c>
       <c r="B134" s="55" t="n">
         <v>1</v>
@@ -6039,30 +6034,30 @@
         <v>3</v>
       </c>
       <c r="F134" s="55" t="n">
-        <v>3020008</v>
+        <v>3020006</v>
       </c>
       <c r="G134" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_8</t>
+          <t>Slime_Atlas_Hat_Hat_6</t>
         </is>
       </c>
       <c r="K134" s="55" t="n">
-        <v>30100008</v>
+        <v>30100006</v>
       </c>
       <c r="L134" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-8</t>
+          <t>史莱姆-帽子-6</t>
         </is>
       </c>
       <c r="M134" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="56">
       <c r="A135" s="55" t="n">
-        <v>30100009</v>
+        <v>30100007</v>
       </c>
       <c r="B135" s="55" t="n">
         <v>1</v>
@@ -6074,30 +6069,25 @@
         <v>3</v>
       </c>
       <c r="F135" s="55" t="n">
-        <v>3020009</v>
+        <v>3020007</v>
       </c>
       <c r="G135" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_9</t>
+          <t>Slime_Atlas_Hat_Hat_7</t>
         </is>
       </c>
       <c r="K135" s="55" t="n">
-        <v>30100009</v>
+        <v>30100007</v>
       </c>
       <c r="L135" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-9</t>
-        </is>
-      </c>
-      <c r="M135" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>史莱姆-帽子-7</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="56">
       <c r="A136" s="55" t="n">
-        <v>30100010</v>
+        <v>30100008</v>
       </c>
       <c r="B136" s="55" t="n">
         <v>1</v>
@@ -6109,19 +6099,19 @@
         <v>3</v>
       </c>
       <c r="F136" s="55" t="n">
-        <v>3020010</v>
+        <v>3020008</v>
       </c>
       <c r="G136" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_10</t>
+          <t>Slime_Atlas_Hat_Hat_8</t>
         </is>
       </c>
       <c r="K136" s="55" t="n">
-        <v>30100010</v>
+        <v>30100008</v>
       </c>
       <c r="L136" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-10</t>
+          <t>史莱姆-帽子-8</t>
         </is>
       </c>
       <c r="M136" s="55" t="inlineStr">
@@ -6132,7 +6122,7 @@
     </row>
     <row r="137" ht="15" customHeight="1" s="56">
       <c r="A137" s="55" t="n">
-        <v>30100011</v>
+        <v>30100009</v>
       </c>
       <c r="B137" s="55" t="n">
         <v>1</v>
@@ -6144,30 +6134,30 @@
         <v>3</v>
       </c>
       <c r="F137" s="55" t="n">
-        <v>3020011</v>
+        <v>3020009</v>
       </c>
       <c r="G137" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_11</t>
+          <t>Slime_Atlas_Hat_Hat_9</t>
         </is>
       </c>
       <c r="K137" s="55" t="n">
-        <v>30100011</v>
+        <v>30100009</v>
       </c>
       <c r="L137" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-11</t>
+          <t>史莱姆-帽子-9</t>
         </is>
       </c>
       <c r="M137" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="56">
       <c r="A138" s="55" t="n">
-        <v>30100012</v>
+        <v>30100010</v>
       </c>
       <c r="B138" s="55" t="n">
         <v>1</v>
@@ -6179,30 +6169,30 @@
         <v>3</v>
       </c>
       <c r="F138" s="55" t="n">
-        <v>3020012</v>
+        <v>3020010</v>
       </c>
       <c r="G138" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_12</t>
+          <t>Slime_Atlas_Hat_Hat_10</t>
         </is>
       </c>
       <c r="K138" s="55" t="n">
-        <v>30100012</v>
+        <v>30100010</v>
       </c>
       <c r="L138" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-12</t>
+          <t>史莱姆-帽子-10</t>
         </is>
       </c>
       <c r="M138" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="56">
       <c r="A139" s="55" t="n">
-        <v>30100013</v>
+        <v>30100011</v>
       </c>
       <c r="B139" s="55" t="n">
         <v>1</v>
@@ -6214,30 +6204,30 @@
         <v>3</v>
       </c>
       <c r="F139" s="55" t="n">
-        <v>3020013</v>
+        <v>3020011</v>
       </c>
       <c r="G139" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_13</t>
+          <t>Slime_Atlas_Hat_Hat_11</t>
         </is>
       </c>
       <c r="K139" s="55" t="n">
-        <v>30100013</v>
+        <v>30100011</v>
       </c>
       <c r="L139" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-13</t>
+          <t>史莱姆-帽子-11</t>
         </is>
       </c>
       <c r="M139" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="56">
       <c r="A140" s="55" t="n">
-        <v>30100014</v>
+        <v>30100012</v>
       </c>
       <c r="B140" s="55" t="n">
         <v>1</v>
@@ -6249,30 +6239,30 @@
         <v>3</v>
       </c>
       <c r="F140" s="55" t="n">
-        <v>3020014</v>
+        <v>3020012</v>
       </c>
       <c r="G140" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_14</t>
+          <t>Slime_Atlas_Hat_Hat_12</t>
         </is>
       </c>
       <c r="K140" s="55" t="n">
-        <v>30100014</v>
+        <v>30100012</v>
       </c>
       <c r="L140" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-14</t>
+          <t>史莱姆-帽子-12</t>
         </is>
       </c>
       <c r="M140" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="56">
       <c r="A141" s="55" t="n">
-        <v>30100015</v>
+        <v>30100013</v>
       </c>
       <c r="B141" s="55" t="n">
         <v>1</v>
@@ -6284,30 +6274,30 @@
         <v>3</v>
       </c>
       <c r="F141" s="55" t="n">
-        <v>3020015</v>
+        <v>3020013</v>
       </c>
       <c r="G141" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_15</t>
+          <t>Slime_Atlas_Hat_Hat_13</t>
         </is>
       </c>
       <c r="K141" s="55" t="n">
-        <v>30100015</v>
+        <v>30100013</v>
       </c>
       <c r="L141" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-15</t>
+          <t>史莱姆-帽子-13</t>
         </is>
       </c>
       <c r="M141" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="56">
       <c r="A142" s="55" t="n">
-        <v>30100016</v>
+        <v>30100014</v>
       </c>
       <c r="B142" s="55" t="n">
         <v>1</v>
@@ -6319,30 +6309,30 @@
         <v>3</v>
       </c>
       <c r="F142" s="55" t="n">
-        <v>3020016</v>
+        <v>3020014</v>
       </c>
       <c r="G142" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_16</t>
+          <t>Slime_Atlas_Hat_Hat_14</t>
         </is>
       </c>
       <c r="K142" s="55" t="n">
-        <v>30100016</v>
+        <v>30100014</v>
       </c>
       <c r="L142" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-16</t>
+          <t>史莱姆-帽子-14</t>
         </is>
       </c>
       <c r="M142" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="55" t="n">
-        <v>30100017</v>
+        <v>30100015</v>
       </c>
       <c r="B143" s="55" t="n">
         <v>1</v>
@@ -6354,30 +6344,30 @@
         <v>3</v>
       </c>
       <c r="F143" s="55" t="n">
-        <v>3020017</v>
+        <v>3020015</v>
       </c>
       <c r="G143" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_17</t>
+          <t>Slime_Atlas_Hat_Hat_15</t>
         </is>
       </c>
       <c r="K143" s="55" t="n">
-        <v>30100017</v>
+        <v>30100015</v>
       </c>
       <c r="L143" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-17</t>
+          <t>史莱姆-帽子-15</t>
         </is>
       </c>
       <c r="M143" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="55" t="n">
-        <v>30100018</v>
+        <v>30100016</v>
       </c>
       <c r="B144" s="55" t="n">
         <v>1</v>
@@ -6389,19 +6379,19 @@
         <v>3</v>
       </c>
       <c r="F144" s="55" t="n">
-        <v>3020018</v>
+        <v>3020016</v>
       </c>
       <c r="G144" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_18</t>
+          <t>Slime_Atlas_Hat_Hat_16</t>
         </is>
       </c>
       <c r="K144" s="55" t="n">
-        <v>30100018</v>
+        <v>30100016</v>
       </c>
       <c r="L144" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-18</t>
+          <t>史莱姆-帽子-16</t>
         </is>
       </c>
       <c r="M144" s="55" t="inlineStr">
@@ -6412,7 +6402,7 @@
     </row>
     <row r="145">
       <c r="A145" s="55" t="n">
-        <v>30100019</v>
+        <v>30100017</v>
       </c>
       <c r="B145" s="55" t="n">
         <v>1</v>
@@ -6424,19 +6414,19 @@
         <v>3</v>
       </c>
       <c r="F145" s="55" t="n">
-        <v>3020019</v>
+        <v>3020017</v>
       </c>
       <c r="G145" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_19</t>
+          <t>Slime_Atlas_Hat_Hat_17</t>
         </is>
       </c>
       <c r="K145" s="55" t="n">
-        <v>30100019</v>
+        <v>30100017</v>
       </c>
       <c r="L145" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-19</t>
+          <t>史莱姆-帽子-17</t>
         </is>
       </c>
       <c r="M145" s="55" t="inlineStr">
@@ -6447,7 +6437,7 @@
     </row>
     <row r="146" ht="12" customHeight="1" s="56">
       <c r="A146" s="55" t="n">
-        <v>30100020</v>
+        <v>30100018</v>
       </c>
       <c r="B146" s="55" t="n">
         <v>1</v>
@@ -6459,19 +6449,19 @@
         <v>3</v>
       </c>
       <c r="F146" s="55" t="n">
-        <v>3020020</v>
+        <v>3020018</v>
       </c>
       <c r="G146" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_20</t>
+          <t>Slime_Atlas_Hat_Hat_18</t>
         </is>
       </c>
       <c r="K146" s="55" t="n">
-        <v>30100020</v>
+        <v>30100018</v>
       </c>
       <c r="L146" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-20</t>
+          <t>史莱姆-帽子-18</t>
         </is>
       </c>
       <c r="M146" s="55" t="inlineStr">
@@ -6482,7 +6472,7 @@
     </row>
     <row r="147">
       <c r="A147" s="55" t="n">
-        <v>40100001</v>
+        <v>30100019</v>
       </c>
       <c r="B147" s="55" t="n">
         <v>1</v>
@@ -6491,66 +6481,71 @@
         <v>1</v>
       </c>
       <c r="E147" s="55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F147" s="55" t="n">
-        <v>4500003</v>
+        <v>3020019</v>
       </c>
       <c r="G147" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Hat_Hat_3</t>
+          <t>Slime_Atlas_Hat_Hat_19</t>
         </is>
       </c>
       <c r="K147" s="55" t="n">
-        <v>40100001</v>
+        <v>30100019</v>
       </c>
       <c r="L147" s="55" t="inlineStr">
         <is>
-          <t>修女帽</t>
+          <t>史莱姆-帽子-19</t>
         </is>
       </c>
       <c r="M147" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="55" t="n">
-        <v>40200001</v>
+        <v>30100020</v>
       </c>
       <c r="B148" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E148" s="55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F148" s="55" t="n">
-        <v>4510001</v>
+        <v>3020020</v>
       </c>
       <c r="G148" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_1</t>
+          <t>Slime_Atlas_Hat_Hat_20</t>
         </is>
       </c>
       <c r="K148" s="55" t="n">
-        <v>40200001</v>
+        <v>30100020</v>
       </c>
       <c r="L148" s="55" t="inlineStr">
         <is>
-          <t>粉色胸罩</t>
+          <t>史莱姆-帽子-20</t>
+        </is>
+      </c>
+      <c r="M148" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="55" t="n">
-        <v>40200002</v>
+        <v>40100001</v>
       </c>
       <c r="B149" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" s="55" t="n">
         <v>1</v>
@@ -6559,25 +6554,30 @@
         <v>4</v>
       </c>
       <c r="F149" s="55" t="n">
-        <v>4510002</v>
+        <v>4500003</v>
       </c>
       <c r="G149" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_2</t>
+          <t>Succubus_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K149" s="55" t="n">
-        <v>40200002</v>
+        <v>40100001</v>
       </c>
       <c r="L149" s="55" t="inlineStr">
         <is>
-          <t>红色胸罩</t>
+          <t>修女帽</t>
+        </is>
+      </c>
+      <c r="M149" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="55" t="n">
-        <v>40200003</v>
+        <v>40200001</v>
       </c>
       <c r="B150" s="55" t="n">
         <v>2</v>
@@ -6589,30 +6589,25 @@
         <v>4</v>
       </c>
       <c r="F150" s="55" t="n">
-        <v>4510003</v>
+        <v>4510001</v>
       </c>
       <c r="G150" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_3</t>
+          <t>Succubus_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K150" s="55" t="n">
-        <v>40200003</v>
+        <v>40200001</v>
       </c>
       <c r="L150" s="55" t="inlineStr">
         <is>
-          <t>修女服</t>
-        </is>
-      </c>
-      <c r="M150" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>粉色胸罩</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="55" t="n">
-        <v>40200004</v>
+        <v>40200002</v>
       </c>
       <c r="B151" s="55" t="n">
         <v>2</v>
@@ -6624,30 +6619,25 @@
         <v>4</v>
       </c>
       <c r="F151" s="55" t="n">
-        <v>4510004</v>
+        <v>4510002</v>
       </c>
       <c r="G151" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_4</t>
+          <t>Succubus_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K151" s="55" t="n">
-        <v>40200004</v>
+        <v>40200002</v>
       </c>
       <c r="L151" s="55" t="inlineStr">
         <is>
-          <t>魔女连体衣</t>
-        </is>
-      </c>
-      <c r="M151" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>红色胸罩</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="55" t="n">
-        <v>40200005</v>
+        <v>40200003</v>
       </c>
       <c r="B152" s="55" t="n">
         <v>2</v>
@@ -6659,19 +6649,19 @@
         <v>4</v>
       </c>
       <c r="F152" s="55" t="n">
-        <v>4510005</v>
+        <v>4510003</v>
       </c>
       <c r="G152" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_5</t>
+          <t>Succubus_Atlas_Clothes_Clothes_3</t>
         </is>
       </c>
       <c r="K152" s="55" t="n">
-        <v>40200005</v>
+        <v>40200003</v>
       </c>
       <c r="L152" s="55" t="inlineStr">
         <is>
-          <t>丝带</t>
+          <t>修女服</t>
         </is>
       </c>
       <c r="M152" s="55" t="inlineStr">
@@ -6682,7 +6672,7 @@
     </row>
     <row r="153">
       <c r="A153" s="55" t="n">
-        <v>40200006</v>
+        <v>40200004</v>
       </c>
       <c r="B153" s="55" t="n">
         <v>2</v>
@@ -6694,33 +6684,33 @@
         <v>4</v>
       </c>
       <c r="F153" s="55" t="n">
-        <v>4510006</v>
+        <v>4510004</v>
       </c>
       <c r="G153" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_6</t>
+          <t>Succubus_Atlas_Clothes_Clothes_4</t>
         </is>
       </c>
       <c r="K153" s="55" t="n">
-        <v>40200006</v>
+        <v>40200004</v>
       </c>
       <c r="L153" s="55" t="inlineStr">
         <is>
-          <t>白色丝带</t>
+          <t>魔女连体衣</t>
         </is>
       </c>
       <c r="M153" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="55" t="n">
-        <v>40300001</v>
+        <v>40200005</v>
       </c>
       <c r="B154" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D154" s="55" t="n">
         <v>1</v>
@@ -6729,28 +6719,33 @@
         <v>4</v>
       </c>
       <c r="F154" s="55" t="n">
-        <v>4520001</v>
+        <v>4510005</v>
       </c>
       <c r="G154" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Pants_Pants_1</t>
+          <t>Succubus_Atlas_Clothes_Clothes_5</t>
         </is>
       </c>
       <c r="K154" s="55" t="n">
-        <v>40300001</v>
+        <v>40200005</v>
       </c>
       <c r="L154" s="55" t="inlineStr">
         <is>
-          <t>粉色丝袜裤</t>
+          <t>丝带</t>
+        </is>
+      </c>
+      <c r="M154" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="55" t="n">
-        <v>40300002</v>
+        <v>40200006</v>
       </c>
       <c r="B155" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D155" s="55" t="n">
         <v>1</v>
@@ -6759,25 +6754,30 @@
         <v>4</v>
       </c>
       <c r="F155" s="55" t="n">
-        <v>4520002</v>
+        <v>4510006</v>
       </c>
       <c r="G155" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Pants_Pants_2</t>
+          <t>Succubus_Atlas_Clothes_Clothes_6</t>
         </is>
       </c>
       <c r="K155" s="55" t="n">
-        <v>40300002</v>
+        <v>40200006</v>
       </c>
       <c r="L155" s="55" t="inlineStr">
         <is>
-          <t>红色内裤</t>
+          <t>白色丝带</t>
+        </is>
+      </c>
+      <c r="M155" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="55" t="n">
-        <v>40300003</v>
+        <v>40300001</v>
       </c>
       <c r="B156" s="55" t="n">
         <v>3</v>
@@ -6789,30 +6789,25 @@
         <v>4</v>
       </c>
       <c r="F156" s="55" t="n">
-        <v>4520003</v>
+        <v>4520001</v>
       </c>
       <c r="G156" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Pants_Pants_3</t>
+          <t>Succubus_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K156" s="55" t="n">
-        <v>40300003</v>
+        <v>40300001</v>
       </c>
       <c r="L156" s="55" t="inlineStr">
         <is>
-          <t>修女裤</t>
-        </is>
-      </c>
-      <c r="M156" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>粉色丝袜裤</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="55" t="n">
-        <v>40300004</v>
+        <v>40300002</v>
       </c>
       <c r="B157" s="55" t="n">
         <v>3</v>
@@ -6824,36 +6819,28 @@
         <v>4</v>
       </c>
       <c r="F157" s="55" t="n">
-        <v>4520004</v>
+        <v>4520002</v>
       </c>
       <c r="G157" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Pants_Pants_4</t>
+          <t>Succubus_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K157" s="55" t="n">
-        <v>40300004</v>
+        <v>40300002</v>
       </c>
       <c r="L157" s="55" t="inlineStr">
         <is>
-          <t>魔女连体裤</t>
-        </is>
-      </c>
-      <c r="M157" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,6</t>
+          <t>红色内裤</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="55" t="n">
-        <v>41000001</v>
+        <v>40300003</v>
       </c>
       <c r="B158" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C158" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D158" s="55" t="n">
         <v>1</v>
@@ -6862,36 +6849,33 @@
         <v>4</v>
       </c>
       <c r="F158" s="55" t="n">
-        <v>4900001</v>
+        <v>4520003</v>
       </c>
       <c r="G158" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_1</t>
+          <t>Succubus_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K158" s="55" t="n">
-        <v>41000001</v>
+        <v>40300003</v>
       </c>
       <c r="L158" s="55" t="inlineStr">
         <is>
-          <t>魔力镰刀</t>
+          <t>修女裤</t>
         </is>
       </c>
       <c r="M158" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="55" t="n">
-        <v>41000002</v>
+        <v>40300004</v>
       </c>
       <c r="B159" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C159" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D159" s="55" t="n">
         <v>1</v>
@@ -6900,25 +6884,30 @@
         <v>4</v>
       </c>
       <c r="F159" s="55" t="n">
-        <v>4900002</v>
+        <v>4520004</v>
       </c>
       <c r="G159" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_2</t>
+          <t>Succubus_Atlas_Pants_Pants_4</t>
         </is>
       </c>
       <c r="K159" s="55" t="n">
-        <v>41000002</v>
+        <v>40300004</v>
       </c>
       <c r="L159" s="55" t="inlineStr">
         <is>
-          <t>木制镰刀</t>
+          <t>魔女连体裤</t>
+        </is>
+      </c>
+      <c r="M159" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,6</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="55" t="n">
-        <v>41000003</v>
+        <v>41000001</v>
       </c>
       <c r="B160" s="55" t="n">
         <v>10</v>
@@ -6933,30 +6922,30 @@
         <v>4</v>
       </c>
       <c r="F160" s="55" t="n">
-        <v>4900003</v>
+        <v>4900001</v>
       </c>
       <c r="G160" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_3</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_1</t>
         </is>
       </c>
       <c r="K160" s="55" t="n">
-        <v>41000003</v>
+        <v>41000001</v>
       </c>
       <c r="L160" s="55" t="inlineStr">
         <is>
-          <t>鹦鹉镰刀</t>
+          <t>魔力镰刀</t>
         </is>
       </c>
       <c r="M160" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="55" t="n">
-        <v>41000004</v>
+        <v>41000002</v>
       </c>
       <c r="B161" s="55" t="n">
         <v>10</v>
@@ -6971,30 +6960,25 @@
         <v>4</v>
       </c>
       <c r="F161" s="55" t="n">
-        <v>4900004</v>
+        <v>4900002</v>
       </c>
       <c r="G161" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_4</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_2</t>
         </is>
       </c>
       <c r="K161" s="55" t="n">
-        <v>41000004</v>
+        <v>41000002</v>
       </c>
       <c r="L161" s="55" t="inlineStr">
         <is>
-          <t>金制镰刀</t>
-        </is>
-      </c>
-      <c r="M161" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>木制镰刀</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="55" t="n">
-        <v>41000005</v>
+        <v>41000003</v>
       </c>
       <c r="B162" s="55" t="n">
         <v>10</v>
@@ -7009,19 +6993,19 @@
         <v>4</v>
       </c>
       <c r="F162" s="55" t="n">
-        <v>4900005</v>
+        <v>4900003</v>
       </c>
       <c r="G162" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_5</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_3</t>
         </is>
       </c>
       <c r="K162" s="55" t="n">
-        <v>41000005</v>
+        <v>41000003</v>
       </c>
       <c r="L162" s="55" t="inlineStr">
         <is>
-          <t>剧毒镰刀</t>
+          <t>鹦鹉镰刀</t>
         </is>
       </c>
       <c r="M162" s="55" t="inlineStr">
@@ -7032,31 +7016,34 @@
     </row>
     <row r="163">
       <c r="A163" s="55" t="n">
-        <v>50100001</v>
+        <v>41000004</v>
       </c>
       <c r="B163" s="55" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C163" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="D163" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E163" s="55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F163" s="55" t="n">
-        <v>5500001</v>
+        <v>4900004</v>
       </c>
       <c r="G163" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Hat_Hat_1</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_4</t>
         </is>
       </c>
       <c r="K163" s="55" t="n">
-        <v>50100001</v>
+        <v>41000004</v>
       </c>
       <c r="L163" s="55" t="inlineStr">
         <is>
-          <t>红色头巾</t>
+          <t>金制镰刀</t>
         </is>
       </c>
       <c r="M163" s="55" t="inlineStr">
@@ -7067,31 +7054,34 @@
     </row>
     <row r="164">
       <c r="A164" s="55" t="n">
-        <v>50100002</v>
+        <v>41000005</v>
       </c>
       <c r="B164" s="55" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C164" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="D164" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E164" s="55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F164" s="55" t="n">
-        <v>5500002</v>
+        <v>4900005</v>
       </c>
       <c r="G164" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Hat_Hat_2</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_5</t>
         </is>
       </c>
       <c r="K164" s="55" t="n">
-        <v>50100002</v>
+        <v>41000005</v>
       </c>
       <c r="L164" s="55" t="inlineStr">
         <is>
-          <t>小花</t>
+          <t>剧毒镰刀</t>
         </is>
       </c>
       <c r="M164" s="55" t="inlineStr">
@@ -7102,7 +7092,7 @@
     </row>
     <row r="165">
       <c r="A165" s="55" t="n">
-        <v>50100003</v>
+        <v>50100001</v>
       </c>
       <c r="B165" s="55" t="n">
         <v>1</v>
@@ -7114,19 +7104,19 @@
         <v>5</v>
       </c>
       <c r="F165" s="55" t="n">
-        <v>5500003</v>
+        <v>5500001</v>
       </c>
       <c r="G165" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Hat_Hat_3</t>
+          <t>Minotaur_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K165" s="55" t="n">
-        <v>50100003</v>
+        <v>50100001</v>
       </c>
       <c r="L165" s="55" t="inlineStr">
         <is>
-          <t>蘑菇</t>
+          <t>红色头巾</t>
         </is>
       </c>
       <c r="M165" s="55" t="inlineStr">
@@ -7137,10 +7127,10 @@
     </row>
     <row r="166">
       <c r="A166" s="55" t="n">
-        <v>50200001</v>
+        <v>50100002</v>
       </c>
       <c r="B166" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D166" s="55" t="n">
         <v>1</v>
@@ -7149,19 +7139,19 @@
         <v>5</v>
       </c>
       <c r="F166" s="55" t="n">
-        <v>5510001</v>
+        <v>5500002</v>
       </c>
       <c r="G166" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Clothes_Clothes_1</t>
+          <t>Minotaur_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K166" s="55" t="n">
-        <v>50200001</v>
+        <v>50100002</v>
       </c>
       <c r="L166" s="55" t="inlineStr">
         <is>
-          <t>银制盔甲</t>
+          <t>小花</t>
         </is>
       </c>
       <c r="M166" s="55" t="inlineStr">
@@ -7172,10 +7162,10 @@
     </row>
     <row r="167" ht="12" customHeight="1" s="56">
       <c r="A167" s="55" t="n">
-        <v>50200002</v>
+        <v>50100003</v>
       </c>
       <c r="B167" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D167" s="55" t="n">
         <v>1</v>
@@ -7184,30 +7174,30 @@
         <v>5</v>
       </c>
       <c r="F167" s="55" t="n">
-        <v>5510002</v>
+        <v>5500003</v>
       </c>
       <c r="G167" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Clothes_Clothes_2</t>
+          <t>Minotaur_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K167" s="55" t="n">
-        <v>50200002</v>
+        <v>50100003</v>
       </c>
       <c r="L167" s="55" t="inlineStr">
         <is>
-          <t>皮甲</t>
+          <t>蘑菇</t>
         </is>
       </c>
       <c r="M167" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="55" t="n">
-        <v>50200003</v>
+        <v>50200001</v>
       </c>
       <c r="B168" s="55" t="n">
         <v>2</v>
@@ -7219,33 +7209,33 @@
         <v>5</v>
       </c>
       <c r="F168" s="55" t="n">
-        <v>5510003</v>
+        <v>5510001</v>
       </c>
       <c r="G168" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Clothes_Clothes_3</t>
+          <t>Minotaur_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K168" s="55" t="n">
-        <v>50200003</v>
+        <v>50200001</v>
       </c>
       <c r="L168" s="55" t="inlineStr">
         <is>
-          <t>皮带胸甲</t>
+          <t>银制盔甲</t>
         </is>
       </c>
       <c r="M168" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="55" t="n">
-        <v>50300001</v>
+        <v>50200002</v>
       </c>
       <c r="B169" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D169" s="55" t="n">
         <v>1</v>
@@ -7254,33 +7244,33 @@
         <v>5</v>
       </c>
       <c r="F169" s="55" t="n">
-        <v>5520001</v>
+        <v>5510002</v>
       </c>
       <c r="G169" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Pants_Pants_1</t>
+          <t>Minotaur_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K169" s="55" t="n">
-        <v>50300001</v>
+        <v>50200002</v>
       </c>
       <c r="L169" s="55" t="inlineStr">
         <is>
-          <t>骷髅腰带</t>
+          <t>皮甲</t>
         </is>
       </c>
       <c r="M169" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="55" t="n">
-        <v>50300002</v>
+        <v>50200003</v>
       </c>
       <c r="B170" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D170" s="55" t="n">
         <v>1</v>
@@ -7289,33 +7279,33 @@
         <v>5</v>
       </c>
       <c r="F170" s="55" t="n">
-        <v>5520002</v>
+        <v>5510003</v>
       </c>
       <c r="G170" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Pants_Pants_2</t>
+          <t>Minotaur_Atlas_Clothes_Clothes_3</t>
         </is>
       </c>
       <c r="K170" s="55" t="n">
-        <v>50300002</v>
+        <v>50200003</v>
       </c>
       <c r="L170" s="55" t="inlineStr">
         <is>
-          <t>红色铁制</t>
+          <t>皮带胸甲</t>
         </is>
       </c>
       <c r="M170" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="55" t="n">
-        <v>50500001</v>
+        <v>50300001</v>
       </c>
       <c r="B171" s="55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D171" s="55" t="n">
         <v>1</v>
@@ -7324,33 +7314,33 @@
         <v>5</v>
       </c>
       <c r="F171" s="55" t="n">
-        <v>5090001</v>
+        <v>5520001</v>
       </c>
       <c r="G171" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_1</t>
+          <t>Minotaur_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K171" s="55" t="n">
-        <v>50500001</v>
+        <v>50300001</v>
       </c>
       <c r="L171" s="55" t="inlineStr">
         <is>
-          <t>铁制鼻环</t>
+          <t>骷髅腰带</t>
         </is>
       </c>
       <c r="M171" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="55" t="n">
-        <v>50500002</v>
+        <v>50300002</v>
       </c>
       <c r="B172" s="55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D172" s="55" t="n">
         <v>1</v>
@@ -7359,30 +7349,30 @@
         <v>5</v>
       </c>
       <c r="F172" s="55" t="n">
-        <v>5090002</v>
+        <v>5520002</v>
       </c>
       <c r="G172" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_2</t>
+          <t>Minotaur_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K172" s="55" t="n">
-        <v>50500002</v>
+        <v>50300002</v>
       </c>
       <c r="L172" s="55" t="inlineStr">
         <is>
-          <t>反向铁制鼻环</t>
+          <t>红色铁制</t>
         </is>
       </c>
       <c r="M172" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="55" t="n">
-        <v>50500003</v>
+        <v>50500001</v>
       </c>
       <c r="B173" s="55" t="n">
         <v>5</v>
@@ -7394,25 +7384,30 @@
         <v>5</v>
       </c>
       <c r="F173" s="55" t="n">
-        <v>5090003</v>
+        <v>5090001</v>
       </c>
       <c r="G173" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_3</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_1</t>
         </is>
       </c>
       <c r="K173" s="55" t="n">
-        <v>50500003</v>
+        <v>50500001</v>
       </c>
       <c r="L173" s="55" t="inlineStr">
         <is>
-          <t>小号铁制鼻环</t>
+          <t>铁制鼻环</t>
+        </is>
+      </c>
+      <c r="M173" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="55" t="n">
-        <v>50500004</v>
+        <v>50500002</v>
       </c>
       <c r="B174" s="55" t="n">
         <v>5</v>
@@ -7424,30 +7419,30 @@
         <v>5</v>
       </c>
       <c r="F174" s="55" t="n">
-        <v>5090004</v>
+        <v>5090002</v>
       </c>
       <c r="G174" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_4</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_2</t>
         </is>
       </c>
       <c r="K174" s="55" t="n">
-        <v>50500004</v>
+        <v>50500002</v>
       </c>
       <c r="L174" s="55" t="inlineStr">
         <is>
-          <t>金制鼻环</t>
+          <t>反向铁制鼻环</t>
         </is>
       </c>
       <c r="M174" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="55" t="n">
-        <v>50500005</v>
+        <v>50500003</v>
       </c>
       <c r="B175" s="55" t="n">
         <v>5</v>
@@ -7459,36 +7454,28 @@
         <v>5</v>
       </c>
       <c r="F175" s="55" t="n">
-        <v>5090005</v>
+        <v>5090003</v>
       </c>
       <c r="G175" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_5</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_3</t>
         </is>
       </c>
       <c r="K175" s="55" t="n">
-        <v>50500005</v>
+        <v>50500003</v>
       </c>
       <c r="L175" s="55" t="inlineStr">
         <is>
-          <t>连环鼻环</t>
-        </is>
-      </c>
-      <c r="M175" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>小号铁制鼻环</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="55" t="n">
-        <v>51010001</v>
+        <v>50500004</v>
       </c>
       <c r="B176" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C176" s="55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D176" s="55" t="n">
         <v>1</v>
@@ -7497,41 +7484,33 @@
         <v>5</v>
       </c>
       <c r="F176" s="55" t="n">
-        <v>5910001</v>
+        <v>5090004</v>
       </c>
       <c r="G176" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Weapon_Weapon_R_1</t>
-        </is>
-      </c>
-      <c r="I176" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_4</t>
         </is>
       </c>
       <c r="K176" s="55" t="n">
-        <v>51010001</v>
+        <v>50500004</v>
       </c>
       <c r="L176" s="55" t="inlineStr">
         <is>
-          <t>石头</t>
+          <t>金制鼻环</t>
         </is>
       </c>
       <c r="M176" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="55" t="n">
-        <v>51010002</v>
+        <v>50500005</v>
       </c>
       <c r="B177" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C177" s="55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D177" s="55" t="n">
         <v>1</v>
@@ -7540,35 +7519,30 @@
         <v>5</v>
       </c>
       <c r="F177" s="55" t="n">
-        <v>5910002</v>
+        <v>5090005</v>
       </c>
       <c r="G177" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Weapon_Weapon_R_2</t>
-        </is>
-      </c>
-      <c r="I177" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_5</t>
         </is>
       </c>
       <c r="K177" s="55" t="n">
-        <v>51010002</v>
+        <v>50500005</v>
       </c>
       <c r="L177" s="55" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>连环鼻环</t>
         </is>
       </c>
       <c r="M177" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="55" t="n">
-        <v>51010003</v>
+        <v>51010001</v>
       </c>
       <c r="B178" s="55" t="n">
         <v>10</v>
@@ -7583,100 +7557,121 @@
         <v>5</v>
       </c>
       <c r="F178" s="55" t="n">
-        <v>5910003</v>
+        <v>5910001</v>
       </c>
       <c r="G178" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Weapon_Weapon_R_3</t>
+          <t>Minotaur_Atlas_Weapon_Weapon_R_1</t>
         </is>
       </c>
       <c r="I178" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
         </is>
       </c>
       <c r="K178" s="55" t="n">
-        <v>51010003</v>
+        <v>51010001</v>
       </c>
       <c r="L178" s="55" t="inlineStr">
         <is>
-          <t>宝箱</t>
+          <t>石头</t>
         </is>
       </c>
       <c r="M178" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="55" t="n">
-        <v>60100001</v>
+        <v>51010002</v>
       </c>
       <c r="B179" s="55" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C179" s="55" t="n">
+        <v>8</v>
       </c>
       <c r="D179" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E179" s="55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F179" s="55" t="n">
-        <v>6500001</v>
+        <v>5910002</v>
       </c>
       <c r="G179" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_1</t>
+          <t>Minotaur_Atlas_Weapon_Weapon_R_2</t>
+        </is>
+      </c>
+      <c r="I179" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
         </is>
       </c>
       <c r="K179" s="55" t="n">
-        <v>60100001</v>
+        <v>51010002</v>
       </c>
       <c r="L179" s="55" t="inlineStr">
         <is>
-          <t>木制面具</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="M179" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="55" t="n">
-        <v>60100002</v>
+        <v>51010003</v>
       </c>
       <c r="B180" s="55" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C180" s="55" t="n">
+        <v>8</v>
       </c>
       <c r="D180" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E180" s="55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F180" s="55" t="n">
-        <v>6500002</v>
+        <v>5910003</v>
       </c>
       <c r="G180" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_2</t>
+          <t>Minotaur_Atlas_Weapon_Weapon_R_3</t>
+        </is>
+      </c>
+      <c r="I180" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
         </is>
       </c>
       <c r="K180" s="55" t="n">
-        <v>60100002</v>
+        <v>51010003</v>
       </c>
       <c r="L180" s="55" t="inlineStr">
         <is>
-          <t>头巾</t>
+          <t>宝箱</t>
+        </is>
+      </c>
+      <c r="M180" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="55" t="n">
-        <v>60100003</v>
+        <v>60100001</v>
       </c>
       <c r="B181" s="55" t="n">
         <v>1</v>
@@ -7688,19 +7683,19 @@
         <v>6</v>
       </c>
       <c r="F181" s="55" t="n">
-        <v>6500003</v>
+        <v>6500001</v>
       </c>
       <c r="G181" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_3</t>
+          <t>Goblin_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K181" s="55" t="n">
-        <v>60100003</v>
+        <v>60100001</v>
       </c>
       <c r="L181" s="55" t="inlineStr">
         <is>
-          <t>金耳环</t>
+          <t>木制面具</t>
         </is>
       </c>
       <c r="M181" s="55" t="inlineStr">
@@ -7711,7 +7706,7 @@
     </row>
     <row r="182" ht="12" customHeight="1" s="56">
       <c r="A182" s="55" t="n">
-        <v>60100004</v>
+        <v>60100002</v>
       </c>
       <c r="B182" s="55" t="n">
         <v>1</v>
@@ -7723,30 +7718,25 @@
         <v>6</v>
       </c>
       <c r="F182" s="55" t="n">
-        <v>6500004</v>
+        <v>6500002</v>
       </c>
       <c r="G182" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_4</t>
+          <t>Goblin_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K182" s="55" t="n">
-        <v>60100004</v>
+        <v>60100002</v>
       </c>
       <c r="L182" s="55" t="inlineStr">
         <is>
-          <t>红色头巾</t>
-        </is>
-      </c>
-      <c r="M182" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>头巾</t>
         </is>
       </c>
     </row>
     <row r="183" ht="12" customHeight="1" s="56">
       <c r="A183" s="55" t="n">
-        <v>60100005</v>
+        <v>60100003</v>
       </c>
       <c r="B183" s="55" t="n">
         <v>1</v>
@@ -7758,30 +7748,30 @@
         <v>6</v>
       </c>
       <c r="F183" s="55" t="n">
-        <v>6500005</v>
+        <v>6500003</v>
       </c>
       <c r="G183" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_5</t>
+          <t>Goblin_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K183" s="55" t="n">
-        <v>60100005</v>
+        <v>60100003</v>
       </c>
       <c r="L183" s="55" t="inlineStr">
         <is>
-          <t>蓝色头巾</t>
+          <t>金耳环</t>
         </is>
       </c>
       <c r="M183" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="184" ht="12" customHeight="1" s="56">
       <c r="A184" s="55" t="n">
-        <v>60100006</v>
+        <v>60100004</v>
       </c>
       <c r="B184" s="55" t="n">
         <v>1</v>
@@ -7793,25 +7783,30 @@
         <v>6</v>
       </c>
       <c r="F184" s="55" t="n">
-        <v>6500006</v>
+        <v>6500004</v>
       </c>
       <c r="G184" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_6</t>
+          <t>Goblin_Atlas_Hat_Hat_4</t>
         </is>
       </c>
       <c r="K184" s="55" t="n">
-        <v>60100006</v>
+        <v>60100004</v>
       </c>
       <c r="L184" s="55" t="inlineStr">
         <is>
-          <t>布头罩</t>
+          <t>红色头巾</t>
+        </is>
+      </c>
+      <c r="M184" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="185" ht="12" customHeight="1" s="56">
       <c r="A185" s="55" t="n">
-        <v>60100007</v>
+        <v>60100005</v>
       </c>
       <c r="B185" s="55" t="n">
         <v>1</v>
@@ -7823,30 +7818,30 @@
         <v>6</v>
       </c>
       <c r="F185" s="55" t="n">
-        <v>6500007</v>
+        <v>6500005</v>
       </c>
       <c r="G185" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_7</t>
+          <t>Goblin_Atlas_Hat_Hat_5</t>
         </is>
       </c>
       <c r="K185" s="55" t="n">
-        <v>60100007</v>
+        <v>60100005</v>
       </c>
       <c r="L185" s="55" t="inlineStr">
         <is>
-          <t>红色羽毛帽</t>
+          <t>蓝色头巾</t>
         </is>
       </c>
       <c r="M185" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="186" ht="12" customHeight="1" s="56">
       <c r="A186" s="55" t="n">
-        <v>60100008</v>
+        <v>60100006</v>
       </c>
       <c r="B186" s="55" t="n">
         <v>1</v>
@@ -7858,30 +7853,25 @@
         <v>6</v>
       </c>
       <c r="F186" s="55" t="n">
-        <v>6500008</v>
+        <v>6500006</v>
       </c>
       <c r="G186" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_8</t>
+          <t>Goblin_Atlas_Hat_Hat_6</t>
         </is>
       </c>
       <c r="K186" s="55" t="n">
-        <v>60100008</v>
+        <v>60100006</v>
       </c>
       <c r="L186" s="55" t="inlineStr">
         <is>
-          <t>熊头帽</t>
-        </is>
-      </c>
-      <c r="M186" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>布头罩</t>
         </is>
       </c>
     </row>
     <row r="187" ht="12" customHeight="1" s="56">
       <c r="A187" s="55" t="n">
-        <v>60100009</v>
+        <v>60100007</v>
       </c>
       <c r="B187" s="55" t="n">
         <v>1</v>
@@ -7893,30 +7883,30 @@
         <v>6</v>
       </c>
       <c r="F187" s="55" t="n">
-        <v>6500009</v>
+        <v>6500007</v>
       </c>
       <c r="G187" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_9</t>
+          <t>Goblin_Atlas_Hat_Hat_7</t>
         </is>
       </c>
       <c r="K187" s="55" t="n">
-        <v>60100009</v>
+        <v>60100007</v>
       </c>
       <c r="L187" s="55" t="inlineStr">
         <is>
-          <t>独眼罩</t>
+          <t>红色羽毛帽</t>
         </is>
       </c>
       <c r="M187" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="188" ht="12" customHeight="1" s="56">
       <c r="A188" s="55" t="n">
-        <v>60100010</v>
+        <v>60100008</v>
       </c>
       <c r="B188" s="55" t="n">
         <v>1</v>
@@ -7928,28 +7918,33 @@
         <v>6</v>
       </c>
       <c r="F188" s="55" t="n">
-        <v>6500010</v>
+        <v>6500008</v>
       </c>
       <c r="G188" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_10</t>
+          <t>Goblin_Atlas_Hat_Hat_8</t>
         </is>
       </c>
       <c r="K188" s="55" t="n">
-        <v>60100010</v>
+        <v>60100008</v>
       </c>
       <c r="L188" s="55" t="inlineStr">
         <is>
-          <t>皮头罩</t>
+          <t>熊头帽</t>
+        </is>
+      </c>
+      <c r="M188" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="55" t="n">
-        <v>60200001</v>
+        <v>60100009</v>
       </c>
       <c r="B189" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D189" s="55" t="n">
         <v>1</v>
@@ -7958,28 +7953,33 @@
         <v>6</v>
       </c>
       <c r="F189" s="55" t="n">
-        <v>6510001</v>
+        <v>6500009</v>
       </c>
       <c r="G189" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Clothes_Clothes_1</t>
+          <t>Goblin_Atlas_Hat_Hat_9</t>
         </is>
       </c>
       <c r="K189" s="55" t="n">
-        <v>60200001</v>
+        <v>60100009</v>
       </c>
       <c r="L189" s="55" t="inlineStr">
         <is>
-          <t>粉色胸罩</t>
+          <t>独眼罩</t>
+        </is>
+      </c>
+      <c r="M189" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="55" t="n">
-        <v>60200002</v>
+        <v>60100010</v>
       </c>
       <c r="B190" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D190" s="55" t="n">
         <v>1</v>
@@ -7988,28 +7988,28 @@
         <v>6</v>
       </c>
       <c r="F190" s="55" t="n">
-        <v>6510002</v>
+        <v>6500010</v>
       </c>
       <c r="G190" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Clothes_Clothes_2</t>
+          <t>Goblin_Atlas_Hat_Hat_10</t>
         </is>
       </c>
       <c r="K190" s="55" t="n">
-        <v>60200002</v>
+        <v>60100010</v>
       </c>
       <c r="L190" s="55" t="inlineStr">
         <is>
-          <t>布衣</t>
+          <t>皮头罩</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="55" t="n">
-        <v>60300001</v>
+        <v>60200001</v>
       </c>
       <c r="B191" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D191" s="55" t="n">
         <v>1</v>
@@ -8018,28 +8018,28 @@
         <v>6</v>
       </c>
       <c r="F191" s="55" t="n">
-        <v>6520001</v>
+        <v>6510001</v>
       </c>
       <c r="G191" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_1</t>
+          <t>Goblin_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K191" s="55" t="n">
-        <v>60300001</v>
+        <v>60200001</v>
       </c>
       <c r="L191" s="55" t="inlineStr">
         <is>
-          <t>皮裤</t>
+          <t>粉色胸罩</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="55" t="n">
-        <v>60300002</v>
+        <v>60200002</v>
       </c>
       <c r="B192" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D192" s="55" t="n">
         <v>1</v>
@@ -8048,30 +8048,25 @@
         <v>6</v>
       </c>
       <c r="F192" s="55" t="n">
-        <v>6520002</v>
+        <v>6510002</v>
       </c>
       <c r="G192" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_2</t>
+          <t>Goblin_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K192" s="55" t="n">
-        <v>60300002</v>
+        <v>60200002</v>
       </c>
       <c r="L192" s="55" t="inlineStr">
         <is>
-          <t>腰盔甲</t>
-        </is>
-      </c>
-      <c r="M192" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>布衣</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="55" t="n">
-        <v>60300003</v>
+        <v>60300001</v>
       </c>
       <c r="B193" s="55" t="n">
         <v>3</v>
@@ -8083,25 +8078,25 @@
         <v>6</v>
       </c>
       <c r="F193" s="55" t="n">
-        <v>6520003</v>
+        <v>6520001</v>
       </c>
       <c r="G193" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_3</t>
+          <t>Goblin_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K193" s="55" t="n">
-        <v>60300003</v>
+        <v>60300001</v>
       </c>
       <c r="L193" s="55" t="inlineStr">
         <is>
-          <t>布裤子</t>
+          <t>皮裤</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="55" t="n">
-        <v>60300004</v>
+        <v>60300002</v>
       </c>
       <c r="B194" s="55" t="n">
         <v>3</v>
@@ -8113,19 +8108,19 @@
         <v>6</v>
       </c>
       <c r="F194" s="55" t="n">
-        <v>6520004</v>
+        <v>6520002</v>
       </c>
       <c r="G194" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_4</t>
+          <t>Goblin_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K194" s="55" t="n">
-        <v>60300004</v>
+        <v>60300002</v>
       </c>
       <c r="L194" s="55" t="inlineStr">
         <is>
-          <t>熊裤子</t>
+          <t>腰盔甲</t>
         </is>
       </c>
       <c r="M194" s="55" t="inlineStr">
@@ -8136,7 +8131,7 @@
     </row>
     <row r="195">
       <c r="A195" s="55" t="n">
-        <v>60300005</v>
+        <v>60300003</v>
       </c>
       <c r="B195" s="55" t="n">
         <v>3</v>
@@ -8148,36 +8143,28 @@
         <v>6</v>
       </c>
       <c r="F195" s="55" t="n">
-        <v>6520005</v>
+        <v>6520003</v>
       </c>
       <c r="G195" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_5</t>
+          <t>Goblin_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K195" s="55" t="n">
-        <v>60300005</v>
+        <v>60300003</v>
       </c>
       <c r="L195" s="55" t="inlineStr">
         <is>
-          <t>蓝裤子</t>
-        </is>
-      </c>
-      <c r="M195" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>布裤子</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="55" t="n">
-        <v>61010001</v>
+        <v>60300004</v>
       </c>
       <c r="B196" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C196" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D196" s="55" t="n">
         <v>1</v>
@@ -8186,19 +8173,19 @@
         <v>6</v>
       </c>
       <c r="F196" s="55" t="n">
-        <v>6910001</v>
+        <v>6520004</v>
       </c>
       <c r="G196" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_1</t>
+          <t>Goblin_Atlas_Pants_Pants_4</t>
         </is>
       </c>
       <c r="K196" s="55" t="n">
-        <v>61010001</v>
+        <v>60300004</v>
       </c>
       <c r="L196" s="55" t="inlineStr">
         <is>
-          <t>金刀</t>
+          <t>熊裤子</t>
         </is>
       </c>
       <c r="M196" s="55" t="inlineStr">
@@ -8209,13 +8196,10 @@
     </row>
     <row r="197">
       <c r="A197" s="55" t="n">
-        <v>61010002</v>
+        <v>60300005</v>
       </c>
       <c r="B197" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C197" s="55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D197" s="55" t="n">
         <v>1</v>
@@ -8224,36 +8208,36 @@
         <v>6</v>
       </c>
       <c r="F197" s="55" t="n">
-        <v>6910002</v>
+        <v>6520005</v>
       </c>
       <c r="G197" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_2</t>
-        </is>
-      </c>
-      <c r="I197" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>Goblin_Atlas_Pants_Pants_5</t>
         </is>
       </c>
       <c r="K197" s="55" t="n">
-        <v>61010002</v>
+        <v>60300005</v>
       </c>
       <c r="L197" s="55" t="inlineStr">
         <is>
-          <t>木弓</t>
+          <t>蓝裤子</t>
+        </is>
+      </c>
+      <c r="M197" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="55" t="n">
-        <v>61010003</v>
+        <v>61010001</v>
       </c>
       <c r="B198" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C198" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D198" s="55" t="n">
         <v>1</v>
@@ -8262,36 +8246,36 @@
         <v>6</v>
       </c>
       <c r="F198" s="55" t="n">
-        <v>6910003</v>
+        <v>6910001</v>
       </c>
       <c r="G198" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_3</t>
-        </is>
-      </c>
-      <c r="I198" s="55" t="inlineStr">
-        <is>
-          <t>StartSize:0.65</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_1</t>
         </is>
       </c>
       <c r="K198" s="55" t="n">
-        <v>61010003</v>
+        <v>61010001</v>
       </c>
       <c r="L198" s="55" t="inlineStr">
         <is>
-          <t>木法杖</t>
+          <t>金刀</t>
+        </is>
+      </c>
+      <c r="M198" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="55" t="n">
-        <v>61010004</v>
+        <v>61010002</v>
       </c>
       <c r="B199" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C199" s="55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D199" s="55" t="n">
         <v>1</v>
@@ -8300,33 +8284,30 @@
         <v>6</v>
       </c>
       <c r="F199" s="55" t="n">
-        <v>6910004</v>
+        <v>6910002</v>
       </c>
       <c r="G199" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_4</t>
-        </is>
-      </c>
-      <c r="H199" s="55" t="n">
-        <v>-45</v>
+          <t>Goblin_Atlas_Weapon_Weapon_R_2</t>
+        </is>
+      </c>
+      <c r="I199" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+        </is>
       </c>
       <c r="K199" s="55" t="n">
-        <v>61010004</v>
+        <v>61010002</v>
       </c>
       <c r="L199" s="55" t="inlineStr">
         <is>
-          <t>骷髅法杖</t>
-        </is>
-      </c>
-      <c r="M199" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>木弓</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="55" t="n">
-        <v>61010005</v>
+        <v>61010003</v>
       </c>
       <c r="B200" s="55" t="n">
         <v>10</v>
@@ -8341,33 +8322,30 @@
         <v>6</v>
       </c>
       <c r="F200" s="55" t="n">
-        <v>6910005</v>
+        <v>6910003</v>
       </c>
       <c r="G200" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_5</t>
-        </is>
-      </c>
-      <c r="H200" s="55" t="n">
-        <v>-45</v>
+          <t>Goblin_Atlas_Weapon_Weapon_R_3</t>
+        </is>
+      </c>
+      <c r="I200" s="55" t="inlineStr">
+        <is>
+          <t>StartSize:0.65</t>
+        </is>
       </c>
       <c r="K200" s="55" t="n">
-        <v>61010005</v>
+        <v>61010003</v>
       </c>
       <c r="L200" s="55" t="inlineStr">
         <is>
-          <t>十字法杖</t>
-        </is>
-      </c>
-      <c r="M200" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>木法杖</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="55" t="n">
-        <v>61010006</v>
+        <v>61010004</v>
       </c>
       <c r="B201" s="55" t="n">
         <v>10</v>
@@ -8382,33 +8360,33 @@
         <v>6</v>
       </c>
       <c r="F201" s="55" t="n">
-        <v>6910006</v>
+        <v>6910004</v>
       </c>
       <c r="G201" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_6</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_4</t>
         </is>
       </c>
       <c r="H201" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K201" s="55" t="n">
-        <v>61010006</v>
+        <v>61010004</v>
       </c>
       <c r="L201" s="55" t="inlineStr">
         <is>
-          <t>蔚蓝法棍</t>
+          <t>骷髅法杖</t>
         </is>
       </c>
       <c r="M201" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="55" t="n">
-        <v>61010007</v>
+        <v>61010005</v>
       </c>
       <c r="B202" s="55" t="n">
         <v>10</v>
@@ -8423,19 +8401,22 @@
         <v>6</v>
       </c>
       <c r="F202" s="55" t="n">
-        <v>6910007</v>
+        <v>6910005</v>
       </c>
       <c r="G202" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_7</t>
-        </is>
+          <t>Goblin_Atlas_Weapon_Weapon_R_5</t>
+        </is>
+      </c>
+      <c r="H202" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K202" s="55" t="n">
-        <v>61010007</v>
+        <v>61010005</v>
       </c>
       <c r="L202" s="55" t="inlineStr">
         <is>
-          <t>死亡之书</t>
+          <t>十字法杖</t>
         </is>
       </c>
       <c r="M202" s="55" t="inlineStr">
@@ -8446,13 +8427,13 @@
     </row>
     <row r="203">
       <c r="A203" s="55" t="n">
-        <v>61010008</v>
+        <v>61010006</v>
       </c>
       <c r="B203" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C203" s="55" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D203" s="55" t="n">
         <v>1</v>
@@ -8461,19 +8442,22 @@
         <v>6</v>
       </c>
       <c r="F203" s="55" t="n">
-        <v>6910008</v>
+        <v>6910006</v>
       </c>
       <c r="G203" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_8</t>
-        </is>
+          <t>Goblin_Atlas_Weapon_Weapon_R_6</t>
+        </is>
+      </c>
+      <c r="H203" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K203" s="55" t="n">
-        <v>61010008</v>
+        <v>61010006</v>
       </c>
       <c r="L203" s="55" t="inlineStr">
         <is>
-          <t>猩红之酒</t>
+          <t>蔚蓝法棍</t>
         </is>
       </c>
       <c r="M203" s="55" t="inlineStr">
@@ -8484,13 +8468,13 @@
     </row>
     <row r="204">
       <c r="A204" s="55" t="n">
-        <v>61010009</v>
+        <v>61010007</v>
       </c>
       <c r="B204" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C204" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D204" s="55" t="n">
         <v>1</v>
@@ -8499,36 +8483,36 @@
         <v>6</v>
       </c>
       <c r="F204" s="55" t="n">
-        <v>6910009</v>
+        <v>6910007</v>
       </c>
       <c r="G204" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_9</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_7</t>
         </is>
       </c>
       <c r="K204" s="55" t="n">
-        <v>61010009</v>
+        <v>61010007</v>
       </c>
       <c r="L204" s="55" t="inlineStr">
         <is>
-          <t>铁剑</t>
+          <t>死亡之书</t>
         </is>
       </c>
       <c r="M204" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="55" t="n">
-        <v>61010010</v>
+        <v>61010008</v>
       </c>
       <c r="B205" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C205" s="55" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D205" s="55" t="n">
         <v>1</v>
@@ -8537,30 +8521,30 @@
         <v>6</v>
       </c>
       <c r="F205" s="55" t="n">
-        <v>6910010</v>
+        <v>6910008</v>
       </c>
       <c r="G205" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_10</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_8</t>
         </is>
       </c>
       <c r="K205" s="55" t="n">
-        <v>61010010</v>
+        <v>61010008</v>
       </c>
       <c r="L205" s="55" t="inlineStr">
         <is>
-          <t>三叉戟</t>
+          <t>猩红之酒</t>
         </is>
       </c>
       <c r="M205" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="55" t="n">
-        <v>61010011</v>
+        <v>61010009</v>
       </c>
       <c r="B206" s="55" t="n">
         <v>10</v>
@@ -8575,30 +8559,30 @@
         <v>6</v>
       </c>
       <c r="F206" s="55" t="n">
-        <v>6910011</v>
+        <v>6910009</v>
       </c>
       <c r="G206" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_11</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_9</t>
         </is>
       </c>
       <c r="K206" s="55" t="n">
-        <v>61010011</v>
+        <v>61010009</v>
       </c>
       <c r="L206" s="55" t="inlineStr">
         <is>
-          <t>华丽刺剑</t>
+          <t>铁剑</t>
         </is>
       </c>
       <c r="M206" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="55" t="n">
-        <v>61010012</v>
+        <v>61010010</v>
       </c>
       <c r="B207" s="55" t="n">
         <v>10</v>
@@ -8613,36 +8597,36 @@
         <v>6</v>
       </c>
       <c r="F207" s="55" t="n">
-        <v>6910012</v>
+        <v>6910010</v>
       </c>
       <c r="G207" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_12</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_10</t>
         </is>
       </c>
       <c r="K207" s="55" t="n">
-        <v>61010012</v>
+        <v>61010010</v>
       </c>
       <c r="L207" s="55" t="inlineStr">
         <is>
-          <t>拐杖剑</t>
+          <t>三叉戟</t>
         </is>
       </c>
       <c r="M207" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="55" t="n">
-        <v>61010013</v>
+        <v>61010011</v>
       </c>
       <c r="B208" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C208" s="55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D208" s="55" t="n">
         <v>1</v>
@@ -8651,41 +8635,36 @@
         <v>6</v>
       </c>
       <c r="F208" s="55" t="n">
-        <v>6910013</v>
+        <v>6910011</v>
       </c>
       <c r="G208" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_13</t>
-        </is>
-      </c>
-      <c r="I208" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_11</t>
         </is>
       </c>
       <c r="K208" s="55" t="n">
-        <v>61010013</v>
+        <v>61010011</v>
       </c>
       <c r="L208" s="55" t="inlineStr">
         <is>
-          <t>木铁弓</t>
+          <t>华丽刺剑</t>
         </is>
       </c>
       <c r="M208" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="55" t="n">
-        <v>61010014</v>
+        <v>61010012</v>
       </c>
       <c r="B209" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C209" s="55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D209" s="55" t="n">
         <v>1</v>
@@ -8694,24 +8673,19 @@
         <v>6</v>
       </c>
       <c r="F209" s="55" t="n">
-        <v>6910014</v>
+        <v>6910012</v>
       </c>
       <c r="G209" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_14</t>
-        </is>
-      </c>
-      <c r="I209" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_12</t>
         </is>
       </c>
       <c r="K209" s="55" t="n">
-        <v>61010014</v>
+        <v>61010012</v>
       </c>
       <c r="L209" s="55" t="inlineStr">
         <is>
-          <t>直弓</t>
+          <t>拐杖剑</t>
         </is>
       </c>
       <c r="M209" s="55" t="inlineStr">
@@ -8722,7 +8696,7 @@
     </row>
     <row r="210">
       <c r="A210" s="55" t="n">
-        <v>61010015</v>
+        <v>61010013</v>
       </c>
       <c r="B210" s="55" t="n">
         <v>10</v>
@@ -8737,11 +8711,11 @@
         <v>6</v>
       </c>
       <c r="F210" s="55" t="n">
-        <v>6910015</v>
+        <v>6910013</v>
       </c>
       <c r="G210" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_15</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_13</t>
         </is>
       </c>
       <c r="I210" s="55" t="inlineStr">
@@ -8750,22 +8724,22 @@
         </is>
       </c>
       <c r="K210" s="55" t="n">
-        <v>61010015</v>
+        <v>61010013</v>
       </c>
       <c r="L210" s="55" t="inlineStr">
         <is>
-          <t>魔力弓</t>
+          <t>木铁弓</t>
         </is>
       </c>
       <c r="M210" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="55" t="n">
-        <v>61010016</v>
+        <v>61010014</v>
       </c>
       <c r="B211" s="55" t="n">
         <v>10</v>
@@ -8780,11 +8754,11 @@
         <v>6</v>
       </c>
       <c r="F211" s="55" t="n">
-        <v>6910016</v>
+        <v>6910014</v>
       </c>
       <c r="G211" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_16</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_14</t>
         </is>
       </c>
       <c r="I211" s="55" t="inlineStr">
@@ -8793,28 +8767,28 @@
         </is>
       </c>
       <c r="K211" s="55" t="n">
-        <v>61010016</v>
+        <v>61010014</v>
       </c>
       <c r="L211" s="55" t="inlineStr">
         <is>
-          <t>金闪闪弓</t>
+          <t>直弓</t>
         </is>
       </c>
       <c r="M211" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="55" t="n">
-        <v>61010017</v>
+        <v>61010015</v>
       </c>
       <c r="B212" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C212" s="55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D212" s="55" t="n">
         <v>1</v>
@@ -8823,31 +8797,41 @@
         <v>6</v>
       </c>
       <c r="F212" s="55" t="n">
-        <v>6910017</v>
+        <v>6910015</v>
       </c>
       <c r="G212" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_17</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_15</t>
+        </is>
+      </c>
+      <c r="I212" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
         </is>
       </c>
       <c r="K212" s="55" t="n">
-        <v>61010017</v>
+        <v>61010015</v>
       </c>
       <c r="L212" s="55" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>魔力弓</t>
+        </is>
+      </c>
+      <c r="M212" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="55" t="n">
-        <v>61010018</v>
+        <v>61010016</v>
       </c>
       <c r="B213" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C213" s="55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D213" s="55" t="n">
         <v>1</v>
@@ -8856,30 +8840,35 @@
         <v>6</v>
       </c>
       <c r="F213" s="55" t="n">
-        <v>6910018</v>
+        <v>6910016</v>
       </c>
       <c r="G213" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_18</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_16</t>
+        </is>
+      </c>
+      <c r="I213" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
         </is>
       </c>
       <c r="K213" s="55" t="n">
-        <v>61010018</v>
+        <v>61010016</v>
       </c>
       <c r="L213" s="55" t="inlineStr">
         <is>
-          <t>火药</t>
+          <t>金闪闪弓</t>
         </is>
       </c>
       <c r="M213" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="55" t="n">
-        <v>61010019</v>
+        <v>61010017</v>
       </c>
       <c r="B214" s="55" t="n">
         <v>10</v>
@@ -8894,30 +8883,25 @@
         <v>6</v>
       </c>
       <c r="F214" s="55" t="n">
-        <v>6910019</v>
+        <v>6910017</v>
       </c>
       <c r="G214" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_19</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_17</t>
         </is>
       </c>
       <c r="K214" s="55" t="n">
-        <v>61010019</v>
+        <v>61010017</v>
       </c>
       <c r="L214" s="55" t="inlineStr">
         <is>
-          <t>危险药剂</t>
-        </is>
-      </c>
-      <c r="M214" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>炸弹</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="55" t="n">
-        <v>61010020</v>
+        <v>61010018</v>
       </c>
       <c r="B215" s="55" t="n">
         <v>10</v>
@@ -8932,103 +8916,109 @@
         <v>6</v>
       </c>
       <c r="F215" s="55" t="n">
-        <v>6910020</v>
+        <v>6910018</v>
       </c>
       <c r="G215" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_20</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_18</t>
         </is>
       </c>
       <c r="K215" s="55" t="n">
-        <v>61010020</v>
+        <v>61010018</v>
       </c>
       <c r="L215" s="55" t="inlineStr">
         <is>
-          <t>奥里给</t>
+          <t>火药</t>
         </is>
       </c>
       <c r="M215" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="55" t="n">
-        <v>70100001</v>
+        <v>61010019</v>
       </c>
       <c r="B216" s="55" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C216" s="55" t="n">
+        <v>9</v>
       </c>
       <c r="D216" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E216" s="55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F216" s="55" t="n">
-        <v>7500001</v>
+        <v>6910019</v>
       </c>
       <c r="G216" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Hat_Hat_1</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_19</t>
         </is>
       </c>
       <c r="K216" s="55" t="n">
-        <v>70100001</v>
+        <v>61010019</v>
       </c>
       <c r="L216" s="55" t="inlineStr">
         <is>
-          <t>皮套帽</t>
+          <t>危险药剂</t>
         </is>
       </c>
       <c r="M216" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="55" t="n">
-        <v>70200001</v>
+        <v>61010020</v>
       </c>
       <c r="B217" s="55" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="C217" s="55" t="n">
+        <v>9</v>
       </c>
       <c r="D217" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E217" s="55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F217" s="55" t="n">
-        <v>7510001</v>
+        <v>6910020</v>
       </c>
       <c r="G217" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Clothes_Clothes_1</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_20</t>
         </is>
       </c>
       <c r="K217" s="55" t="n">
-        <v>70200001</v>
+        <v>61010020</v>
       </c>
       <c r="L217" s="55" t="inlineStr">
         <is>
-          <t>带刺肩甲</t>
+          <t>奥里给</t>
         </is>
       </c>
       <c r="M217" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="55" t="n">
-        <v>70200002</v>
+        <v>70100001</v>
       </c>
       <c r="B218" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218" s="55" t="n">
         <v>1</v>
@@ -9037,19 +9027,19 @@
         <v>7</v>
       </c>
       <c r="F218" s="55" t="n">
-        <v>7510002</v>
+        <v>7500001</v>
       </c>
       <c r="G218" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Clothes_Clothes_2</t>
+          <t>Orc_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K218" s="55" t="n">
-        <v>70200002</v>
+        <v>70100001</v>
       </c>
       <c r="L218" s="55" t="inlineStr">
         <is>
-          <t>皮甲</t>
+          <t>皮套帽</t>
         </is>
       </c>
       <c r="M218" s="55" t="inlineStr">
@@ -9060,10 +9050,10 @@
     </row>
     <row r="219">
       <c r="A219" s="55" t="n">
-        <v>70300001</v>
+        <v>70200001</v>
       </c>
       <c r="B219" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D219" s="55" t="n">
         <v>1</v>
@@ -9072,33 +9062,33 @@
         <v>7</v>
       </c>
       <c r="F219" s="55" t="n">
-        <v>7520001</v>
+        <v>7510001</v>
       </c>
       <c r="G219" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Pants_Pants_1</t>
+          <t>Orc_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K219" s="55" t="n">
-        <v>70300001</v>
+        <v>70200001</v>
       </c>
       <c r="L219" s="55" t="inlineStr">
         <is>
-          <t>华丽皮带</t>
+          <t>带刺肩甲</t>
         </is>
       </c>
       <c r="M219" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="55" t="n">
-        <v>70300002</v>
+        <v>70200002</v>
       </c>
       <c r="B220" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D220" s="55" t="n">
         <v>1</v>
@@ -9107,25 +9097,30 @@
         <v>7</v>
       </c>
       <c r="F220" s="55" t="n">
-        <v>7520002</v>
+        <v>7510002</v>
       </c>
       <c r="G220" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Pants_Pants_2</t>
+          <t>Orc_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K220" s="55" t="n">
-        <v>70300002</v>
+        <v>70200002</v>
       </c>
       <c r="L220" s="55" t="inlineStr">
         <is>
-          <t>布腰带</t>
+          <t>皮甲</t>
+        </is>
+      </c>
+      <c r="M220" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="55" t="n">
-        <v>70300003</v>
+        <v>70300001</v>
       </c>
       <c r="B221" s="55" t="n">
         <v>3</v>
@@ -9137,30 +9132,30 @@
         <v>7</v>
       </c>
       <c r="F221" s="55" t="n">
-        <v>7520003</v>
+        <v>7520001</v>
       </c>
       <c r="G221" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Pants_Pants_3</t>
+          <t>Orc_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K221" s="55" t="n">
-        <v>70300003</v>
+        <v>70300001</v>
       </c>
       <c r="L221" s="55" t="inlineStr">
         <is>
-          <t>金属裤带</t>
+          <t>华丽皮带</t>
         </is>
       </c>
       <c r="M221" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="55" t="n">
-        <v>70300004</v>
+        <v>70300002</v>
       </c>
       <c r="B222" s="55" t="n">
         <v>3</v>
@@ -9172,36 +9167,28 @@
         <v>7</v>
       </c>
       <c r="F222" s="55" t="n">
-        <v>7520004</v>
+        <v>7520002</v>
       </c>
       <c r="G222" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Pants_Pants_4</t>
+          <t>Orc_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K222" s="55" t="n">
-        <v>70300004</v>
+        <v>70300002</v>
       </c>
       <c r="L222" s="55" t="inlineStr">
         <is>
-          <t>皮腰带</t>
-        </is>
-      </c>
-      <c r="M222" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>布腰带</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="55" t="n">
-        <v>71000001</v>
+        <v>70300003</v>
       </c>
       <c r="B223" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C223" s="55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D223" s="55" t="n">
         <v>1</v>
@@ -9210,36 +9197,33 @@
         <v>7</v>
       </c>
       <c r="F223" s="55" t="n">
-        <v>7900001</v>
+        <v>7520003</v>
       </c>
       <c r="G223" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_L_1</t>
-        </is>
-      </c>
-      <c r="I223" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1.5</t>
+          <t>Orc_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K223" s="55" t="n">
-        <v>71000001</v>
+        <v>70300003</v>
       </c>
       <c r="L223" s="55" t="inlineStr">
         <is>
-          <t>木制标枪</t>
+          <t>金属裤带</t>
+        </is>
+      </c>
+      <c r="M223" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="55" t="n">
-        <v>71000002</v>
+        <v>70300004</v>
       </c>
       <c r="B224" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C224" s="55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D224" s="55" t="n">
         <v>1</v>
@@ -9248,35 +9232,30 @@
         <v>7</v>
       </c>
       <c r="F224" s="55" t="n">
-        <v>7900002</v>
+        <v>7520004</v>
       </c>
       <c r="G224" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_L_2</t>
-        </is>
-      </c>
-      <c r="I224" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>Orc_Atlas_Pants_Pants_4</t>
         </is>
       </c>
       <c r="K224" s="55" t="n">
-        <v>71000002</v>
+        <v>70300004</v>
       </c>
       <c r="L224" s="55" t="inlineStr">
         <is>
-          <t>骨制标枪</t>
+          <t>皮腰带</t>
         </is>
       </c>
       <c r="M224" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="55" t="n">
-        <v>71000003</v>
+        <v>71000001</v>
       </c>
       <c r="B225" s="55" t="n">
         <v>10</v>
@@ -9291,35 +9270,30 @@
         <v>7</v>
       </c>
       <c r="F225" s="55" t="n">
-        <v>7900003</v>
+        <v>7900001</v>
       </c>
       <c r="G225" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_L_3</t>
+          <t>Orc_Atlas_Weapon_Weapon_L_1</t>
         </is>
       </c>
       <c r="I225" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_3&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1.5</t>
         </is>
       </c>
       <c r="K225" s="55" t="n">
-        <v>71000003</v>
+        <v>71000001</v>
       </c>
       <c r="L225" s="55" t="inlineStr">
         <is>
-          <t>铁制三叉戟</t>
-        </is>
-      </c>
-      <c r="M225" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>木制标枪</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="55" t="n">
-        <v>71010001</v>
+        <v>71000002</v>
       </c>
       <c r="B226" s="55" t="n">
         <v>10</v>
@@ -9334,25 +9308,35 @@
         <v>7</v>
       </c>
       <c r="F226" s="55" t="n">
-        <v>7910001</v>
+        <v>7900002</v>
       </c>
       <c r="G226" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_1</t>
+          <t>Orc_Atlas_Weapon_Weapon_L_2</t>
+        </is>
+      </c>
+      <c r="I226" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
         </is>
       </c>
       <c r="K226" s="55" t="n">
-        <v>71010001</v>
+        <v>71000002</v>
       </c>
       <c r="L226" s="55" t="inlineStr">
         <is>
-          <t>血腥骨锤</t>
+          <t>骨制标枪</t>
+        </is>
+      </c>
+      <c r="M226" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="55" t="n">
-        <v>71010002</v>
+        <v>71000003</v>
       </c>
       <c r="B227" s="55" t="n">
         <v>10</v>
@@ -9367,25 +9351,35 @@
         <v>7</v>
       </c>
       <c r="F227" s="55" t="n">
-        <v>7910002</v>
+        <v>7900003</v>
       </c>
       <c r="G227" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_2</t>
+          <t>Orc_Atlas_Weapon_Weapon_L_3</t>
+        </is>
+      </c>
+      <c r="I227" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_3&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
         </is>
       </c>
       <c r="K227" s="55" t="n">
-        <v>71010002</v>
+        <v>71000003</v>
       </c>
       <c r="L227" s="55" t="inlineStr">
         <is>
-          <t>石斧</t>
+          <t>铁制三叉戟</t>
+        </is>
+      </c>
+      <c r="M227" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="55" t="n">
-        <v>71010003</v>
+        <v>71010001</v>
       </c>
       <c r="B228" s="55" t="n">
         <v>10</v>
@@ -9400,36 +9394,31 @@
         <v>7</v>
       </c>
       <c r="F228" s="55" t="n">
-        <v>7910003</v>
+        <v>7910001</v>
       </c>
       <c r="G228" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_3</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_1</t>
         </is>
       </c>
       <c r="K228" s="55" t="n">
-        <v>71010003</v>
+        <v>71010001</v>
       </c>
       <c r="L228" s="55" t="inlineStr">
         <is>
-          <t>水晶劈刀</t>
-        </is>
-      </c>
-      <c r="M228" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>血腥骨锤</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="55" t="n">
-        <v>71010004</v>
+        <v>71010002</v>
       </c>
       <c r="B229" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C229" s="55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D229" s="55" t="n">
         <v>1</v>
@@ -9438,36 +9427,31 @@
         <v>7</v>
       </c>
       <c r="F229" s="55" t="n">
-        <v>7910004</v>
+        <v>7910002</v>
       </c>
       <c r="G229" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_4</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_2</t>
         </is>
       </c>
       <c r="K229" s="55" t="n">
-        <v>71010004</v>
+        <v>71010002</v>
       </c>
       <c r="L229" s="55" t="inlineStr">
         <is>
-          <t>黑色法杖</t>
-        </is>
-      </c>
-      <c r="M229" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>石斧</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="55" t="n">
-        <v>71010005</v>
+        <v>71010003</v>
       </c>
       <c r="B230" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C230" s="55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D230" s="55" t="n">
         <v>1</v>
@@ -9476,19 +9460,19 @@
         <v>7</v>
       </c>
       <c r="F230" s="55" t="n">
-        <v>7910005</v>
+        <v>7910003</v>
       </c>
       <c r="G230" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_5</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_3</t>
         </is>
       </c>
       <c r="K230" s="55" t="n">
-        <v>71010005</v>
+        <v>71010003</v>
       </c>
       <c r="L230" s="55" t="inlineStr">
         <is>
-          <t>诡异魔法书</t>
+          <t>水晶劈刀</t>
         </is>
       </c>
       <c r="M230" s="55" t="inlineStr">
@@ -9499,7 +9483,7 @@
     </row>
     <row r="231">
       <c r="A231" s="55" t="n">
-        <v>71010006</v>
+        <v>71010004</v>
       </c>
       <c r="B231" s="55" t="n">
         <v>10</v>
@@ -9514,47 +9498,123 @@
         <v>7</v>
       </c>
       <c r="F231" s="55" t="n">
-        <v>7910006</v>
+        <v>7910004</v>
       </c>
       <c r="G231" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_6</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_4</t>
         </is>
       </c>
       <c r="K231" s="55" t="n">
-        <v>71010006</v>
+        <v>71010004</v>
       </c>
       <c r="L231" s="55" t="inlineStr">
         <is>
-          <t>木制法杖</t>
+          <t>黑色法杖</t>
+        </is>
+      </c>
+      <c r="M231" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="55" t="n">
+        <v>71010005</v>
+      </c>
+      <c r="B232" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C232" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F232" s="55" t="n">
+        <v>7910005</v>
+      </c>
+      <c r="G232" s="55" t="inlineStr">
+        <is>
+          <t>Orc_Atlas_Weapon_Weapon_R_5</t>
+        </is>
+      </c>
+      <c r="K232" s="55" t="n">
+        <v>71010005</v>
+      </c>
+      <c r="L232" s="55" t="inlineStr">
+        <is>
+          <t>诡异魔法书</t>
+        </is>
+      </c>
+      <c r="M232" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="55" t="n">
+        <v>71010006</v>
+      </c>
+      <c r="B233" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C233" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F233" s="55" t="n">
+        <v>7910006</v>
+      </c>
+      <c r="G233" s="55" t="inlineStr">
+        <is>
+          <t>Orc_Atlas_Weapon_Weapon_R_6</t>
+        </is>
+      </c>
+      <c r="K233" s="55" t="n">
+        <v>71010006</v>
+      </c>
+      <c r="L233" s="55" t="inlineStr">
+        <is>
+          <t>木制法杖</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="55" t="n">
         <v>200001</v>
       </c>
-      <c r="B232" s="55" t="n">
+      <c r="B234" s="55" t="n">
         <v>11</v>
       </c>
-      <c r="D232" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E232" s="55" t="n">
+      <c r="D234" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F232" s="55" t="n">
+      <c r="F234" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="G232" s="55" t="inlineStr">
+      <c r="G234" s="55" t="inlineStr">
         <is>
           <t>Item_Juicer_1</t>
         </is>
       </c>
-      <c r="K232" s="55" t="n">
+      <c r="K234" s="55" t="n">
         <v>200001</v>
       </c>
-      <c r="L232" s="55" t="inlineStr">
+      <c r="L234" s="55" t="inlineStr">
         <is>
           <t>魔汁(榨汁产物,对魔物使用后增加经验)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -1182,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M234"/>
+  <dimension ref="A1:N233"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="10.75" customWidth="1" style="56" min="1" max="1"/>
@@ -1265,6 +1265,11 @@
           <t>reward_rarity</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="55" t="inlineStr">
@@ -1332,6 +1337,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="55" t="inlineStr">
@@ -1397,6 +1407,11 @@
       <c r="M3" s="55" t="inlineStr">
         <is>
           <t>奖励可出的稀有度白名单(逗号分隔,空=全稀有度) 1N 2R 3SR 4SSR 5UR 6L</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>道具来源白名单(逗号分隔枚举值,空=默认来源) 1=征服模式奖励</t>
         </is>
       </c>
     </row>
@@ -1456,68 +1471,73 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>200002</v>
-      </c>
-      <c r="B6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="A6" s="55" t="n">
+        <v>200003</v>
+      </c>
+      <c r="B6" s="55" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Item_TransformPotion_1</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>200002</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>幻化药(对生物使用替换spine形象,以最后吃的为准,Portrait优先,Mod移除后失效)</t>
+      <c r="G6" s="55" t="inlineStr">
+        <is>
+          <t>Item_RestorePotion_1</t>
+        </is>
+      </c>
+      <c r="K6" s="55" t="n">
+        <v>200003</v>
+      </c>
+      <c r="L6" s="55" t="inlineStr">
+        <is>
+          <t>幻原药(清除幻化,恢复原本形象)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>200003</v>
-      </c>
-      <c r="B7" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Item_RestorePotion_1</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>200003</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>幻原药(清除幻化,恢复原本形象)</t>
+      <c r="A7" s="55" t="n">
+        <v>10100001</v>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="55" t="n">
+        <v>1500001</v>
+      </c>
+      <c r="G7" s="55" t="inlineStr">
+        <is>
+          <t>Human_Atlas_Hat_Hat_1</t>
+        </is>
+      </c>
+      <c r="K7" s="55" t="n">
+        <v>10100001</v>
+      </c>
+      <c r="L7" s="55" t="inlineStr">
+        <is>
+          <t>钢头盔-------------------------------</t>
+        </is>
+      </c>
+      <c r="M7" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="55" t="n">
-        <v>10100001</v>
+        <v>10100002</v>
       </c>
       <c r="B8" s="55" t="n">
         <v>1</v>
@@ -1529,30 +1549,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="55" t="n">
-        <v>1500001</v>
+        <v>1500002</v>
       </c>
       <c r="G8" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_1</t>
+          <t>Human_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K8" s="55" t="n">
-        <v>10100001</v>
+        <v>10100002</v>
       </c>
       <c r="L8" s="55" t="inlineStr">
         <is>
-          <t>钢头盔-------------------------------</t>
+          <t>大魔法师帽</t>
         </is>
       </c>
       <c r="M8" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="55" t="n">
-        <v>10100002</v>
+        <v>10100003</v>
       </c>
       <c r="B9" s="55" t="n">
         <v>1</v>
@@ -1564,30 +1584,26 @@
         <v>1</v>
       </c>
       <c r="F9" s="55" t="n">
-        <v>1500002</v>
+        <v>1500003</v>
       </c>
       <c r="G9" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_2</t>
+          <t>Human_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K9" s="55" t="n">
-        <v>10100002</v>
+        <v>10100003</v>
       </c>
       <c r="L9" s="55" t="inlineStr">
         <is>
-          <t>大魔法师帽</t>
-        </is>
-      </c>
-      <c r="M9" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
-        </is>
-      </c>
+          <t>铁头盔</t>
+        </is>
+      </c>
+      <c r="M9" s="55" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="55" t="n">
-        <v>10100003</v>
+        <v>10100004</v>
       </c>
       <c r="B10" s="55" t="n">
         <v>1</v>
@@ -1599,26 +1615,25 @@
         <v>1</v>
       </c>
       <c r="F10" s="55" t="n">
-        <v>1500003</v>
+        <v>1500004</v>
       </c>
       <c r="G10" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_3</t>
+          <t>Human_Atlas_Hat_Hat_4</t>
         </is>
       </c>
       <c r="K10" s="55" t="n">
-        <v>10100003</v>
+        <v>10100004</v>
       </c>
       <c r="L10" s="55" t="inlineStr">
         <is>
-          <t>铁头盔</t>
-        </is>
-      </c>
-      <c r="M10" s="55" t="inlineStr"/>
+          <t>射手兜帽</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="55" t="n">
-        <v>10100004</v>
+        <v>10100005</v>
       </c>
       <c r="B11" s="55" t="n">
         <v>1</v>
@@ -1630,25 +1645,30 @@
         <v>1</v>
       </c>
       <c r="F11" s="55" t="n">
-        <v>1500004</v>
+        <v>1500005</v>
       </c>
       <c r="G11" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_4</t>
+          <t>Human_Atlas_Hat_Hat_5</t>
         </is>
       </c>
       <c r="K11" s="55" t="n">
-        <v>10100004</v>
+        <v>10100005</v>
       </c>
       <c r="L11" s="55" t="inlineStr">
         <is>
-          <t>射手兜帽</t>
+          <t>魔法师帽</t>
+        </is>
+      </c>
+      <c r="M11" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="55" t="n">
-        <v>10100005</v>
+        <v>10100007</v>
       </c>
       <c r="B12" s="55" t="n">
         <v>1</v>
@@ -1660,19 +1680,19 @@
         <v>1</v>
       </c>
       <c r="F12" s="55" t="n">
-        <v>1500005</v>
+        <v>1500007</v>
       </c>
       <c r="G12" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_5</t>
+          <t>Human_Atlas_Hat_Hat_7</t>
         </is>
       </c>
       <c r="K12" s="55" t="n">
-        <v>10100005</v>
+        <v>10100007</v>
       </c>
       <c r="L12" s="55" t="inlineStr">
         <is>
-          <t>魔法师帽</t>
+          <t>精英魔法师兜帽</t>
         </is>
       </c>
       <c r="M12" s="55" t="inlineStr">
@@ -1683,7 +1703,7 @@
     </row>
     <row r="13">
       <c r="A13" s="55" t="n">
-        <v>10100007</v>
+        <v>10100008</v>
       </c>
       <c r="B13" s="55" t="n">
         <v>1</v>
@@ -1695,30 +1715,30 @@
         <v>1</v>
       </c>
       <c r="F13" s="55" t="n">
-        <v>1500007</v>
+        <v>1500008</v>
       </c>
       <c r="G13" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_7</t>
+          <t>Human_Atlas_Hat_Hat_8</t>
         </is>
       </c>
       <c r="K13" s="55" t="n">
-        <v>10100007</v>
+        <v>10100008</v>
       </c>
       <c r="L13" s="55" t="inlineStr">
         <is>
-          <t>精英魔法师兜帽</t>
+          <t>暗杀者兜帽</t>
         </is>
       </c>
       <c r="M13" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="55" t="n">
-        <v>10100008</v>
+        <v>10100010</v>
       </c>
       <c r="B14" s="55" t="n">
         <v>1</v>
@@ -1730,19 +1750,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="55" t="n">
-        <v>1500008</v>
+        <v>1500010</v>
       </c>
       <c r="G14" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_8</t>
+          <t>Human_Atlas_Hat_Hat_10</t>
         </is>
       </c>
       <c r="K14" s="55" t="n">
-        <v>10100008</v>
+        <v>10100010</v>
       </c>
       <c r="L14" s="55" t="inlineStr">
         <is>
-          <t>暗杀者兜帽</t>
+          <t>骑士头盔</t>
         </is>
       </c>
       <c r="M14" s="55" t="inlineStr">
@@ -1753,7 +1773,7 @@
     </row>
     <row r="15">
       <c r="A15" s="55" t="n">
-        <v>10100010</v>
+        <v>10100012</v>
       </c>
       <c r="B15" s="55" t="n">
         <v>1</v>
@@ -1765,19 +1785,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="55" t="n">
-        <v>1500010</v>
+        <v>1500012</v>
       </c>
       <c r="G15" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_10</t>
+          <t>Human_Atlas_Hat_Hat_12</t>
         </is>
       </c>
       <c r="K15" s="55" t="n">
-        <v>10100010</v>
+        <v>10100012</v>
       </c>
       <c r="L15" s="55" t="inlineStr">
         <is>
-          <t>骑士头盔</t>
+          <t>死灵师面具</t>
         </is>
       </c>
       <c r="M15" s="55" t="inlineStr">
@@ -1788,7 +1808,7 @@
     </row>
     <row r="16">
       <c r="A16" s="55" t="n">
-        <v>10100012</v>
+        <v>10100013</v>
       </c>
       <c r="B16" s="55" t="n">
         <v>1</v>
@@ -1800,19 +1820,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="55" t="n">
-        <v>1500012</v>
+        <v>1500013</v>
       </c>
       <c r="G16" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_12</t>
+          <t>Human_Atlas_Hat_Hat_13</t>
         </is>
       </c>
       <c r="K16" s="55" t="n">
-        <v>10100012</v>
+        <v>10100013</v>
       </c>
       <c r="L16" s="55" t="inlineStr">
         <is>
-          <t>死灵师面具</t>
+          <t>金骑士头盔</t>
         </is>
       </c>
       <c r="M16" s="55" t="inlineStr">
@@ -1823,7 +1843,7 @@
     </row>
     <row r="17">
       <c r="A17" s="55" t="n">
-        <v>10100013</v>
+        <v>10100014</v>
       </c>
       <c r="B17" s="55" t="n">
         <v>1</v>
@@ -1835,30 +1855,30 @@
         <v>1</v>
       </c>
       <c r="F17" s="55" t="n">
-        <v>1500013</v>
+        <v>1500014</v>
       </c>
       <c r="G17" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_13</t>
+          <t>Human_Atlas_Hat_Hat_14</t>
         </is>
       </c>
       <c r="K17" s="55" t="n">
-        <v>10100013</v>
+        <v>10100014</v>
       </c>
       <c r="L17" s="55" t="inlineStr">
         <is>
-          <t>金骑士头盔</t>
+          <t>勇者头盔</t>
         </is>
       </c>
       <c r="M17" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="55" t="n">
-        <v>10100014</v>
+        <v>10100015</v>
       </c>
       <c r="B18" s="55" t="n">
         <v>1</v>
@@ -1870,30 +1890,30 @@
         <v>1</v>
       </c>
       <c r="F18" s="55" t="n">
-        <v>1500014</v>
+        <v>1500015</v>
       </c>
       <c r="G18" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_14</t>
+          <t>Human_Atlas_Hat_Hat_15</t>
         </is>
       </c>
       <c r="K18" s="55" t="n">
-        <v>10100014</v>
+        <v>10100015</v>
       </c>
       <c r="L18" s="55" t="inlineStr">
         <is>
-          <t>勇者头盔</t>
+          <t>魔力帽</t>
         </is>
       </c>
       <c r="M18" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="55" t="n">
-        <v>10100015</v>
+        <v>10100016</v>
       </c>
       <c r="B19" s="55" t="n">
         <v>1</v>
@@ -1905,30 +1925,30 @@
         <v>1</v>
       </c>
       <c r="F19" s="55" t="n">
-        <v>1500015</v>
+        <v>1500016</v>
       </c>
       <c r="G19" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_15</t>
+          <t>Human_Atlas_Hat_Hat_16</t>
         </is>
       </c>
       <c r="K19" s="55" t="n">
-        <v>10100015</v>
+        <v>10100016</v>
       </c>
       <c r="L19" s="55" t="inlineStr">
         <is>
-          <t>魔力帽</t>
+          <t>暗黑骑士头盔</t>
         </is>
       </c>
       <c r="M19" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="55" t="n">
-        <v>10100016</v>
+        <v>10100017</v>
       </c>
       <c r="B20" s="55" t="n">
         <v>1</v>
@@ -1940,19 +1960,19 @@
         <v>1</v>
       </c>
       <c r="F20" s="55" t="n">
-        <v>1500016</v>
+        <v>1500017</v>
       </c>
       <c r="G20" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_16</t>
+          <t>Human_Atlas_Hat_Hat_17</t>
         </is>
       </c>
       <c r="K20" s="55" t="n">
-        <v>10100016</v>
+        <v>10100017</v>
       </c>
       <c r="L20" s="55" t="inlineStr">
         <is>
-          <t>暗黑骑士头盔</t>
+          <t>银色骑士头盔</t>
         </is>
       </c>
       <c r="M20" s="55" t="inlineStr">
@@ -1963,10 +1983,10 @@
     </row>
     <row r="21">
       <c r="A21" s="55" t="n">
-        <v>10100017</v>
+        <v>10200001</v>
       </c>
       <c r="B21" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="55" t="n">
         <v>1</v>
@@ -1975,30 +1995,30 @@
         <v>1</v>
       </c>
       <c r="F21" s="55" t="n">
-        <v>1500017</v>
+        <v>1510001</v>
       </c>
       <c r="G21" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Hat_Hat_17</t>
+          <t>Human_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K21" s="55" t="n">
-        <v>10100017</v>
+        <v>10200001</v>
       </c>
       <c r="L21" s="55" t="inlineStr">
         <is>
-          <t>银色骑士头盔</t>
+          <t>钢盔甲上衣---------------------------</t>
         </is>
       </c>
       <c r="M21" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="55" t="n">
-        <v>10200001</v>
+        <v>10200002</v>
       </c>
       <c r="B22" s="55" t="n">
         <v>2</v>
@@ -2010,30 +2030,30 @@
         <v>1</v>
       </c>
       <c r="F22" s="55" t="n">
-        <v>1510001</v>
+        <v>1510002</v>
       </c>
       <c r="G22" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_1</t>
+          <t>Human_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K22" s="55" t="n">
-        <v>10200001</v>
+        <v>10200002</v>
       </c>
       <c r="L22" s="55" t="inlineStr">
         <is>
-          <t>钢盔甲上衣---------------------------</t>
+          <t>大魔法师上衣</t>
         </is>
       </c>
       <c r="M22" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="55" t="n">
-        <v>10200002</v>
+        <v>10200003</v>
       </c>
       <c r="B23" s="55" t="n">
         <v>2</v>
@@ -2045,30 +2065,26 @@
         <v>1</v>
       </c>
       <c r="F23" s="55" t="n">
-        <v>1510002</v>
+        <v>1510003</v>
       </c>
       <c r="G23" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_2</t>
+          <t>Human_Atlas_Clothes_Clothes_3</t>
         </is>
       </c>
       <c r="K23" s="55" t="n">
-        <v>10200002</v>
+        <v>10200003</v>
       </c>
       <c r="L23" s="55" t="inlineStr">
         <is>
-          <t>大魔法师上衣</t>
-        </is>
-      </c>
-      <c r="M23" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
-        </is>
-      </c>
+          <t>冒险者上衣</t>
+        </is>
+      </c>
+      <c r="M23" s="55" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="55" t="n">
-        <v>10200003</v>
+        <v>10200004</v>
       </c>
       <c r="B24" s="55" t="n">
         <v>2</v>
@@ -2080,26 +2096,25 @@
         <v>1</v>
       </c>
       <c r="F24" s="55" t="n">
-        <v>1510003</v>
+        <v>1510004</v>
       </c>
       <c r="G24" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_3</t>
+          <t>Human_Atlas_Clothes_Clothes_4</t>
         </is>
       </c>
       <c r="K24" s="55" t="n">
-        <v>10200003</v>
+        <v>10200004</v>
       </c>
       <c r="L24" s="55" t="inlineStr">
         <is>
-          <t>冒险者上衣</t>
-        </is>
-      </c>
-      <c r="M24" s="55" t="inlineStr"/>
+          <t>射手上衣</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="55" t="n">
-        <v>10200004</v>
+        <v>10200005</v>
       </c>
       <c r="B25" s="55" t="n">
         <v>2</v>
@@ -2111,25 +2126,30 @@
         <v>1</v>
       </c>
       <c r="F25" s="55" t="n">
-        <v>1510004</v>
+        <v>1510005</v>
       </c>
       <c r="G25" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_4</t>
+          <t>Human_Atlas_Clothes_Clothes_5</t>
         </is>
       </c>
       <c r="K25" s="55" t="n">
-        <v>10200004</v>
+        <v>10200005</v>
       </c>
       <c r="L25" s="55" t="inlineStr">
         <is>
-          <t>射手上衣</t>
+          <t>魔法师上衣</t>
+        </is>
+      </c>
+      <c r="M25" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="55" t="n">
-        <v>10200005</v>
+        <v>10200006</v>
       </c>
       <c r="B26" s="55" t="n">
         <v>2</v>
@@ -2141,19 +2161,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="55" t="n">
-        <v>1510005</v>
+        <v>1510006</v>
       </c>
       <c r="G26" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_5</t>
+          <t>Human_Atlas_Clothes_Clothes_6</t>
         </is>
       </c>
       <c r="K26" s="55" t="n">
-        <v>10200005</v>
+        <v>10200006</v>
       </c>
       <c r="L26" s="55" t="inlineStr">
         <is>
-          <t>魔法师上衣</t>
+          <t>狩猎者上衣</t>
         </is>
       </c>
       <c r="M26" s="55" t="inlineStr">
@@ -2164,7 +2184,7 @@
     </row>
     <row r="27">
       <c r="A27" s="55" t="n">
-        <v>10200006</v>
+        <v>10200007</v>
       </c>
       <c r="B27" s="55" t="n">
         <v>2</v>
@@ -2176,19 +2196,19 @@
         <v>1</v>
       </c>
       <c r="F27" s="55" t="n">
-        <v>1510006</v>
+        <v>1510007</v>
       </c>
       <c r="G27" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_6</t>
+          <t>Human_Atlas_Clothes_Clothes_7</t>
         </is>
       </c>
       <c r="K27" s="55" t="n">
-        <v>10200006</v>
+        <v>10200007</v>
       </c>
       <c r="L27" s="55" t="inlineStr">
         <is>
-          <t>狩猎者上衣</t>
+          <t>精英魔法师上衣</t>
         </is>
       </c>
       <c r="M27" s="55" t="inlineStr">
@@ -2199,7 +2219,7 @@
     </row>
     <row r="28">
       <c r="A28" s="55" t="n">
-        <v>10200007</v>
+        <v>10200008</v>
       </c>
       <c r="B28" s="55" t="n">
         <v>2</v>
@@ -2211,30 +2231,30 @@
         <v>1</v>
       </c>
       <c r="F28" s="55" t="n">
-        <v>1510007</v>
+        <v>1510008</v>
       </c>
       <c r="G28" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_7</t>
+          <t>Human_Atlas_Clothes_Clothes_8</t>
         </is>
       </c>
       <c r="K28" s="55" t="n">
-        <v>10200007</v>
+        <v>10200008</v>
       </c>
       <c r="L28" s="55" t="inlineStr">
         <is>
-          <t>精英魔法师上衣</t>
+          <t>暗杀者上衣</t>
         </is>
       </c>
       <c r="M28" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="55" t="n">
-        <v>10200008</v>
+        <v>10200009</v>
       </c>
       <c r="B29" s="55" t="n">
         <v>2</v>
@@ -2246,19 +2266,19 @@
         <v>1</v>
       </c>
       <c r="F29" s="55" t="n">
-        <v>1510008</v>
+        <v>1510009</v>
       </c>
       <c r="G29" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_8</t>
+          <t>Human_Atlas_Clothes_Clothes_9</t>
         </is>
       </c>
       <c r="K29" s="55" t="n">
-        <v>10200008</v>
+        <v>10200009</v>
       </c>
       <c r="L29" s="55" t="inlineStr">
         <is>
-          <t>暗杀者上衣</t>
+          <t>竞技者上衣</t>
         </is>
       </c>
       <c r="M29" s="55" t="inlineStr">
@@ -2269,7 +2289,7 @@
     </row>
     <row r="30">
       <c r="A30" s="55" t="n">
-        <v>10200009</v>
+        <v>10200010</v>
       </c>
       <c r="B30" s="55" t="n">
         <v>2</v>
@@ -2281,19 +2301,19 @@
         <v>1</v>
       </c>
       <c r="F30" s="55" t="n">
-        <v>1510009</v>
+        <v>1510010</v>
       </c>
       <c r="G30" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_9</t>
+          <t>Human_Atlas_Clothes_Clothes_10</t>
         </is>
       </c>
       <c r="K30" s="55" t="n">
-        <v>10200009</v>
+        <v>10200010</v>
       </c>
       <c r="L30" s="55" t="inlineStr">
         <is>
-          <t>竞技者上衣</t>
+          <t>骑士盔甲</t>
         </is>
       </c>
       <c r="M30" s="55" t="inlineStr">
@@ -2304,7 +2324,7 @@
     </row>
     <row r="31">
       <c r="A31" s="55" t="n">
-        <v>10200010</v>
+        <v>10200011</v>
       </c>
       <c r="B31" s="55" t="n">
         <v>2</v>
@@ -2316,30 +2336,30 @@
         <v>1</v>
       </c>
       <c r="F31" s="55" t="n">
-        <v>1510010</v>
+        <v>1510011</v>
       </c>
       <c r="G31" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_10</t>
+          <t>Human_Atlas_Clothes_Clothes_11</t>
         </is>
       </c>
       <c r="K31" s="55" t="n">
-        <v>10200010</v>
+        <v>10200011</v>
       </c>
       <c r="L31" s="55" t="inlineStr">
         <is>
-          <t>骑士盔甲</t>
+          <t>治疗师长袍</t>
         </is>
       </c>
       <c r="M31" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="55" t="n">
-        <v>10200011</v>
+        <v>10200012</v>
       </c>
       <c r="B32" s="55" t="n">
         <v>2</v>
@@ -2351,30 +2371,30 @@
         <v>1</v>
       </c>
       <c r="F32" s="55" t="n">
-        <v>1510011</v>
+        <v>1510012</v>
       </c>
       <c r="G32" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_11</t>
+          <t>Human_Atlas_Clothes_Clothes_12</t>
         </is>
       </c>
       <c r="K32" s="55" t="n">
-        <v>10200011</v>
+        <v>10200012</v>
       </c>
       <c r="L32" s="55" t="inlineStr">
         <is>
-          <t>治疗师长袍</t>
+          <t>死灵师长袍</t>
         </is>
       </c>
       <c r="M32" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="55" t="n">
-        <v>10200012</v>
+        <v>10200013</v>
       </c>
       <c r="B33" s="55" t="n">
         <v>2</v>
@@ -2386,19 +2406,19 @@
         <v>1</v>
       </c>
       <c r="F33" s="55" t="n">
-        <v>1510012</v>
+        <v>1510013</v>
       </c>
       <c r="G33" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_12</t>
+          <t>Human_Atlas_Clothes_Clothes_13</t>
         </is>
       </c>
       <c r="K33" s="55" t="n">
-        <v>10200012</v>
+        <v>10200013</v>
       </c>
       <c r="L33" s="55" t="inlineStr">
         <is>
-          <t>死灵师长袍</t>
+          <t>金骑士盔甲</t>
         </is>
       </c>
       <c r="M33" s="55" t="inlineStr">
@@ -2409,7 +2429,7 @@
     </row>
     <row r="34">
       <c r="A34" s="55" t="n">
-        <v>10200013</v>
+        <v>10200014</v>
       </c>
       <c r="B34" s="55" t="n">
         <v>2</v>
@@ -2421,30 +2441,30 @@
         <v>1</v>
       </c>
       <c r="F34" s="55" t="n">
-        <v>1510013</v>
+        <v>1510014</v>
       </c>
       <c r="G34" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_13</t>
+          <t>Human_Atlas_Clothes_Clothes_14</t>
         </is>
       </c>
       <c r="K34" s="55" t="n">
-        <v>10200013</v>
+        <v>10200014</v>
       </c>
       <c r="L34" s="55" t="inlineStr">
         <is>
-          <t>金骑士盔甲</t>
+          <t>勇者上衣</t>
         </is>
       </c>
       <c r="M34" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="55" t="n">
-        <v>10200014</v>
+        <v>10200015</v>
       </c>
       <c r="B35" s="55" t="n">
         <v>2</v>
@@ -2456,30 +2476,30 @@
         <v>1</v>
       </c>
       <c r="F35" s="55" t="n">
-        <v>1510014</v>
+        <v>1510015</v>
       </c>
       <c r="G35" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_14</t>
+          <t>Human_Atlas_Clothes_Clothes_15</t>
         </is>
       </c>
       <c r="K35" s="55" t="n">
-        <v>10200014</v>
+        <v>10200015</v>
       </c>
       <c r="L35" s="55" t="inlineStr">
         <is>
-          <t>勇者上衣</t>
+          <t>魔力法师上衣</t>
         </is>
       </c>
       <c r="M35" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="55" t="n">
-        <v>10200015</v>
+        <v>10200016</v>
       </c>
       <c r="B36" s="55" t="n">
         <v>2</v>
@@ -2491,30 +2511,30 @@
         <v>1</v>
       </c>
       <c r="F36" s="55" t="n">
-        <v>1510015</v>
+        <v>1510016</v>
       </c>
       <c r="G36" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_15</t>
+          <t>Human_Atlas_Clothes_Clothes_16</t>
         </is>
       </c>
       <c r="K36" s="55" t="n">
-        <v>10200015</v>
+        <v>10200016</v>
       </c>
       <c r="L36" s="55" t="inlineStr">
         <is>
-          <t>魔力法师上衣</t>
+          <t>暗黑骑士盔甲</t>
         </is>
       </c>
       <c r="M36" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="55" t="n">
-        <v>10200016</v>
+        <v>10200017</v>
       </c>
       <c r="B37" s="55" t="n">
         <v>2</v>
@@ -2526,19 +2546,19 @@
         <v>1</v>
       </c>
       <c r="F37" s="55" t="n">
-        <v>1510016</v>
+        <v>1510017</v>
       </c>
       <c r="G37" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_16</t>
+          <t>Human_Atlas_Clothes_Clothes_17</t>
         </is>
       </c>
       <c r="K37" s="55" t="n">
-        <v>10200016</v>
+        <v>10200017</v>
       </c>
       <c r="L37" s="55" t="inlineStr">
         <is>
-          <t>暗黑骑士盔甲</t>
+          <t>银色骑士盔甲</t>
         </is>
       </c>
       <c r="M37" s="55" t="inlineStr">
@@ -2549,10 +2569,10 @@
     </row>
     <row r="38">
       <c r="A38" s="55" t="n">
-        <v>10200017</v>
+        <v>10300001</v>
       </c>
       <c r="B38" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" s="55" t="n">
         <v>1</v>
@@ -2561,30 +2581,30 @@
         <v>1</v>
       </c>
       <c r="F38" s="55" t="n">
-        <v>1510017</v>
+        <v>1520001</v>
       </c>
       <c r="G38" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Clothes_Clothes_17</t>
+          <t>Human_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K38" s="55" t="n">
-        <v>10200017</v>
+        <v>10300001</v>
       </c>
       <c r="L38" s="55" t="inlineStr">
         <is>
-          <t>银色骑士盔甲</t>
+          <t>钢盔甲裤--------------------------</t>
         </is>
       </c>
       <c r="M38" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="55" t="n">
-        <v>10300001</v>
+        <v>10300002</v>
       </c>
       <c r="B39" s="55" t="n">
         <v>3</v>
@@ -2596,30 +2616,30 @@
         <v>1</v>
       </c>
       <c r="F39" s="55" t="n">
-        <v>1520001</v>
+        <v>1520002</v>
       </c>
       <c r="G39" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_1</t>
+          <t>Human_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K39" s="55" t="n">
-        <v>10300001</v>
+        <v>10300002</v>
       </c>
       <c r="L39" s="55" t="inlineStr">
         <is>
-          <t>钢盔甲裤--------------------------</t>
+          <t>大魔法师裤</t>
         </is>
       </c>
       <c r="M39" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="55" t="n">
-        <v>10300002</v>
+        <v>10300003</v>
       </c>
       <c r="B40" s="55" t="n">
         <v>3</v>
@@ -2631,30 +2651,26 @@
         <v>1</v>
       </c>
       <c r="F40" s="55" t="n">
-        <v>1520002</v>
+        <v>1520003</v>
       </c>
       <c r="G40" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_2</t>
+          <t>Human_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K40" s="55" t="n">
-        <v>10300002</v>
+        <v>10300003</v>
       </c>
       <c r="L40" s="55" t="inlineStr">
         <is>
-          <t>大魔法师裤</t>
-        </is>
-      </c>
-      <c r="M40" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
-        </is>
-      </c>
+          <t>冒险者裤子</t>
+        </is>
+      </c>
+      <c r="M40" s="55" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="55" t="n">
-        <v>10300003</v>
+        <v>10300004</v>
       </c>
       <c r="B41" s="55" t="n">
         <v>3</v>
@@ -2666,26 +2682,25 @@
         <v>1</v>
       </c>
       <c r="F41" s="55" t="n">
-        <v>1520003</v>
+        <v>1520004</v>
       </c>
       <c r="G41" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_3</t>
+          <t>Human_Atlas_Pants_Pants_4</t>
         </is>
       </c>
       <c r="K41" s="55" t="n">
-        <v>10300003</v>
+        <v>10300004</v>
       </c>
       <c r="L41" s="55" t="inlineStr">
         <is>
-          <t>冒险者裤子</t>
-        </is>
-      </c>
-      <c r="M41" s="55" t="inlineStr"/>
+          <t>射手裤子</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="55" t="n">
-        <v>10300004</v>
+        <v>10300005</v>
       </c>
       <c r="B42" s="55" t="n">
         <v>3</v>
@@ -2697,25 +2712,30 @@
         <v>1</v>
       </c>
       <c r="F42" s="55" t="n">
-        <v>1520004</v>
+        <v>1520005</v>
       </c>
       <c r="G42" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_4</t>
+          <t>Human_Atlas_Pants_Pants_5</t>
         </is>
       </c>
       <c r="K42" s="55" t="n">
-        <v>10300004</v>
+        <v>10300005</v>
       </c>
       <c r="L42" s="55" t="inlineStr">
         <is>
-          <t>射手裤子</t>
+          <t>魔法师裤</t>
+        </is>
+      </c>
+      <c r="M42" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="55" t="n">
-        <v>10300005</v>
+        <v>10300006</v>
       </c>
       <c r="B43" s="55" t="n">
         <v>3</v>
@@ -2727,19 +2747,19 @@
         <v>1</v>
       </c>
       <c r="F43" s="55" t="n">
-        <v>1520005</v>
+        <v>1520006</v>
       </c>
       <c r="G43" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_5</t>
+          <t>Human_Atlas_Pants_Pants_6</t>
         </is>
       </c>
       <c r="K43" s="55" t="n">
-        <v>10300005</v>
+        <v>10300006</v>
       </c>
       <c r="L43" s="55" t="inlineStr">
         <is>
-          <t>魔法师裤</t>
+          <t>狩猎者裤</t>
         </is>
       </c>
       <c r="M43" s="55" t="inlineStr">
@@ -2750,7 +2770,7 @@
     </row>
     <row r="44">
       <c r="A44" s="55" t="n">
-        <v>10300006</v>
+        <v>10300007</v>
       </c>
       <c r="B44" s="55" t="n">
         <v>3</v>
@@ -2762,19 +2782,19 @@
         <v>1</v>
       </c>
       <c r="F44" s="55" t="n">
-        <v>1520006</v>
+        <v>1520007</v>
       </c>
       <c r="G44" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_6</t>
+          <t>Human_Atlas_Pants_Pants_7</t>
         </is>
       </c>
       <c r="K44" s="55" t="n">
-        <v>10300006</v>
+        <v>10300007</v>
       </c>
       <c r="L44" s="55" t="inlineStr">
         <is>
-          <t>狩猎者裤</t>
+          <t>精英魔法师裤</t>
         </is>
       </c>
       <c r="M44" s="55" t="inlineStr">
@@ -2785,7 +2805,7 @@
     </row>
     <row r="45">
       <c r="A45" s="55" t="n">
-        <v>10300007</v>
+        <v>10300008</v>
       </c>
       <c r="B45" s="55" t="n">
         <v>3</v>
@@ -2797,30 +2817,30 @@
         <v>1</v>
       </c>
       <c r="F45" s="55" t="n">
-        <v>1520007</v>
+        <v>1520008</v>
       </c>
       <c r="G45" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_7</t>
+          <t>Human_Atlas_Pants_Pants_8</t>
         </is>
       </c>
       <c r="K45" s="55" t="n">
-        <v>10300007</v>
+        <v>10300008</v>
       </c>
       <c r="L45" s="55" t="inlineStr">
         <is>
-          <t>精英魔法师裤</t>
+          <t>暗杀者裤</t>
         </is>
       </c>
       <c r="M45" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="55" t="n">
-        <v>10300008</v>
+        <v>10300009</v>
       </c>
       <c r="B46" s="55" t="n">
         <v>3</v>
@@ -2832,19 +2852,19 @@
         <v>1</v>
       </c>
       <c r="F46" s="55" t="n">
-        <v>1520008</v>
+        <v>1520009</v>
       </c>
       <c r="G46" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_8</t>
+          <t>Human_Atlas_Pants_Pants_9</t>
         </is>
       </c>
       <c r="K46" s="55" t="n">
-        <v>10300008</v>
+        <v>10300009</v>
       </c>
       <c r="L46" s="55" t="inlineStr">
         <is>
-          <t>暗杀者裤</t>
+          <t>竞技者裤</t>
         </is>
       </c>
       <c r="M46" s="55" t="inlineStr">
@@ -2855,7 +2875,7 @@
     </row>
     <row r="47">
       <c r="A47" s="55" t="n">
-        <v>10300009</v>
+        <v>10300010</v>
       </c>
       <c r="B47" s="55" t="n">
         <v>3</v>
@@ -2867,19 +2887,19 @@
         <v>1</v>
       </c>
       <c r="F47" s="55" t="n">
-        <v>1520009</v>
+        <v>1520010</v>
       </c>
       <c r="G47" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_9</t>
+          <t>Human_Atlas_Pants_Pants_10</t>
         </is>
       </c>
       <c r="K47" s="55" t="n">
-        <v>10300009</v>
+        <v>10300010</v>
       </c>
       <c r="L47" s="55" t="inlineStr">
         <is>
-          <t>竞技者裤</t>
+          <t>骑士裤</t>
         </is>
       </c>
       <c r="M47" s="55" t="inlineStr">
@@ -2890,7 +2910,7 @@
     </row>
     <row r="48">
       <c r="A48" s="55" t="n">
-        <v>10300010</v>
+        <v>10300011</v>
       </c>
       <c r="B48" s="55" t="n">
         <v>3</v>
@@ -2902,30 +2922,30 @@
         <v>1</v>
       </c>
       <c r="F48" s="55" t="n">
-        <v>1520010</v>
+        <v>1520011</v>
       </c>
       <c r="G48" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_10</t>
+          <t>Human_Atlas_Pants_Pants_11</t>
         </is>
       </c>
       <c r="K48" s="55" t="n">
-        <v>10300010</v>
+        <v>10300011</v>
       </c>
       <c r="L48" s="55" t="inlineStr">
         <is>
-          <t>骑士裤</t>
+          <t>治疗师裤</t>
         </is>
       </c>
       <c r="M48" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="55" t="n">
-        <v>10300011</v>
+        <v>10300012</v>
       </c>
       <c r="B49" s="55" t="n">
         <v>3</v>
@@ -2937,30 +2957,30 @@
         <v>1</v>
       </c>
       <c r="F49" s="55" t="n">
-        <v>1520011</v>
+        <v>1520012</v>
       </c>
       <c r="G49" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_11</t>
+          <t>Human_Atlas_Pants_Pants_12</t>
         </is>
       </c>
       <c r="K49" s="55" t="n">
-        <v>10300011</v>
+        <v>10300012</v>
       </c>
       <c r="L49" s="55" t="inlineStr">
         <is>
-          <t>治疗师裤</t>
+          <t>死灵师裤</t>
         </is>
       </c>
       <c r="M49" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="55" t="n">
-        <v>10300012</v>
+        <v>10300013</v>
       </c>
       <c r="B50" s="55" t="n">
         <v>3</v>
@@ -2972,19 +2992,19 @@
         <v>1</v>
       </c>
       <c r="F50" s="55" t="n">
-        <v>1520012</v>
+        <v>1520013</v>
       </c>
       <c r="G50" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_12</t>
+          <t>Human_Atlas_Pants_Pants_13</t>
         </is>
       </c>
       <c r="K50" s="55" t="n">
-        <v>10300012</v>
+        <v>10300013</v>
       </c>
       <c r="L50" s="55" t="inlineStr">
         <is>
-          <t>死灵师裤</t>
+          <t>金骑士裤</t>
         </is>
       </c>
       <c r="M50" s="55" t="inlineStr">
@@ -2995,7 +3015,7 @@
     </row>
     <row r="51">
       <c r="A51" s="55" t="n">
-        <v>10300013</v>
+        <v>10300014</v>
       </c>
       <c r="B51" s="55" t="n">
         <v>3</v>
@@ -3007,30 +3027,30 @@
         <v>1</v>
       </c>
       <c r="F51" s="55" t="n">
-        <v>1520013</v>
+        <v>1520014</v>
       </c>
       <c r="G51" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_13</t>
+          <t>Human_Atlas_Pants_Pants_14</t>
         </is>
       </c>
       <c r="K51" s="55" t="n">
-        <v>10300013</v>
+        <v>10300014</v>
       </c>
       <c r="L51" s="55" t="inlineStr">
         <is>
-          <t>金骑士裤</t>
+          <t>勇者裤</t>
         </is>
       </c>
       <c r="M51" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="55" t="n">
-        <v>10300014</v>
+        <v>10300015</v>
       </c>
       <c r="B52" s="55" t="n">
         <v>3</v>
@@ -3042,30 +3062,30 @@
         <v>1</v>
       </c>
       <c r="F52" s="55" t="n">
-        <v>1520014</v>
+        <v>1520015</v>
       </c>
       <c r="G52" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_14</t>
+          <t>Human_Atlas_Pants_Pants_15</t>
         </is>
       </c>
       <c r="K52" s="55" t="n">
-        <v>10300014</v>
+        <v>10300015</v>
       </c>
       <c r="L52" s="55" t="inlineStr">
         <is>
-          <t>勇者裤</t>
+          <t>魔力法师裤</t>
         </is>
       </c>
       <c r="M52" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="55" t="n">
-        <v>10300015</v>
+        <v>10300016</v>
       </c>
       <c r="B53" s="55" t="n">
         <v>3</v>
@@ -3077,30 +3097,30 @@
         <v>1</v>
       </c>
       <c r="F53" s="55" t="n">
-        <v>1520015</v>
+        <v>1520016</v>
       </c>
       <c r="G53" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_15</t>
+          <t>Human_Atlas_Pants_Pants_16</t>
         </is>
       </c>
       <c r="K53" s="55" t="n">
-        <v>10300015</v>
+        <v>10300016</v>
       </c>
       <c r="L53" s="55" t="inlineStr">
         <is>
-          <t>魔力法师裤</t>
+          <t>暗黑骑士裤</t>
         </is>
       </c>
       <c r="M53" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="55" t="n">
-        <v>10300016</v>
+        <v>10300017</v>
       </c>
       <c r="B54" s="55" t="n">
         <v>3</v>
@@ -3112,19 +3132,19 @@
         <v>1</v>
       </c>
       <c r="F54" s="55" t="n">
-        <v>1520016</v>
+        <v>1520017</v>
       </c>
       <c r="G54" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_16</t>
+          <t>Human_Atlas_Pants_Pants_17</t>
         </is>
       </c>
       <c r="K54" s="55" t="n">
-        <v>10300016</v>
+        <v>10300017</v>
       </c>
       <c r="L54" s="55" t="inlineStr">
         <is>
-          <t>暗黑骑士裤</t>
+          <t>银色骑士裤</t>
         </is>
       </c>
       <c r="M54" s="55" t="inlineStr">
@@ -3135,10 +3155,13 @@
     </row>
     <row r="55">
       <c r="A55" s="55" t="n">
-        <v>10300017</v>
+        <v>11000001</v>
       </c>
       <c r="B55" s="55" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C55" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="D55" s="55" t="n">
         <v>1</v>
@@ -3147,30 +3170,30 @@
         <v>1</v>
       </c>
       <c r="F55" s="55" t="n">
-        <v>1520017</v>
+        <v>1900001</v>
       </c>
       <c r="G55" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Pants_Pants_17</t>
+          <t>Human_Atlas_Weapon_Weapon_L_1</t>
         </is>
       </c>
       <c r="K55" s="55" t="n">
-        <v>10300017</v>
+        <v>11000001</v>
       </c>
       <c r="L55" s="55" t="inlineStr">
         <is>
-          <t>银色骑士裤</t>
+          <t>钢剑----------------------------</t>
         </is>
       </c>
       <c r="M55" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="55" t="n">
-        <v>11000001</v>
+        <v>11000002</v>
       </c>
       <c r="B56" s="55" t="n">
         <v>10</v>
@@ -3185,36 +3208,32 @@
         <v>1</v>
       </c>
       <c r="F56" s="55" t="n">
-        <v>1900001</v>
+        <v>1900002</v>
       </c>
       <c r="G56" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_1</t>
+          <t>Human_Atlas_Weapon_Weapon_L_2</t>
         </is>
       </c>
       <c r="K56" s="55" t="n">
-        <v>11000001</v>
+        <v>11000002</v>
       </c>
       <c r="L56" s="55" t="inlineStr">
         <is>
-          <t>钢剑----------------------------</t>
-        </is>
-      </c>
-      <c r="M56" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>铁剑</t>
+        </is>
+      </c>
+      <c r="M56" s="55" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="55" t="n">
-        <v>11000002</v>
+        <v>11000003</v>
       </c>
       <c r="B57" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C57" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="55" t="n">
         <v>1</v>
@@ -3223,26 +3242,26 @@
         <v>1</v>
       </c>
       <c r="F57" s="55" t="n">
-        <v>1900002</v>
+        <v>1900003</v>
       </c>
       <c r="G57" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_2</t>
+          <t>Human_Atlas_Weapon_Weapon_L_3</t>
         </is>
       </c>
       <c r="K57" s="55" t="n">
-        <v>11000002</v>
+        <v>11000003</v>
       </c>
       <c r="L57" s="55" t="inlineStr">
         <is>
-          <t>铁剑</t>
+          <t>火法杖</t>
         </is>
       </c>
       <c r="M57" s="55" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="55" t="n">
-        <v>11000003</v>
+        <v>11000004</v>
       </c>
       <c r="B58" s="55" t="n">
         <v>10</v>
@@ -3257,32 +3276,32 @@
         <v>1</v>
       </c>
       <c r="F58" s="55" t="n">
-        <v>1900003</v>
+        <v>1900004</v>
       </c>
       <c r="G58" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_3</t>
+          <t>Human_Atlas_Weapon_Weapon_L_4</t>
         </is>
       </c>
       <c r="K58" s="55" t="n">
-        <v>11000003</v>
+        <v>11000004</v>
       </c>
       <c r="L58" s="55" t="inlineStr">
         <is>
-          <t>火法杖</t>
+          <t>冰法杖</t>
         </is>
       </c>
       <c r="M58" s="55" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="55" t="n">
-        <v>11000004</v>
+        <v>11000005</v>
       </c>
       <c r="B59" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C59" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="55" t="n">
         <v>1</v>
@@ -3291,26 +3310,26 @@
         <v>1</v>
       </c>
       <c r="F59" s="55" t="n">
-        <v>1900004</v>
+        <v>1900005</v>
       </c>
       <c r="G59" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_4</t>
+          <t>Human_Atlas_Weapon_Weapon_L_5</t>
         </is>
       </c>
       <c r="K59" s="55" t="n">
-        <v>11000004</v>
+        <v>11000005</v>
       </c>
       <c r="L59" s="55" t="inlineStr">
         <is>
-          <t>冰法杖</t>
+          <t>残破剑</t>
         </is>
       </c>
       <c r="M59" s="55" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="55" t="n">
-        <v>11000005</v>
+        <v>11000006</v>
       </c>
       <c r="B60" s="55" t="n">
         <v>10</v>
@@ -3325,32 +3344,32 @@
         <v>1</v>
       </c>
       <c r="F60" s="55" t="n">
-        <v>1900005</v>
+        <v>1900006</v>
       </c>
       <c r="G60" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_5</t>
+          <t>Human_Atlas_Weapon_Weapon_L_6</t>
         </is>
       </c>
       <c r="K60" s="55" t="n">
-        <v>11000005</v>
+        <v>11000006</v>
       </c>
       <c r="L60" s="55" t="inlineStr">
         <is>
-          <t>残破剑</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="M60" s="55" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="55" t="n">
-        <v>11000006</v>
+        <v>11000007</v>
       </c>
       <c r="B61" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C61" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" s="55" t="n">
         <v>1</v>
@@ -3359,26 +3378,30 @@
         <v>1</v>
       </c>
       <c r="F61" s="55" t="n">
-        <v>1900006</v>
+        <v>1900007</v>
       </c>
       <c r="G61" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_6</t>
+          <t>Human_Atlas_Weapon_Weapon_L_7</t>
         </is>
       </c>
       <c r="K61" s="55" t="n">
-        <v>11000006</v>
+        <v>11000007</v>
       </c>
       <c r="L61" s="55" t="inlineStr">
         <is>
-          <t>短刀</t>
-        </is>
-      </c>
-      <c r="M61" s="55" t="inlineStr"/>
+          <t>绿宝石法杖</t>
+        </is>
+      </c>
+      <c r="M61" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="55" t="n">
-        <v>11000007</v>
+        <v>11000008</v>
       </c>
       <c r="B62" s="55" t="n">
         <v>10</v>
@@ -3393,19 +3416,19 @@
         <v>1</v>
       </c>
       <c r="F62" s="55" t="n">
-        <v>1900007</v>
+        <v>1900008</v>
       </c>
       <c r="G62" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_7</t>
+          <t>Human_Atlas_Weapon_Weapon_L_8</t>
         </is>
       </c>
       <c r="K62" s="55" t="n">
-        <v>11000007</v>
+        <v>11000008</v>
       </c>
       <c r="L62" s="55" t="inlineStr">
         <is>
-          <t>绿宝石法杖</t>
+          <t>魔力法杖</t>
         </is>
       </c>
       <c r="M62" s="55" t="inlineStr">
@@ -3416,7 +3439,7 @@
     </row>
     <row r="63">
       <c r="A63" s="55" t="n">
-        <v>11000008</v>
+        <v>11000009</v>
       </c>
       <c r="B63" s="55" t="n">
         <v>10</v>
@@ -3431,30 +3454,30 @@
         <v>1</v>
       </c>
       <c r="F63" s="55" t="n">
-        <v>1900008</v>
+        <v>1900009</v>
       </c>
       <c r="G63" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_8</t>
+          <t>Human_Atlas_Weapon_Weapon_L_9</t>
         </is>
       </c>
       <c r="K63" s="55" t="n">
-        <v>11000008</v>
+        <v>11000009</v>
       </c>
       <c r="L63" s="55" t="inlineStr">
         <is>
-          <t>魔力法杖</t>
+          <t>星之法杖</t>
         </is>
       </c>
       <c r="M63" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="55" t="n">
-        <v>11000009</v>
+        <v>11000010</v>
       </c>
       <c r="B64" s="55" t="n">
         <v>10</v>
@@ -3469,30 +3492,26 @@
         <v>1</v>
       </c>
       <c r="F64" s="55" t="n">
-        <v>1900009</v>
+        <v>1900010</v>
       </c>
       <c r="G64" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_9</t>
+          <t>Human_Atlas_Weapon_Weapon_L_10</t>
         </is>
       </c>
       <c r="K64" s="55" t="n">
-        <v>11000009</v>
+        <v>11000010</v>
       </c>
       <c r="L64" s="55" t="inlineStr">
         <is>
-          <t>星之法杖</t>
-        </is>
-      </c>
-      <c r="M64" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
-        </is>
-      </c>
+          <t>冰法杖</t>
+        </is>
+      </c>
+      <c r="M64" s="55" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="55" t="n">
-        <v>11000010</v>
+        <v>11000011</v>
       </c>
       <c r="B65" s="55" t="n">
         <v>10</v>
@@ -3507,32 +3526,32 @@
         <v>1</v>
       </c>
       <c r="F65" s="55" t="n">
-        <v>1900010</v>
+        <v>1900011</v>
       </c>
       <c r="G65" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_10</t>
+          <t>Human_Atlas_Weapon_Weapon_L_11</t>
         </is>
       </c>
       <c r="K65" s="55" t="n">
-        <v>11000010</v>
+        <v>11000011</v>
       </c>
       <c r="L65" s="55" t="inlineStr">
         <is>
-          <t>冰法杖</t>
+          <t>电法杖</t>
         </is>
       </c>
       <c r="M65" s="55" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="55" t="n">
-        <v>11000011</v>
+        <v>11000012</v>
       </c>
       <c r="B66" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C66" s="55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" s="55" t="n">
         <v>1</v>
@@ -3541,32 +3560,36 @@
         <v>1</v>
       </c>
       <c r="F66" s="55" t="n">
-        <v>1900011</v>
+        <v>1900012</v>
       </c>
       <c r="G66" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_11</t>
+          <t>Human_Atlas_Weapon_Weapon_L_12</t>
         </is>
       </c>
       <c r="K66" s="55" t="n">
-        <v>11000011</v>
+        <v>11000012</v>
       </c>
       <c r="L66" s="55" t="inlineStr">
         <is>
-          <t>电法杖</t>
-        </is>
-      </c>
-      <c r="M66" s="55" t="inlineStr"/>
+          <t>大剑</t>
+        </is>
+      </c>
+      <c r="M66" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="55" t="n">
-        <v>11000012</v>
+        <v>11000013</v>
       </c>
       <c r="B67" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C67" s="55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67" s="55" t="n">
         <v>1</v>
@@ -3575,19 +3598,19 @@
         <v>1</v>
       </c>
       <c r="F67" s="55" t="n">
-        <v>1900012</v>
+        <v>1900013</v>
       </c>
       <c r="G67" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_12</t>
+          <t>Human_Atlas_Weapon_Weapon_L_13</t>
         </is>
       </c>
       <c r="K67" s="55" t="n">
-        <v>11000012</v>
+        <v>11000013</v>
       </c>
       <c r="L67" s="55" t="inlineStr">
         <is>
-          <t>大剑</t>
+          <t>死灵法杖</t>
         </is>
       </c>
       <c r="M67" s="55" t="inlineStr">
@@ -3598,13 +3621,13 @@
     </row>
     <row r="68">
       <c r="A68" s="55" t="n">
-        <v>11000013</v>
+        <v>11000015</v>
       </c>
       <c r="B68" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C68" s="55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D68" s="55" t="n">
         <v>1</v>
@@ -3613,36 +3636,36 @@
         <v>1</v>
       </c>
       <c r="F68" s="55" t="n">
-        <v>1900013</v>
+        <v>1900015</v>
       </c>
       <c r="G68" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_13</t>
+          <t>Human_Atlas_Weapon_Weapon_L_15</t>
         </is>
       </c>
       <c r="K68" s="55" t="n">
-        <v>11000013</v>
+        <v>11000015</v>
       </c>
       <c r="L68" s="55" t="inlineStr">
         <is>
-          <t>死灵法杖</t>
+          <t>钢铁盾</t>
         </is>
       </c>
       <c r="M68" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="55" t="n">
-        <v>11000015</v>
+        <v>11010001</v>
       </c>
       <c r="B69" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C69" s="55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" s="55" t="n">
         <v>1</v>
@@ -3651,30 +3674,31 @@
         <v>1</v>
       </c>
       <c r="F69" s="55" t="n">
-        <v>1900015</v>
+        <v>1910001</v>
       </c>
       <c r="G69" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_L_15</t>
+          <t>Human_Atlas_Weapon_Weapon_R_1</t>
+        </is>
+      </c>
+      <c r="I69" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Human_Atlas_Other_Arrow_1&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180</t>
         </is>
       </c>
       <c r="K69" s="55" t="n">
-        <v>11000015</v>
+        <v>11010001</v>
       </c>
       <c r="L69" s="55" t="inlineStr">
         <is>
-          <t>钢铁盾</t>
-        </is>
-      </c>
-      <c r="M69" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>木弓</t>
+        </is>
+      </c>
+      <c r="M69" s="55" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="55" t="n">
-        <v>11010001</v>
+        <v>11010002</v>
       </c>
       <c r="B70" s="55" t="n">
         <v>10</v>
@@ -3689,31 +3713,35 @@
         <v>1</v>
       </c>
       <c r="F70" s="55" t="n">
-        <v>1910001</v>
+        <v>1910002</v>
       </c>
       <c r="G70" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_R_1</t>
+          <t>Human_Atlas_Weapon_Weapon_R_2</t>
         </is>
       </c>
       <c r="I70" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Human_Atlas_Other_Arrow_1&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180</t>
+          <t>ShowSprite:Human_Atlas_Other_Arrow_2&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
         </is>
       </c>
       <c r="K70" s="55" t="n">
-        <v>11010001</v>
+        <v>11010002</v>
       </c>
       <c r="L70" s="55" t="inlineStr">
         <is>
-          <t>木弓</t>
-        </is>
-      </c>
-      <c r="M70" s="55" t="inlineStr"/>
+          <t>钢弓</t>
+        </is>
+      </c>
+      <c r="M70" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="55" t="n">
-        <v>11010002</v>
+        <v>11010003</v>
       </c>
       <c r="B71" s="55" t="n">
         <v>10</v>
@@ -3728,24 +3756,24 @@
         <v>1</v>
       </c>
       <c r="F71" s="55" t="n">
-        <v>1910002</v>
+        <v>1910003</v>
       </c>
       <c r="G71" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_R_2</t>
+          <t>Human_Atlas_Weapon_Weapon_R_3</t>
         </is>
       </c>
       <c r="I71" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Human_Atlas_Other_Arrow_2&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
+          <t>ShowSprite:Human_Atlas_Other_Arrow_3&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
         </is>
       </c>
       <c r="K71" s="55" t="n">
-        <v>11010002</v>
+        <v>11010003</v>
       </c>
       <c r="L71" s="55" t="inlineStr">
         <is>
-          <t>钢弓</t>
+          <t>红木弓</t>
         </is>
       </c>
       <c r="M71" s="55" t="inlineStr">
@@ -3756,13 +3784,13 @@
     </row>
     <row r="72">
       <c r="A72" s="55" t="n">
-        <v>11010003</v>
+        <v>11020021</v>
       </c>
       <c r="B72" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C72" s="55" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D72" s="55" t="n">
         <v>1</v>
@@ -3771,24 +3799,19 @@
         <v>1</v>
       </c>
       <c r="F72" s="55" t="n">
-        <v>1910003</v>
+        <v>1920021</v>
       </c>
       <c r="G72" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_R_3</t>
-        </is>
-      </c>
-      <c r="I72" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Human_Atlas_Other_Arrow_3&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
+          <t>Human_Atlas_Weapon_Weapon_LR_21</t>
         </is>
       </c>
       <c r="K72" s="55" t="n">
-        <v>11010003</v>
+        <v>11020021</v>
       </c>
       <c r="L72" s="55" t="inlineStr">
         <is>
-          <t>红木弓</t>
+          <t>冒险者盾剑</t>
         </is>
       </c>
       <c r="M72" s="55" t="inlineStr">
@@ -3799,7 +3822,7 @@
     </row>
     <row r="73">
       <c r="A73" s="55" t="n">
-        <v>11020021</v>
+        <v>11020022</v>
       </c>
       <c r="B73" s="55" t="n">
         <v>10</v>
@@ -3814,36 +3837,36 @@
         <v>1</v>
       </c>
       <c r="F73" s="55" t="n">
-        <v>1920021</v>
+        <v>1920022</v>
       </c>
       <c r="G73" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_LR_21</t>
+          <t>Human_Atlas_Weapon_Weapon_LR_22</t>
         </is>
       </c>
       <c r="K73" s="55" t="n">
-        <v>11020021</v>
+        <v>11020022</v>
       </c>
       <c r="L73" s="55" t="inlineStr">
         <is>
-          <t>冒险者盾剑</t>
+          <t>勇者盾剑</t>
         </is>
       </c>
       <c r="M73" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="55" t="n">
-        <v>11020022</v>
+        <v>11020014</v>
       </c>
       <c r="B74" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C74" s="55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D74" s="55" t="n">
         <v>1</v>
@@ -3852,68 +3875,60 @@
         <v>1</v>
       </c>
       <c r="F74" s="55" t="n">
-        <v>1920022</v>
+        <v>1920014</v>
       </c>
       <c r="G74" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_LR_22</t>
+          <t>Human_Atlas_Weapon_Weapon_LR_14</t>
         </is>
       </c>
       <c r="K74" s="55" t="n">
-        <v>11020022</v>
+        <v>11020014</v>
       </c>
       <c r="L74" s="55" t="inlineStr">
         <is>
-          <t>勇者盾剑</t>
+          <t>精致短刀</t>
         </is>
       </c>
       <c r="M74" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="55" t="n">
-        <v>11020014</v>
+        <v>20100001</v>
       </c>
       <c r="B75" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C75" s="55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="55" t="n">
-        <v>1920014</v>
+        <v>2500001</v>
       </c>
       <c r="G75" s="55" t="inlineStr">
         <is>
-          <t>Human_Atlas_Weapon_Weapon_LR_14</t>
+          <t>Skeleton_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K75" s="55" t="n">
-        <v>11020014</v>
+        <v>20100001</v>
       </c>
       <c r="L75" s="55" t="inlineStr">
         <is>
-          <t>精致短刀</t>
-        </is>
-      </c>
-      <c r="M75" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>骷髅-帽子-皇冠-------------------</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="55" t="n">
-        <v>20100001</v>
+        <v>20100002</v>
       </c>
       <c r="B76" s="55" t="n">
         <v>1</v>
@@ -3925,25 +3940,30 @@
         <v>2</v>
       </c>
       <c r="F76" s="55" t="n">
-        <v>2500001</v>
+        <v>2500002</v>
       </c>
       <c r="G76" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_1</t>
+          <t>Skeleton_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K76" s="55" t="n">
-        <v>20100001</v>
+        <v>20100002</v>
       </c>
       <c r="L76" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-皇冠-------------------</t>
+          <t>骷髅-帽子-铁制头盔</t>
+        </is>
+      </c>
+      <c r="M76" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="55" t="n">
-        <v>20100002</v>
+        <v>20100003</v>
       </c>
       <c r="B77" s="55" t="n">
         <v>1</v>
@@ -3955,19 +3975,19 @@
         <v>2</v>
       </c>
       <c r="F77" s="55" t="n">
-        <v>2500002</v>
+        <v>2500003</v>
       </c>
       <c r="G77" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_2</t>
+          <t>Skeleton_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K77" s="55" t="n">
-        <v>20100002</v>
+        <v>20100003</v>
       </c>
       <c r="L77" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-铁制头盔</t>
+          <t>骷髅-帽子-异域头巾</t>
         </is>
       </c>
       <c r="M77" s="55" t="inlineStr">
@@ -3978,7 +3998,7 @@
     </row>
     <row r="78">
       <c r="A78" s="55" t="n">
-        <v>20100003</v>
+        <v>20100004</v>
       </c>
       <c r="B78" s="55" t="n">
         <v>1</v>
@@ -3990,19 +4010,19 @@
         <v>2</v>
       </c>
       <c r="F78" s="55" t="n">
-        <v>2500003</v>
+        <v>2500004</v>
       </c>
       <c r="G78" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_3</t>
+          <t>Skeleton_Atlas_Hat_Hat_4</t>
         </is>
       </c>
       <c r="K78" s="55" t="n">
-        <v>20100003</v>
+        <v>20100004</v>
       </c>
       <c r="L78" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-异域头巾</t>
+          <t>骷髅-帽子-魔力帽</t>
         </is>
       </c>
       <c r="M78" s="55" t="inlineStr">
@@ -4013,7 +4033,7 @@
     </row>
     <row r="79">
       <c r="A79" s="55" t="n">
-        <v>20100004</v>
+        <v>20100005</v>
       </c>
       <c r="B79" s="55" t="n">
         <v>1</v>
@@ -4025,30 +4045,30 @@
         <v>2</v>
       </c>
       <c r="F79" s="55" t="n">
-        <v>2500004</v>
+        <v>2500005</v>
       </c>
       <c r="G79" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_4</t>
+          <t>Skeleton_Atlas_Hat_Hat_5</t>
         </is>
       </c>
       <c r="K79" s="55" t="n">
-        <v>20100004</v>
+        <v>20100005</v>
       </c>
       <c r="L79" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-魔力帽</t>
+          <t>骷髅-帽子-草帽</t>
         </is>
       </c>
       <c r="M79" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="55" t="n">
-        <v>20100005</v>
+        <v>20100006</v>
       </c>
       <c r="B80" s="55" t="n">
         <v>1</v>
@@ -4060,30 +4080,30 @@
         <v>2</v>
       </c>
       <c r="F80" s="55" t="n">
-        <v>2500005</v>
+        <v>2500006</v>
       </c>
       <c r="G80" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_5</t>
+          <t>Skeleton_Atlas_Hat_Hat_6</t>
         </is>
       </c>
       <c r="K80" s="55" t="n">
-        <v>20100005</v>
+        <v>20100006</v>
       </c>
       <c r="L80" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-草帽</t>
+          <t>骷髅-帽子-恶魔头颅</t>
         </is>
       </c>
       <c r="M80" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="55" t="n">
-        <v>20100006</v>
+        <v>20100007</v>
       </c>
       <c r="B81" s="55" t="n">
         <v>1</v>
@@ -4095,33 +4115,33 @@
         <v>2</v>
       </c>
       <c r="F81" s="55" t="n">
-        <v>2500006</v>
+        <v>2500007</v>
       </c>
       <c r="G81" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_6</t>
+          <t>Skeleton_Atlas_Hat_Hat_7</t>
         </is>
       </c>
       <c r="K81" s="55" t="n">
-        <v>20100006</v>
+        <v>20100007</v>
       </c>
       <c r="L81" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-恶魔头颅</t>
+          <t>骷髅-帽子-魔王之角</t>
         </is>
       </c>
       <c r="M81" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="55" t="n">
-        <v>20100007</v>
+        <v>20200001</v>
       </c>
       <c r="B82" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" s="55" t="n">
         <v>1</v>
@@ -4130,30 +4150,25 @@
         <v>2</v>
       </c>
       <c r="F82" s="55" t="n">
-        <v>2500007</v>
+        <v>2510001</v>
       </c>
       <c r="G82" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Hat_Hat_7</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K82" s="55" t="n">
-        <v>20100007</v>
+        <v>20200001</v>
       </c>
       <c r="L82" s="55" t="inlineStr">
         <is>
-          <t>骷髅-帽子-魔王之角</t>
-        </is>
-      </c>
-      <c r="M82" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>骷髅-衣服-肩甲1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="55" t="n">
-        <v>20200001</v>
+        <v>20200002</v>
       </c>
       <c r="B83" s="55" t="n">
         <v>2</v>
@@ -4165,25 +4180,25 @@
         <v>2</v>
       </c>
       <c r="F83" s="55" t="n">
-        <v>2510001</v>
+        <v>2510002</v>
       </c>
       <c r="G83" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_1</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K83" s="55" t="n">
-        <v>20200001</v>
+        <v>20200002</v>
       </c>
       <c r="L83" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-肩甲1</t>
+          <t>骷髅-衣服-肩甲2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="55" t="n">
-        <v>20200002</v>
+        <v>20200003</v>
       </c>
       <c r="B84" s="55" t="n">
         <v>2</v>
@@ -4195,25 +4210,25 @@
         <v>2</v>
       </c>
       <c r="F84" s="55" t="n">
-        <v>2510002</v>
+        <v>2510003</v>
       </c>
       <c r="G84" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_2</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_3</t>
         </is>
       </c>
       <c r="K84" s="55" t="n">
-        <v>20200002</v>
+        <v>20200003</v>
       </c>
       <c r="L84" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-肩甲2</t>
+          <t>骷髅-衣服-破烂的肩甲</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="55" t="n">
-        <v>20200003</v>
+        <v>20200004</v>
       </c>
       <c r="B85" s="55" t="n">
         <v>2</v>
@@ -4225,25 +4240,30 @@
         <v>2</v>
       </c>
       <c r="F85" s="55" t="n">
-        <v>2510003</v>
+        <v>2510004</v>
       </c>
       <c r="G85" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_3</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_4</t>
         </is>
       </c>
       <c r="K85" s="55" t="n">
-        <v>20200003</v>
+        <v>20200004</v>
       </c>
       <c r="L85" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂的肩甲</t>
+          <t>骷髅-衣服-丝绸披肩</t>
+        </is>
+      </c>
+      <c r="M85" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="55" t="n">
-        <v>20200004</v>
+        <v>20200005</v>
       </c>
       <c r="B86" s="55" t="n">
         <v>2</v>
@@ -4255,19 +4275,19 @@
         <v>2</v>
       </c>
       <c r="F86" s="55" t="n">
-        <v>2510004</v>
+        <v>2510005</v>
       </c>
       <c r="G86" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_4</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_5</t>
         </is>
       </c>
       <c r="K86" s="55" t="n">
-        <v>20200004</v>
+        <v>20200005</v>
       </c>
       <c r="L86" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-丝绸披肩</t>
+          <t>骷髅-衣服-魔法披肩</t>
         </is>
       </c>
       <c r="M86" s="55" t="inlineStr">
@@ -4278,7 +4298,7 @@
     </row>
     <row r="87">
       <c r="A87" s="55" t="n">
-        <v>20200005</v>
+        <v>20200006</v>
       </c>
       <c r="B87" s="55" t="n">
         <v>2</v>
@@ -4290,30 +4310,25 @@
         <v>2</v>
       </c>
       <c r="F87" s="55" t="n">
-        <v>2510005</v>
+        <v>2510006</v>
       </c>
       <c r="G87" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_5</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_6</t>
         </is>
       </c>
       <c r="K87" s="55" t="n">
-        <v>20200005</v>
+        <v>20200006</v>
       </c>
       <c r="L87" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-魔法披肩</t>
-        </is>
-      </c>
-      <c r="M87" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>骷髅-衣服-麻布衣</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="55" t="n">
-        <v>20200006</v>
+        <v>20200007</v>
       </c>
       <c r="B88" s="55" t="n">
         <v>2</v>
@@ -4325,25 +4340,30 @@
         <v>2</v>
       </c>
       <c r="F88" s="55" t="n">
-        <v>2510006</v>
+        <v>2510007</v>
       </c>
       <c r="G88" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_6</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_7</t>
         </is>
       </c>
       <c r="K88" s="55" t="n">
-        <v>20200006</v>
+        <v>20200007</v>
       </c>
       <c r="L88" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-麻布衣</t>
+          <t>骷髅-衣服-蔚蓝铠甲</t>
+        </is>
+      </c>
+      <c r="M88" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="55" t="n">
-        <v>20200007</v>
+        <v>20200008</v>
       </c>
       <c r="B89" s="55" t="n">
         <v>2</v>
@@ -4355,30 +4375,25 @@
         <v>2</v>
       </c>
       <c r="F89" s="55" t="n">
-        <v>2510007</v>
+        <v>2510008</v>
       </c>
       <c r="G89" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_7</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_8</t>
         </is>
       </c>
       <c r="K89" s="55" t="n">
-        <v>20200007</v>
+        <v>20200008</v>
       </c>
       <c r="L89" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-蔚蓝铠甲</t>
-        </is>
-      </c>
-      <c r="M89" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-衣服-破烂法衣</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="55" t="n">
-        <v>20200008</v>
+        <v>20200009</v>
       </c>
       <c r="B90" s="55" t="n">
         <v>2</v>
@@ -4390,25 +4405,30 @@
         <v>2</v>
       </c>
       <c r="F90" s="55" t="n">
-        <v>2510008</v>
+        <v>2510009</v>
       </c>
       <c r="G90" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_8</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_9</t>
         </is>
       </c>
       <c r="K90" s="55" t="n">
-        <v>20200008</v>
+        <v>20200009</v>
       </c>
       <c r="L90" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂法衣</t>
+          <t>骷髅-衣服-琥珀铠甲</t>
+        </is>
+      </c>
+      <c r="M90" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="55" t="n">
-        <v>20200009</v>
+        <v>20200010</v>
       </c>
       <c r="B91" s="55" t="n">
         <v>2</v>
@@ -4420,30 +4440,30 @@
         <v>2</v>
       </c>
       <c r="F91" s="55" t="n">
-        <v>2510009</v>
+        <v>2510010</v>
       </c>
       <c r="G91" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_9</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_10</t>
         </is>
       </c>
       <c r="K91" s="55" t="n">
-        <v>20200009</v>
+        <v>20200010</v>
       </c>
       <c r="L91" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-琥珀铠甲</t>
+          <t>骷髅-衣服-远古铠甲</t>
         </is>
       </c>
       <c r="M91" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="55" t="n">
-        <v>20200010</v>
+        <v>20200011</v>
       </c>
       <c r="B92" s="55" t="n">
         <v>2</v>
@@ -4455,33 +4475,33 @@
         <v>2</v>
       </c>
       <c r="F92" s="55" t="n">
-        <v>2510010</v>
+        <v>2510011</v>
       </c>
       <c r="G92" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_10</t>
+          <t>Skeleton_Atlas_Clothes_Clothes_11</t>
         </is>
       </c>
       <c r="K92" s="55" t="n">
-        <v>20200010</v>
+        <v>20200011</v>
       </c>
       <c r="L92" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-远古铠甲</t>
+          <t>骷髅-衣服-深红战衣</t>
         </is>
       </c>
       <c r="M92" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="55" t="n">
-        <v>20200011</v>
+        <v>20300001</v>
       </c>
       <c r="B93" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" s="55" t="n">
         <v>1</v>
@@ -4490,30 +4510,25 @@
         <v>2</v>
       </c>
       <c r="F93" s="55" t="n">
-        <v>2510011</v>
+        <v>2520001</v>
       </c>
       <c r="G93" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Clothes_Clothes_11</t>
+          <t>Skeleton_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K93" s="55" t="n">
-        <v>20200011</v>
+        <v>20300001</v>
       </c>
       <c r="L93" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-深红战衣</t>
-        </is>
-      </c>
-      <c r="M93" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-衣服-破烂腰带</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="55" t="n">
-        <v>20300001</v>
+        <v>20300003</v>
       </c>
       <c r="B94" s="55" t="n">
         <v>3</v>
@@ -4525,25 +4540,25 @@
         <v>2</v>
       </c>
       <c r="F94" s="55" t="n">
-        <v>2520001</v>
+        <v>2520003</v>
       </c>
       <c r="G94" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_1</t>
+          <t>Skeleton_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K94" s="55" t="n">
-        <v>20300001</v>
+        <v>20300003</v>
       </c>
       <c r="L94" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂腰带</t>
+          <t>骷髅-衣服-破烂法裤</t>
         </is>
       </c>
     </row>
     <row r="95" ht="12" customHeight="1" s="56">
       <c r="A95" s="55" t="n">
-        <v>20300003</v>
+        <v>20300007</v>
       </c>
       <c r="B95" s="55" t="n">
         <v>3</v>
@@ -4555,25 +4570,30 @@
         <v>2</v>
       </c>
       <c r="F95" s="55" t="n">
-        <v>2520003</v>
+        <v>2520007</v>
       </c>
       <c r="G95" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_3</t>
+          <t>Skeleton_Atlas_Pants_Pants_7</t>
         </is>
       </c>
       <c r="K95" s="55" t="n">
-        <v>20300003</v>
+        <v>20300007</v>
       </c>
       <c r="L95" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂法裤</t>
+          <t>骷髅-衣服-蔚蓝腰带</t>
+        </is>
+      </c>
+      <c r="M95" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="55" t="n">
-        <v>20300007</v>
+        <v>20300009</v>
       </c>
       <c r="B96" s="55" t="n">
         <v>3</v>
@@ -4585,19 +4605,19 @@
         <v>2</v>
       </c>
       <c r="F96" s="55" t="n">
-        <v>2520007</v>
+        <v>2520009</v>
       </c>
       <c r="G96" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_7</t>
+          <t>Skeleton_Atlas_Pants_Pants_9</t>
         </is>
       </c>
       <c r="K96" s="55" t="n">
-        <v>20300007</v>
+        <v>20300009</v>
       </c>
       <c r="L96" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-蔚蓝腰带</t>
+          <t>骷髅-衣服-琥珀腰带</t>
         </is>
       </c>
       <c r="M96" s="55" t="inlineStr">
@@ -4608,7 +4628,7 @@
     </row>
     <row r="97">
       <c r="A97" s="55" t="n">
-        <v>20300009</v>
+        <v>20300011</v>
       </c>
       <c r="B97" s="55" t="n">
         <v>3</v>
@@ -4620,19 +4640,19 @@
         <v>2</v>
       </c>
       <c r="F97" s="55" t="n">
-        <v>2520009</v>
+        <v>2520011</v>
       </c>
       <c r="G97" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_9</t>
+          <t>Skeleton_Atlas_Pants_Pants_11</t>
         </is>
       </c>
       <c r="K97" s="55" t="n">
-        <v>20300009</v>
+        <v>20300011</v>
       </c>
       <c r="L97" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-琥珀腰带</t>
+          <t>骷髅-衣服-深红腰带</t>
         </is>
       </c>
       <c r="M97" s="55" t="inlineStr">
@@ -4643,10 +4663,13 @@
     </row>
     <row r="98">
       <c r="A98" s="55" t="n">
-        <v>20300011</v>
+        <v>21000001</v>
       </c>
       <c r="B98" s="55" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C98" s="55" t="n">
+        <v>8</v>
       </c>
       <c r="D98" s="55" t="n">
         <v>1</v>
@@ -4655,30 +4678,33 @@
         <v>2</v>
       </c>
       <c r="F98" s="55" t="n">
-        <v>2520011</v>
+        <v>2900001</v>
       </c>
       <c r="G98" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Pants_Pants_11</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_1</t>
+        </is>
+      </c>
+      <c r="H98" s="55" t="n">
+        <v>45</v>
+      </c>
+      <c r="I98" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K98" s="55" t="n">
-        <v>20300011</v>
+        <v>21000001</v>
       </c>
       <c r="L98" s="55" t="inlineStr">
         <is>
-          <t>骷髅-衣服-深红腰带</t>
-        </is>
-      </c>
-      <c r="M98" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-武器-骨头</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="55" t="n">
-        <v>21000001</v>
+        <v>21000002</v>
       </c>
       <c r="B99" s="55" t="n">
         <v>10</v>
@@ -4693,11 +4719,11 @@
         <v>2</v>
       </c>
       <c r="F99" s="55" t="n">
-        <v>2900001</v>
+        <v>2900002</v>
       </c>
       <c r="G99" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_1</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_2</t>
         </is>
       </c>
       <c r="H99" s="55" t="n">
@@ -4705,21 +4731,26 @@
       </c>
       <c r="I99" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K99" s="55" t="n">
-        <v>21000001</v>
+        <v>21000002</v>
       </c>
       <c r="L99" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-骨头</t>
+          <t>骷髅-武器-鸡腿</t>
+        </is>
+      </c>
+      <c r="M99" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="55" t="n">
-        <v>21000002</v>
+        <v>21000003</v>
       </c>
       <c r="B100" s="55" t="n">
         <v>10</v>
@@ -4734,38 +4765,30 @@
         <v>2</v>
       </c>
       <c r="F100" s="55" t="n">
-        <v>2900002</v>
+        <v>2900003</v>
       </c>
       <c r="G100" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_2</t>
-        </is>
-      </c>
-      <c r="H100" s="55" t="n">
-        <v>45</v>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_3</t>
+        </is>
       </c>
       <c r="I100" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K100" s="55" t="n">
-        <v>21000002</v>
+        <v>21000003</v>
       </c>
       <c r="L100" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-鸡腿</t>
-        </is>
-      </c>
-      <c r="M100" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>骷髅-武器-无用之书</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="55" t="n">
-        <v>21000003</v>
+        <v>21000004</v>
       </c>
       <c r="B101" s="55" t="n">
         <v>10</v>
@@ -4780,30 +4803,30 @@
         <v>2</v>
       </c>
       <c r="F101" s="55" t="n">
-        <v>2900003</v>
+        <v>2900004</v>
       </c>
       <c r="G101" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_3</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_4</t>
         </is>
       </c>
       <c r="I101" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_4&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K101" s="55" t="n">
-        <v>21000003</v>
+        <v>21000004</v>
       </c>
       <c r="L101" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-无用之书</t>
+          <t>骷髅-武器-木制圆盾</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="55" t="n">
-        <v>21000004</v>
+        <v>21000005</v>
       </c>
       <c r="B102" s="55" t="n">
         <v>10</v>
@@ -4818,30 +4841,35 @@
         <v>2</v>
       </c>
       <c r="F102" s="55" t="n">
-        <v>2900004</v>
+        <v>2900005</v>
       </c>
       <c r="G102" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_4</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_5</t>
         </is>
       </c>
       <c r="I102" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_4&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_5&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K102" s="55" t="n">
-        <v>21000004</v>
+        <v>21000005</v>
       </c>
       <c r="L102" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-木制圆盾</t>
+          <t>骷髅-武器-飞镖</t>
+        </is>
+      </c>
+      <c r="M102" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="55" t="n">
-        <v>21000005</v>
+        <v>21000006</v>
       </c>
       <c r="B103" s="55" t="n">
         <v>10</v>
@@ -4856,35 +4884,35 @@
         <v>2</v>
       </c>
       <c r="F103" s="55" t="n">
-        <v>2900005</v>
+        <v>2900006</v>
       </c>
       <c r="G103" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_5</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_6</t>
         </is>
       </c>
       <c r="I103" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_5&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_6&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K103" s="55" t="n">
-        <v>21000005</v>
+        <v>21000006</v>
       </c>
       <c r="L103" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-飞镖</t>
+          <t>骷髅-武器-骷髅头</t>
         </is>
       </c>
       <c r="M103" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="55" t="n">
-        <v>21000006</v>
+        <v>21000007</v>
       </c>
       <c r="B104" s="55" t="n">
         <v>10</v>
@@ -4899,35 +4927,35 @@
         <v>2</v>
       </c>
       <c r="F104" s="55" t="n">
-        <v>2900006</v>
+        <v>2900007</v>
       </c>
       <c r="G104" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_6</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_7</t>
         </is>
       </c>
       <c r="I104" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_6&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_7&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K104" s="55" t="n">
-        <v>21000006</v>
+        <v>21000007</v>
       </c>
       <c r="L104" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-骷髅头</t>
+          <t>骷髅-武器-欧里给</t>
         </is>
       </c>
       <c r="M104" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="55" t="n">
-        <v>21000007</v>
+        <v>21000008</v>
       </c>
       <c r="B105" s="55" t="n">
         <v>10</v>
@@ -4942,35 +4970,35 @@
         <v>2</v>
       </c>
       <c r="F105" s="55" t="n">
-        <v>2900007</v>
+        <v>2900008</v>
       </c>
       <c r="G105" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_7</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_8</t>
         </is>
       </c>
       <c r="I105" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_7&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_8&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K105" s="55" t="n">
-        <v>21000007</v>
+        <v>21000008</v>
       </c>
       <c r="L105" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-欧里给</t>
+          <t>骷髅-武器-苹果</t>
         </is>
       </c>
       <c r="M105" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="55" t="n">
-        <v>21000008</v>
+        <v>21000009</v>
       </c>
       <c r="B106" s="55" t="n">
         <v>10</v>
@@ -4985,35 +5013,35 @@
         <v>2</v>
       </c>
       <c r="F106" s="55" t="n">
-        <v>2900008</v>
+        <v>2900009</v>
       </c>
       <c r="G106" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_8</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_9</t>
         </is>
       </c>
       <c r="I106" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_8&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_9&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K106" s="55" t="n">
-        <v>21000008</v>
+        <v>21000009</v>
       </c>
       <c r="L106" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-苹果</t>
+          <t>骷髅-武器-28年拉菲</t>
         </is>
       </c>
       <c r="M106" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="55" t="n">
-        <v>21000009</v>
+        <v>21000010</v>
       </c>
       <c r="B107" s="55" t="n">
         <v>10</v>
@@ -5028,41 +5056,41 @@
         <v>2</v>
       </c>
       <c r="F107" s="55" t="n">
-        <v>2900009</v>
+        <v>2900010</v>
       </c>
       <c r="G107" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_9</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_L_10</t>
         </is>
       </c>
       <c r="I107" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_9&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
+          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_10&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
         </is>
       </c>
       <c r="K107" s="55" t="n">
-        <v>21000009</v>
+        <v>21000010</v>
       </c>
       <c r="L107" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-28年拉菲</t>
+          <t>骷髅-武器-金币</t>
         </is>
       </c>
       <c r="M107" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="55" t="n">
-        <v>21000010</v>
+        <v>21010001</v>
       </c>
       <c r="B108" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C108" s="55" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D108" s="55" t="n">
         <v>1</v>
@@ -5071,24 +5099,22 @@
         <v>2</v>
       </c>
       <c r="F108" s="55" t="n">
-        <v>2900010</v>
+        <v>2910001</v>
       </c>
       <c r="G108" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_L_10</t>
-        </is>
-      </c>
-      <c r="I108" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_10&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
-        </is>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_1</t>
+        </is>
+      </c>
+      <c r="H108" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K108" s="55" t="n">
-        <v>21000010</v>
+        <v>21010001</v>
       </c>
       <c r="L108" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-金币</t>
+          <t>骷髅-武器-铁剑</t>
         </is>
       </c>
       <c r="M108" s="55" t="inlineStr">
@@ -5099,13 +5125,13 @@
     </row>
     <row r="109">
       <c r="A109" s="55" t="n">
-        <v>21010001</v>
+        <v>21010002</v>
       </c>
       <c r="B109" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C109" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" s="55" t="n">
         <v>1</v>
@@ -5114,33 +5140,28 @@
         <v>2</v>
       </c>
       <c r="F109" s="55" t="n">
-        <v>2910001</v>
+        <v>2910002</v>
       </c>
       <c r="G109" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_1</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_2</t>
         </is>
       </c>
       <c r="H109" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K109" s="55" t="n">
-        <v>21010001</v>
+        <v>21010002</v>
       </c>
       <c r="L109" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-铁剑</t>
-        </is>
-      </c>
-      <c r="M109" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>骷髅-武器-火法杖</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="55" t="n">
-        <v>21010002</v>
+        <v>21010003</v>
       </c>
       <c r="B110" s="55" t="n">
         <v>10</v>
@@ -5155,34 +5176,34 @@
         <v>2</v>
       </c>
       <c r="F110" s="55" t="n">
-        <v>2910002</v>
+        <v>2910003</v>
       </c>
       <c r="G110" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_2</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_3</t>
         </is>
       </c>
       <c r="H110" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K110" s="55" t="n">
-        <v>21010002</v>
+        <v>21010003</v>
       </c>
       <c r="L110" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-火法杖</t>
+          <t>骷髅-武器-冰法杖</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="55" t="n">
-        <v>21010003</v>
+        <v>21010004</v>
       </c>
       <c r="B111" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C111" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" s="55" t="n">
         <v>1</v>
@@ -5191,28 +5212,28 @@
         <v>2</v>
       </c>
       <c r="F111" s="55" t="n">
-        <v>2910003</v>
+        <v>2910004</v>
       </c>
       <c r="G111" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_3</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_4</t>
         </is>
       </c>
       <c r="H111" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K111" s="55" t="n">
-        <v>21010003</v>
+        <v>21010004</v>
       </c>
       <c r="L111" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-冰法杖</t>
+          <t>骷髅-武器-残破剑</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="55" t="n">
-        <v>21010004</v>
+        <v>21010005</v>
       </c>
       <c r="B112" s="55" t="n">
         <v>10</v>
@@ -5227,28 +5248,25 @@
         <v>2</v>
       </c>
       <c r="F112" s="55" t="n">
-        <v>2910004</v>
+        <v>2910005</v>
       </c>
       <c r="G112" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_4</t>
-        </is>
-      </c>
-      <c r="H112" s="55" t="n">
-        <v>-45</v>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_5</t>
+        </is>
       </c>
       <c r="K112" s="55" t="n">
-        <v>21010004</v>
+        <v>21010005</v>
       </c>
       <c r="L112" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-残破剑</t>
+          <t>骷髅-武器-短刀</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="55" t="n">
-        <v>21010005</v>
+        <v>21010006</v>
       </c>
       <c r="B113" s="55" t="n">
         <v>10</v>
@@ -5263,25 +5281,30 @@
         <v>2</v>
       </c>
       <c r="F113" s="55" t="n">
-        <v>2910005</v>
+        <v>2910006</v>
       </c>
       <c r="G113" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_5</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_6</t>
         </is>
       </c>
       <c r="K113" s="55" t="n">
-        <v>21010005</v>
+        <v>21010006</v>
       </c>
       <c r="L113" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-短刀</t>
+          <t>骷髅-武器-骷髅剑</t>
+        </is>
+      </c>
+      <c r="M113" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="55" t="n">
-        <v>21010006</v>
+        <v>21010007</v>
       </c>
       <c r="B114" s="55" t="n">
         <v>10</v>
@@ -5296,19 +5319,19 @@
         <v>2</v>
       </c>
       <c r="F114" s="55" t="n">
-        <v>2910006</v>
+        <v>2910007</v>
       </c>
       <c r="G114" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_6</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_7</t>
         </is>
       </c>
       <c r="K114" s="55" t="n">
-        <v>21010006</v>
+        <v>21010007</v>
       </c>
       <c r="L114" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-骷髅剑</t>
+          <t>骷髅-武器-金色刺剑</t>
         </is>
       </c>
       <c r="M114" s="55" t="inlineStr">
@@ -5319,7 +5342,7 @@
     </row>
     <row r="115">
       <c r="A115" s="55" t="n">
-        <v>21010007</v>
+        <v>21010008</v>
       </c>
       <c r="B115" s="55" t="n">
         <v>10</v>
@@ -5334,30 +5357,25 @@
         <v>2</v>
       </c>
       <c r="F115" s="55" t="n">
-        <v>2910007</v>
+        <v>2910008</v>
       </c>
       <c r="G115" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_7</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_8</t>
         </is>
       </c>
       <c r="K115" s="55" t="n">
-        <v>21010007</v>
+        <v>21010008</v>
       </c>
       <c r="L115" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-金色刺剑</t>
-        </is>
-      </c>
-      <c r="M115" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>骷髅-武器-铲子</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="55" t="n">
-        <v>21010008</v>
+        <v>21010009</v>
       </c>
       <c r="B116" s="55" t="n">
         <v>10</v>
@@ -5372,25 +5390,30 @@
         <v>2</v>
       </c>
       <c r="F116" s="55" t="n">
-        <v>2910008</v>
+        <v>2910009</v>
       </c>
       <c r="G116" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_8</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_9</t>
         </is>
       </c>
       <c r="K116" s="55" t="n">
-        <v>21010008</v>
+        <v>21010009</v>
       </c>
       <c r="L116" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-铲子</t>
+          <t>骷髅-武器-冰之哀伤</t>
+        </is>
+      </c>
+      <c r="M116" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="55" t="n">
-        <v>21010009</v>
+        <v>21010010</v>
       </c>
       <c r="B117" s="55" t="n">
         <v>10</v>
@@ -5405,19 +5428,19 @@
         <v>2</v>
       </c>
       <c r="F117" s="55" t="n">
-        <v>2910009</v>
+        <v>2910010</v>
       </c>
       <c r="G117" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_9</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_10</t>
         </is>
       </c>
       <c r="K117" s="55" t="n">
-        <v>21010009</v>
+        <v>21010010</v>
       </c>
       <c r="L117" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-冰之哀伤</t>
+          <t>骷髅-武器-火之高兴</t>
         </is>
       </c>
       <c r="M117" s="55" t="inlineStr">
@@ -5428,13 +5451,13 @@
     </row>
     <row r="118">
       <c r="A118" s="55" t="n">
-        <v>21010010</v>
+        <v>21010011</v>
       </c>
       <c r="B118" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C118" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118" s="55" t="n">
         <v>1</v>
@@ -5443,30 +5466,33 @@
         <v>2</v>
       </c>
       <c r="F118" s="55" t="n">
-        <v>2910010</v>
+        <v>2910011</v>
       </c>
       <c r="G118" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_10</t>
-        </is>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_11</t>
+        </is>
+      </c>
+      <c r="H118" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K118" s="55" t="n">
-        <v>21010010</v>
+        <v>21010011</v>
       </c>
       <c r="L118" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-火之高兴</t>
+          <t>骷髅-武器-绿宝石法杖</t>
         </is>
       </c>
       <c r="M118" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="55" t="n">
-        <v>21010011</v>
+        <v>21010012</v>
       </c>
       <c r="B119" s="55" t="n">
         <v>10</v>
@@ -5481,22 +5507,22 @@
         <v>2</v>
       </c>
       <c r="F119" s="55" t="n">
-        <v>2910011</v>
+        <v>2910012</v>
       </c>
       <c r="G119" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_11</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_12</t>
         </is>
       </c>
       <c r="H119" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K119" s="55" t="n">
-        <v>21010011</v>
+        <v>21010012</v>
       </c>
       <c r="L119" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-绿宝石法杖</t>
+          <t>骷髅-武器-魔力法杖</t>
         </is>
       </c>
       <c r="M119" s="55" t="inlineStr">
@@ -5507,7 +5533,7 @@
     </row>
     <row r="120">
       <c r="A120" s="55" t="n">
-        <v>21010012</v>
+        <v>21010013</v>
       </c>
       <c r="B120" s="55" t="n">
         <v>10</v>
@@ -5522,22 +5548,19 @@
         <v>2</v>
       </c>
       <c r="F120" s="55" t="n">
-        <v>2910012</v>
+        <v>2910013</v>
       </c>
       <c r="G120" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_12</t>
-        </is>
-      </c>
-      <c r="H120" s="55" t="n">
-        <v>-45</v>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_13</t>
+        </is>
       </c>
       <c r="K120" s="55" t="n">
-        <v>21010012</v>
+        <v>21010013</v>
       </c>
       <c r="L120" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-魔力法杖</t>
+          <t>骷髅-武器-扫帚</t>
         </is>
       </c>
       <c r="M120" s="55" t="inlineStr">
@@ -5548,7 +5571,7 @@
     </row>
     <row r="121">
       <c r="A121" s="55" t="n">
-        <v>21010013</v>
+        <v>21010014</v>
       </c>
       <c r="B121" s="55" t="n">
         <v>10</v>
@@ -5563,30 +5586,30 @@
         <v>2</v>
       </c>
       <c r="F121" s="55" t="n">
-        <v>2910013</v>
+        <v>2910014</v>
       </c>
       <c r="G121" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_13</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_14</t>
         </is>
       </c>
       <c r="K121" s="55" t="n">
-        <v>21010013</v>
+        <v>21010014</v>
       </c>
       <c r="L121" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-扫帚</t>
+          <t>骷髅-武器-星之法杖</t>
         </is>
       </c>
       <c r="M121" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="55" t="n">
-        <v>21010014</v>
+        <v>21010015</v>
       </c>
       <c r="B122" s="55" t="n">
         <v>10</v>
@@ -5601,19 +5624,19 @@
         <v>2</v>
       </c>
       <c r="F122" s="55" t="n">
-        <v>2910014</v>
+        <v>2910015</v>
       </c>
       <c r="G122" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_14</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_15</t>
         </is>
       </c>
       <c r="K122" s="55" t="n">
-        <v>21010014</v>
+        <v>21010015</v>
       </c>
       <c r="L122" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-星之法杖</t>
+          <t>骷髅-武器-百变法杖</t>
         </is>
       </c>
       <c r="M122" s="55" t="inlineStr">
@@ -5624,7 +5647,7 @@
     </row>
     <row r="123">
       <c r="A123" s="55" t="n">
-        <v>21010015</v>
+        <v>21010016</v>
       </c>
       <c r="B123" s="55" t="n">
         <v>10</v>
@@ -5639,19 +5662,19 @@
         <v>2</v>
       </c>
       <c r="F123" s="55" t="n">
-        <v>2910015</v>
+        <v>2910016</v>
       </c>
       <c r="G123" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_15</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_16</t>
         </is>
       </c>
       <c r="K123" s="55" t="n">
-        <v>21010015</v>
+        <v>21010016</v>
       </c>
       <c r="L123" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-百变法杖</t>
+          <t>骷髅-武器-琥珀法杖</t>
         </is>
       </c>
       <c r="M123" s="55" t="inlineStr">
@@ -5662,7 +5685,7 @@
     </row>
     <row r="124">
       <c r="A124" s="55" t="n">
-        <v>21010016</v>
+        <v>21010017</v>
       </c>
       <c r="B124" s="55" t="n">
         <v>10</v>
@@ -5677,19 +5700,19 @@
         <v>2</v>
       </c>
       <c r="F124" s="55" t="n">
-        <v>2910016</v>
+        <v>2910017</v>
       </c>
       <c r="G124" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_16</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_17</t>
         </is>
       </c>
       <c r="K124" s="55" t="n">
-        <v>21010016</v>
+        <v>21010017</v>
       </c>
       <c r="L124" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-琥珀法杖</t>
+          <t>骷髅-武器-爱之天使</t>
         </is>
       </c>
       <c r="M124" s="55" t="inlineStr">
@@ -5700,7 +5723,7 @@
     </row>
     <row r="125">
       <c r="A125" s="55" t="n">
-        <v>21010017</v>
+        <v>21010018</v>
       </c>
       <c r="B125" s="55" t="n">
         <v>10</v>
@@ -5715,19 +5738,19 @@
         <v>2</v>
       </c>
       <c r="F125" s="55" t="n">
-        <v>2910017</v>
+        <v>2910018</v>
       </c>
       <c r="G125" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_17</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_18</t>
         </is>
       </c>
       <c r="K125" s="55" t="n">
-        <v>21010017</v>
+        <v>21010018</v>
       </c>
       <c r="L125" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-爱之天使</t>
+          <t>骷髅-武器-星域之杖</t>
         </is>
       </c>
       <c r="M125" s="55" t="inlineStr">
@@ -5738,7 +5761,7 @@
     </row>
     <row r="126">
       <c r="A126" s="55" t="n">
-        <v>21010018</v>
+        <v>21010019</v>
       </c>
       <c r="B126" s="55" t="n">
         <v>10</v>
@@ -5753,30 +5776,30 @@
         <v>2</v>
       </c>
       <c r="F126" s="55" t="n">
-        <v>2910018</v>
+        <v>2910019</v>
       </c>
       <c r="G126" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_18</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_19</t>
         </is>
       </c>
       <c r="K126" s="55" t="n">
-        <v>21010018</v>
+        <v>21010019</v>
       </c>
       <c r="L126" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-星域之杖</t>
+          <t>骷髅-武器-结晶法杖</t>
         </is>
       </c>
       <c r="M126" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="55" t="n">
-        <v>21010019</v>
+        <v>21010020</v>
       </c>
       <c r="B127" s="55" t="n">
         <v>10</v>
@@ -5791,19 +5814,19 @@
         <v>2</v>
       </c>
       <c r="F127" s="55" t="n">
-        <v>2910019</v>
+        <v>2910020</v>
       </c>
       <c r="G127" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_19</t>
+          <t>Skeleton_Atlas_Weapon_Weapon_R_20</t>
         </is>
       </c>
       <c r="K127" s="55" t="n">
-        <v>21010019</v>
+        <v>21010020</v>
       </c>
       <c r="L127" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-结晶法杖</t>
+          <t>骷髅-武器-黑暗法杖</t>
         </is>
       </c>
       <c r="M127" s="55" t="inlineStr">
@@ -5814,34 +5837,31 @@
     </row>
     <row r="128">
       <c r="A128" s="55" t="n">
-        <v>21010020</v>
+        <v>30100001</v>
       </c>
       <c r="B128" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C128" s="55" t="n">
         <v>1</v>
       </c>
       <c r="D128" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E128" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" s="55" t="n">
-        <v>2910020</v>
+        <v>3020001</v>
       </c>
       <c r="G128" s="55" t="inlineStr">
         <is>
-          <t>Skeleton_Atlas_Weapon_Weapon_R_20</t>
+          <t>Slime_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K128" s="55" t="n">
-        <v>21010020</v>
+        <v>30100001</v>
       </c>
       <c r="L128" s="55" t="inlineStr">
         <is>
-          <t>骷髅-武器-黑暗法杖</t>
+          <t>史莱姆-帽子-1</t>
         </is>
       </c>
       <c r="M128" s="55" t="inlineStr">
@@ -5852,7 +5872,7 @@
     </row>
     <row r="129">
       <c r="A129" s="55" t="n">
-        <v>30100001</v>
+        <v>30100002</v>
       </c>
       <c r="B129" s="55" t="n">
         <v>1</v>
@@ -5864,30 +5884,25 @@
         <v>3</v>
       </c>
       <c r="F129" s="55" t="n">
-        <v>3020001</v>
+        <v>3020002</v>
       </c>
       <c r="G129" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_1</t>
+          <t>Slime_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K129" s="55" t="n">
-        <v>30100001</v>
+        <v>30100002</v>
       </c>
       <c r="L129" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-1</t>
-        </is>
-      </c>
-      <c r="M129" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>史莱姆-帽子-2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="55" t="n">
-        <v>30100002</v>
+        <v>30100003</v>
       </c>
       <c r="B130" s="55" t="n">
         <v>1</v>
@@ -5899,25 +5914,30 @@
         <v>3</v>
       </c>
       <c r="F130" s="55" t="n">
-        <v>3020002</v>
+        <v>3020003</v>
       </c>
       <c r="G130" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_2</t>
+          <t>Slime_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K130" s="55" t="n">
-        <v>30100002</v>
+        <v>30100003</v>
       </c>
       <c r="L130" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-2</t>
+          <t>史莱姆-帽子-3</t>
+        </is>
+      </c>
+      <c r="M130" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="55" t="n">
-        <v>30100003</v>
+        <v>30100004</v>
       </c>
       <c r="B131" s="55" t="n">
         <v>1</v>
@@ -5929,30 +5949,30 @@
         <v>3</v>
       </c>
       <c r="F131" s="55" t="n">
-        <v>3020003</v>
+        <v>3020004</v>
       </c>
       <c r="G131" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_3</t>
+          <t>Slime_Atlas_Hat_Hat_4</t>
         </is>
       </c>
       <c r="K131" s="55" t="n">
-        <v>30100003</v>
+        <v>30100004</v>
       </c>
       <c r="L131" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-3</t>
+          <t>史莱姆-帽子-4</t>
         </is>
       </c>
       <c r="M131" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="56">
       <c r="A132" s="55" t="n">
-        <v>30100004</v>
+        <v>30100005</v>
       </c>
       <c r="B132" s="55" t="n">
         <v>1</v>
@@ -5964,30 +5984,30 @@
         <v>3</v>
       </c>
       <c r="F132" s="55" t="n">
-        <v>3020004</v>
+        <v>3020005</v>
       </c>
       <c r="G132" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_4</t>
+          <t>Slime_Atlas_Hat_Hat_5</t>
         </is>
       </c>
       <c r="K132" s="55" t="n">
-        <v>30100004</v>
+        <v>30100005</v>
       </c>
       <c r="L132" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-4</t>
+          <t>史莱姆-帽子-5</t>
         </is>
       </c>
       <c r="M132" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="56">
       <c r="A133" s="55" t="n">
-        <v>30100005</v>
+        <v>30100006</v>
       </c>
       <c r="B133" s="55" t="n">
         <v>1</v>
@@ -5999,19 +6019,19 @@
         <v>3</v>
       </c>
       <c r="F133" s="55" t="n">
-        <v>3020005</v>
+        <v>3020006</v>
       </c>
       <c r="G133" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_5</t>
+          <t>Slime_Atlas_Hat_Hat_6</t>
         </is>
       </c>
       <c r="K133" s="55" t="n">
-        <v>30100005</v>
+        <v>30100006</v>
       </c>
       <c r="L133" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-5</t>
+          <t>史莱姆-帽子-6</t>
         </is>
       </c>
       <c r="M133" s="55" t="inlineStr">
@@ -6022,7 +6042,7 @@
     </row>
     <row r="134" ht="15" customHeight="1" s="56">
       <c r="A134" s="55" t="n">
-        <v>30100006</v>
+        <v>30100007</v>
       </c>
       <c r="B134" s="55" t="n">
         <v>1</v>
@@ -6034,30 +6054,25 @@
         <v>3</v>
       </c>
       <c r="F134" s="55" t="n">
-        <v>3020006</v>
+        <v>3020007</v>
       </c>
       <c r="G134" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_6</t>
+          <t>Slime_Atlas_Hat_Hat_7</t>
         </is>
       </c>
       <c r="K134" s="55" t="n">
-        <v>30100006</v>
+        <v>30100007</v>
       </c>
       <c r="L134" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-6</t>
-        </is>
-      </c>
-      <c r="M134" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>史莱姆-帽子-7</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="56">
       <c r="A135" s="55" t="n">
-        <v>30100007</v>
+        <v>30100008</v>
       </c>
       <c r="B135" s="55" t="n">
         <v>1</v>
@@ -6069,25 +6084,30 @@
         <v>3</v>
       </c>
       <c r="F135" s="55" t="n">
-        <v>3020007</v>
+        <v>3020008</v>
       </c>
       <c r="G135" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_7</t>
+          <t>Slime_Atlas_Hat_Hat_8</t>
         </is>
       </c>
       <c r="K135" s="55" t="n">
-        <v>30100007</v>
+        <v>30100008</v>
       </c>
       <c r="L135" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-7</t>
+          <t>史莱姆-帽子-8</t>
+        </is>
+      </c>
+      <c r="M135" s="55" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="56">
       <c r="A136" s="55" t="n">
-        <v>30100008</v>
+        <v>30100009</v>
       </c>
       <c r="B136" s="55" t="n">
         <v>1</v>
@@ -6099,30 +6119,30 @@
         <v>3</v>
       </c>
       <c r="F136" s="55" t="n">
-        <v>3020008</v>
+        <v>3020009</v>
       </c>
       <c r="G136" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_8</t>
+          <t>Slime_Atlas_Hat_Hat_9</t>
         </is>
       </c>
       <c r="K136" s="55" t="n">
-        <v>30100008</v>
+        <v>30100009</v>
       </c>
       <c r="L136" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-8</t>
+          <t>史莱姆-帽子-9</t>
         </is>
       </c>
       <c r="M136" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="56">
       <c r="A137" s="55" t="n">
-        <v>30100009</v>
+        <v>30100010</v>
       </c>
       <c r="B137" s="55" t="n">
         <v>1</v>
@@ -6134,30 +6154,30 @@
         <v>3</v>
       </c>
       <c r="F137" s="55" t="n">
-        <v>3020009</v>
+        <v>3020010</v>
       </c>
       <c r="G137" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_9</t>
+          <t>Slime_Atlas_Hat_Hat_10</t>
         </is>
       </c>
       <c r="K137" s="55" t="n">
-        <v>30100009</v>
+        <v>30100010</v>
       </c>
       <c r="L137" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-9</t>
+          <t>史莱姆-帽子-10</t>
         </is>
       </c>
       <c r="M137" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="56">
       <c r="A138" s="55" t="n">
-        <v>30100010</v>
+        <v>30100011</v>
       </c>
       <c r="B138" s="55" t="n">
         <v>1</v>
@@ -6169,19 +6189,19 @@
         <v>3</v>
       </c>
       <c r="F138" s="55" t="n">
-        <v>3020010</v>
+        <v>3020011</v>
       </c>
       <c r="G138" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_10</t>
+          <t>Slime_Atlas_Hat_Hat_11</t>
         </is>
       </c>
       <c r="K138" s="55" t="n">
-        <v>30100010</v>
+        <v>30100011</v>
       </c>
       <c r="L138" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-10</t>
+          <t>史莱姆-帽子-11</t>
         </is>
       </c>
       <c r="M138" s="55" t="inlineStr">
@@ -6192,7 +6212,7 @@
     </row>
     <row r="139" ht="15" customHeight="1" s="56">
       <c r="A139" s="55" t="n">
-        <v>30100011</v>
+        <v>30100012</v>
       </c>
       <c r="B139" s="55" t="n">
         <v>1</v>
@@ -6204,30 +6224,30 @@
         <v>3</v>
       </c>
       <c r="F139" s="55" t="n">
-        <v>3020011</v>
+        <v>3020012</v>
       </c>
       <c r="G139" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_11</t>
+          <t>Slime_Atlas_Hat_Hat_12</t>
         </is>
       </c>
       <c r="K139" s="55" t="n">
-        <v>30100011</v>
+        <v>30100012</v>
       </c>
       <c r="L139" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-11</t>
+          <t>史莱姆-帽子-12</t>
         </is>
       </c>
       <c r="M139" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="56">
       <c r="A140" s="55" t="n">
-        <v>30100012</v>
+        <v>30100013</v>
       </c>
       <c r="B140" s="55" t="n">
         <v>1</v>
@@ -6239,30 +6259,30 @@
         <v>3</v>
       </c>
       <c r="F140" s="55" t="n">
-        <v>3020012</v>
+        <v>3020013</v>
       </c>
       <c r="G140" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_12</t>
+          <t>Slime_Atlas_Hat_Hat_13</t>
         </is>
       </c>
       <c r="K140" s="55" t="n">
-        <v>30100012</v>
+        <v>30100013</v>
       </c>
       <c r="L140" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-12</t>
+          <t>史莱姆-帽子-13</t>
         </is>
       </c>
       <c r="M140" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="56">
       <c r="A141" s="55" t="n">
-        <v>30100013</v>
+        <v>30100014</v>
       </c>
       <c r="B141" s="55" t="n">
         <v>1</v>
@@ -6274,30 +6294,30 @@
         <v>3</v>
       </c>
       <c r="F141" s="55" t="n">
-        <v>3020013</v>
+        <v>3020014</v>
       </c>
       <c r="G141" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_13</t>
+          <t>Slime_Atlas_Hat_Hat_14</t>
         </is>
       </c>
       <c r="K141" s="55" t="n">
-        <v>30100013</v>
+        <v>30100014</v>
       </c>
       <c r="L141" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-13</t>
+          <t>史莱姆-帽子-14</t>
         </is>
       </c>
       <c r="M141" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="56">
       <c r="A142" s="55" t="n">
-        <v>30100014</v>
+        <v>30100015</v>
       </c>
       <c r="B142" s="55" t="n">
         <v>1</v>
@@ -6309,19 +6329,19 @@
         <v>3</v>
       </c>
       <c r="F142" s="55" t="n">
-        <v>3020014</v>
+        <v>3020015</v>
       </c>
       <c r="G142" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_14</t>
+          <t>Slime_Atlas_Hat_Hat_15</t>
         </is>
       </c>
       <c r="K142" s="55" t="n">
-        <v>30100014</v>
+        <v>30100015</v>
       </c>
       <c r="L142" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-14</t>
+          <t>史莱姆-帽子-15</t>
         </is>
       </c>
       <c r="M142" s="55" t="inlineStr">
@@ -6332,7 +6352,7 @@
     </row>
     <row r="143">
       <c r="A143" s="55" t="n">
-        <v>30100015</v>
+        <v>30100016</v>
       </c>
       <c r="B143" s="55" t="n">
         <v>1</v>
@@ -6344,30 +6364,30 @@
         <v>3</v>
       </c>
       <c r="F143" s="55" t="n">
-        <v>3020015</v>
+        <v>3020016</v>
       </c>
       <c r="G143" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_15</t>
+          <t>Slime_Atlas_Hat_Hat_16</t>
         </is>
       </c>
       <c r="K143" s="55" t="n">
-        <v>30100015</v>
+        <v>30100016</v>
       </c>
       <c r="L143" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-15</t>
+          <t>史莱姆-帽子-16</t>
         </is>
       </c>
       <c r="M143" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="55" t="n">
-        <v>30100016</v>
+        <v>30100017</v>
       </c>
       <c r="B144" s="55" t="n">
         <v>1</v>
@@ -6379,19 +6399,19 @@
         <v>3</v>
       </c>
       <c r="F144" s="55" t="n">
-        <v>3020016</v>
+        <v>3020017</v>
       </c>
       <c r="G144" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_16</t>
+          <t>Slime_Atlas_Hat_Hat_17</t>
         </is>
       </c>
       <c r="K144" s="55" t="n">
-        <v>30100016</v>
+        <v>30100017</v>
       </c>
       <c r="L144" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-16</t>
+          <t>史莱姆-帽子-17</t>
         </is>
       </c>
       <c r="M144" s="55" t="inlineStr">
@@ -6402,7 +6422,7 @@
     </row>
     <row r="145">
       <c r="A145" s="55" t="n">
-        <v>30100017</v>
+        <v>30100018</v>
       </c>
       <c r="B145" s="55" t="n">
         <v>1</v>
@@ -6414,19 +6434,19 @@
         <v>3</v>
       </c>
       <c r="F145" s="55" t="n">
-        <v>3020017</v>
+        <v>3020018</v>
       </c>
       <c r="G145" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_17</t>
+          <t>Slime_Atlas_Hat_Hat_18</t>
         </is>
       </c>
       <c r="K145" s="55" t="n">
-        <v>30100017</v>
+        <v>30100018</v>
       </c>
       <c r="L145" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-17</t>
+          <t>史莱姆-帽子-18</t>
         </is>
       </c>
       <c r="M145" s="55" t="inlineStr">
@@ -6437,7 +6457,7 @@
     </row>
     <row r="146" ht="12" customHeight="1" s="56">
       <c r="A146" s="55" t="n">
-        <v>30100018</v>
+        <v>30100019</v>
       </c>
       <c r="B146" s="55" t="n">
         <v>1</v>
@@ -6449,19 +6469,19 @@
         <v>3</v>
       </c>
       <c r="F146" s="55" t="n">
-        <v>3020018</v>
+        <v>3020019</v>
       </c>
       <c r="G146" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_18</t>
+          <t>Slime_Atlas_Hat_Hat_19</t>
         </is>
       </c>
       <c r="K146" s="55" t="n">
-        <v>30100018</v>
+        <v>30100019</v>
       </c>
       <c r="L146" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-18</t>
+          <t>史莱姆-帽子-19</t>
         </is>
       </c>
       <c r="M146" s="55" t="inlineStr">
@@ -6472,7 +6492,7 @@
     </row>
     <row r="147">
       <c r="A147" s="55" t="n">
-        <v>30100019</v>
+        <v>30100020</v>
       </c>
       <c r="B147" s="55" t="n">
         <v>1</v>
@@ -6484,19 +6504,19 @@
         <v>3</v>
       </c>
       <c r="F147" s="55" t="n">
-        <v>3020019</v>
+        <v>3020020</v>
       </c>
       <c r="G147" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_19</t>
+          <t>Slime_Atlas_Hat_Hat_20</t>
         </is>
       </c>
       <c r="K147" s="55" t="n">
-        <v>30100019</v>
+        <v>30100020</v>
       </c>
       <c r="L147" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-19</t>
+          <t>史莱姆-帽子-20</t>
         </is>
       </c>
       <c r="M147" s="55" t="inlineStr">
@@ -6507,7 +6527,7 @@
     </row>
     <row r="148">
       <c r="A148" s="55" t="n">
-        <v>30100020</v>
+        <v>40100001</v>
       </c>
       <c r="B148" s="55" t="n">
         <v>1</v>
@@ -6516,36 +6536,36 @@
         <v>1</v>
       </c>
       <c r="E148" s="55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F148" s="55" t="n">
-        <v>3020020</v>
+        <v>4500003</v>
       </c>
       <c r="G148" s="55" t="inlineStr">
         <is>
-          <t>Slime_Atlas_Hat_Hat_20</t>
+          <t>Succubus_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K148" s="55" t="n">
-        <v>30100020</v>
+        <v>40100001</v>
       </c>
       <c r="L148" s="55" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-20</t>
+          <t>修女帽</t>
         </is>
       </c>
       <c r="M148" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="55" t="n">
-        <v>40100001</v>
+        <v>40200001</v>
       </c>
       <c r="B149" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D149" s="55" t="n">
         <v>1</v>
@@ -6554,30 +6574,25 @@
         <v>4</v>
       </c>
       <c r="F149" s="55" t="n">
-        <v>4500003</v>
+        <v>4510001</v>
       </c>
       <c r="G149" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Hat_Hat_3</t>
+          <t>Succubus_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K149" s="55" t="n">
-        <v>40100001</v>
+        <v>40200001</v>
       </c>
       <c r="L149" s="55" t="inlineStr">
         <is>
-          <t>修女帽</t>
-        </is>
-      </c>
-      <c r="M149" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>粉色胸罩</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="55" t="n">
-        <v>40200001</v>
+        <v>40200002</v>
       </c>
       <c r="B150" s="55" t="n">
         <v>2</v>
@@ -6589,25 +6604,25 @@
         <v>4</v>
       </c>
       <c r="F150" s="55" t="n">
-        <v>4510001</v>
+        <v>4510002</v>
       </c>
       <c r="G150" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_1</t>
+          <t>Succubus_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K150" s="55" t="n">
-        <v>40200001</v>
+        <v>40200002</v>
       </c>
       <c r="L150" s="55" t="inlineStr">
         <is>
-          <t>粉色胸罩</t>
+          <t>红色胸罩</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="55" t="n">
-        <v>40200002</v>
+        <v>40200003</v>
       </c>
       <c r="B151" s="55" t="n">
         <v>2</v>
@@ -6619,25 +6634,30 @@
         <v>4</v>
       </c>
       <c r="F151" s="55" t="n">
-        <v>4510002</v>
+        <v>4510003</v>
       </c>
       <c r="G151" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_2</t>
+          <t>Succubus_Atlas_Clothes_Clothes_3</t>
         </is>
       </c>
       <c r="K151" s="55" t="n">
-        <v>40200002</v>
+        <v>40200003</v>
       </c>
       <c r="L151" s="55" t="inlineStr">
         <is>
-          <t>红色胸罩</t>
+          <t>修女服</t>
+        </is>
+      </c>
+      <c r="M151" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="55" t="n">
-        <v>40200003</v>
+        <v>40200004</v>
       </c>
       <c r="B152" s="55" t="n">
         <v>2</v>
@@ -6649,30 +6669,30 @@
         <v>4</v>
       </c>
       <c r="F152" s="55" t="n">
-        <v>4510003</v>
+        <v>4510004</v>
       </c>
       <c r="G152" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_3</t>
+          <t>Succubus_Atlas_Clothes_Clothes_4</t>
         </is>
       </c>
       <c r="K152" s="55" t="n">
-        <v>40200003</v>
+        <v>40200004</v>
       </c>
       <c r="L152" s="55" t="inlineStr">
         <is>
-          <t>修女服</t>
+          <t>魔女连体衣</t>
         </is>
       </c>
       <c r="M152" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="55" t="n">
-        <v>40200004</v>
+        <v>40200005</v>
       </c>
       <c r="B153" s="55" t="n">
         <v>2</v>
@@ -6684,30 +6704,30 @@
         <v>4</v>
       </c>
       <c r="F153" s="55" t="n">
-        <v>4510004</v>
+        <v>4510005</v>
       </c>
       <c r="G153" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_4</t>
+          <t>Succubus_Atlas_Clothes_Clothes_5</t>
         </is>
       </c>
       <c r="K153" s="55" t="n">
-        <v>40200004</v>
+        <v>40200005</v>
       </c>
       <c r="L153" s="55" t="inlineStr">
         <is>
-          <t>魔女连体衣</t>
+          <t>丝带</t>
         </is>
       </c>
       <c r="M153" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="55" t="n">
-        <v>40200005</v>
+        <v>40200006</v>
       </c>
       <c r="B154" s="55" t="n">
         <v>2</v>
@@ -6719,33 +6739,33 @@
         <v>4</v>
       </c>
       <c r="F154" s="55" t="n">
-        <v>4510005</v>
+        <v>4510006</v>
       </c>
       <c r="G154" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_5</t>
+          <t>Succubus_Atlas_Clothes_Clothes_6</t>
         </is>
       </c>
       <c r="K154" s="55" t="n">
-        <v>40200005</v>
+        <v>40200006</v>
       </c>
       <c r="L154" s="55" t="inlineStr">
         <is>
-          <t>丝带</t>
+          <t>白色丝带</t>
         </is>
       </c>
       <c r="M154" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="55" t="n">
-        <v>40200006</v>
+        <v>40300001</v>
       </c>
       <c r="B155" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D155" s="55" t="n">
         <v>1</v>
@@ -6754,30 +6774,25 @@
         <v>4</v>
       </c>
       <c r="F155" s="55" t="n">
-        <v>4510006</v>
+        <v>4520001</v>
       </c>
       <c r="G155" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Clothes_Clothes_6</t>
+          <t>Succubus_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K155" s="55" t="n">
-        <v>40200006</v>
+        <v>40300001</v>
       </c>
       <c r="L155" s="55" t="inlineStr">
         <is>
-          <t>白色丝带</t>
-        </is>
-      </c>
-      <c r="M155" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>粉色丝袜裤</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="55" t="n">
-        <v>40300001</v>
+        <v>40300002</v>
       </c>
       <c r="B156" s="55" t="n">
         <v>3</v>
@@ -6789,25 +6804,25 @@
         <v>4</v>
       </c>
       <c r="F156" s="55" t="n">
-        <v>4520001</v>
+        <v>4520002</v>
       </c>
       <c r="G156" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Pants_Pants_1</t>
+          <t>Succubus_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K156" s="55" t="n">
-        <v>40300001</v>
+        <v>40300002</v>
       </c>
       <c r="L156" s="55" t="inlineStr">
         <is>
-          <t>粉色丝袜裤</t>
+          <t>红色内裤</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="55" t="n">
-        <v>40300002</v>
+        <v>40300003</v>
       </c>
       <c r="B157" s="55" t="n">
         <v>3</v>
@@ -6819,25 +6834,30 @@
         <v>4</v>
       </c>
       <c r="F157" s="55" t="n">
-        <v>4520002</v>
+        <v>4520003</v>
       </c>
       <c r="G157" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Pants_Pants_2</t>
+          <t>Succubus_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K157" s="55" t="n">
-        <v>40300002</v>
+        <v>40300003</v>
       </c>
       <c r="L157" s="55" t="inlineStr">
         <is>
-          <t>红色内裤</t>
+          <t>修女裤</t>
+        </is>
+      </c>
+      <c r="M157" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="55" t="n">
-        <v>40300003</v>
+        <v>40300004</v>
       </c>
       <c r="B158" s="55" t="n">
         <v>3</v>
@@ -6849,33 +6869,36 @@
         <v>4</v>
       </c>
       <c r="F158" s="55" t="n">
-        <v>4520003</v>
+        <v>4520004</v>
       </c>
       <c r="G158" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Pants_Pants_3</t>
+          <t>Succubus_Atlas_Pants_Pants_4</t>
         </is>
       </c>
       <c r="K158" s="55" t="n">
-        <v>40300003</v>
+        <v>40300004</v>
       </c>
       <c r="L158" s="55" t="inlineStr">
         <is>
-          <t>修女裤</t>
+          <t>魔女连体裤</t>
         </is>
       </c>
       <c r="M158" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,6</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="55" t="n">
-        <v>40300004</v>
+        <v>41000001</v>
       </c>
       <c r="B159" s="55" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C159" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="D159" s="55" t="n">
         <v>1</v>
@@ -6884,30 +6907,30 @@
         <v>4</v>
       </c>
       <c r="F159" s="55" t="n">
-        <v>4520004</v>
+        <v>4900001</v>
       </c>
       <c r="G159" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Pants_Pants_4</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_1</t>
         </is>
       </c>
       <c r="K159" s="55" t="n">
-        <v>40300004</v>
+        <v>41000001</v>
       </c>
       <c r="L159" s="55" t="inlineStr">
         <is>
-          <t>魔女连体裤</t>
+          <t>魔力镰刀</t>
         </is>
       </c>
       <c r="M159" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="55" t="n">
-        <v>41000001</v>
+        <v>41000002</v>
       </c>
       <c r="B160" s="55" t="n">
         <v>10</v>
@@ -6922,30 +6945,25 @@
         <v>4</v>
       </c>
       <c r="F160" s="55" t="n">
-        <v>4900001</v>
+        <v>4900002</v>
       </c>
       <c r="G160" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_1</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_2</t>
         </is>
       </c>
       <c r="K160" s="55" t="n">
-        <v>41000001</v>
+        <v>41000002</v>
       </c>
       <c r="L160" s="55" t="inlineStr">
         <is>
-          <t>魔力镰刀</t>
-        </is>
-      </c>
-      <c r="M160" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>木制镰刀</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="55" t="n">
-        <v>41000002</v>
+        <v>41000003</v>
       </c>
       <c r="B161" s="55" t="n">
         <v>10</v>
@@ -6960,25 +6978,30 @@
         <v>4</v>
       </c>
       <c r="F161" s="55" t="n">
-        <v>4900002</v>
+        <v>4900003</v>
       </c>
       <c r="G161" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_2</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_3</t>
         </is>
       </c>
       <c r="K161" s="55" t="n">
-        <v>41000002</v>
+        <v>41000003</v>
       </c>
       <c r="L161" s="55" t="inlineStr">
         <is>
-          <t>木制镰刀</t>
+          <t>鹦鹉镰刀</t>
+        </is>
+      </c>
+      <c r="M161" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="55" t="n">
-        <v>41000003</v>
+        <v>41000004</v>
       </c>
       <c r="B162" s="55" t="n">
         <v>10</v>
@@ -6993,19 +7016,19 @@
         <v>4</v>
       </c>
       <c r="F162" s="55" t="n">
-        <v>4900003</v>
+        <v>4900004</v>
       </c>
       <c r="G162" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_3</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_4</t>
         </is>
       </c>
       <c r="K162" s="55" t="n">
-        <v>41000003</v>
+        <v>41000004</v>
       </c>
       <c r="L162" s="55" t="inlineStr">
         <is>
-          <t>鹦鹉镰刀</t>
+          <t>金制镰刀</t>
         </is>
       </c>
       <c r="M162" s="55" t="inlineStr">
@@ -7016,7 +7039,7 @@
     </row>
     <row r="163">
       <c r="A163" s="55" t="n">
-        <v>41000004</v>
+        <v>41000005</v>
       </c>
       <c r="B163" s="55" t="n">
         <v>10</v>
@@ -7031,19 +7054,19 @@
         <v>4</v>
       </c>
       <c r="F163" s="55" t="n">
-        <v>4900004</v>
+        <v>4900005</v>
       </c>
       <c r="G163" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_4</t>
+          <t>Succubus_Atlas_Weapon_Weapon_L_5</t>
         </is>
       </c>
       <c r="K163" s="55" t="n">
-        <v>41000004</v>
+        <v>41000005</v>
       </c>
       <c r="L163" s="55" t="inlineStr">
         <is>
-          <t>金制镰刀</t>
+          <t>剧毒镰刀</t>
         </is>
       </c>
       <c r="M163" s="55" t="inlineStr">
@@ -7054,34 +7077,31 @@
     </row>
     <row r="164">
       <c r="A164" s="55" t="n">
-        <v>41000005</v>
+        <v>50100001</v>
       </c>
       <c r="B164" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C164" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D164" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E164" s="55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F164" s="55" t="n">
-        <v>4900005</v>
+        <v>5500001</v>
       </c>
       <c r="G164" s="55" t="inlineStr">
         <is>
-          <t>Succubus_Atlas_Weapon_Weapon_L_5</t>
+          <t>Minotaur_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K164" s="55" t="n">
-        <v>41000005</v>
+        <v>50100001</v>
       </c>
       <c r="L164" s="55" t="inlineStr">
         <is>
-          <t>剧毒镰刀</t>
+          <t>红色头巾</t>
         </is>
       </c>
       <c r="M164" s="55" t="inlineStr">
@@ -7092,7 +7112,7 @@
     </row>
     <row r="165">
       <c r="A165" s="55" t="n">
-        <v>50100001</v>
+        <v>50100002</v>
       </c>
       <c r="B165" s="55" t="n">
         <v>1</v>
@@ -7104,19 +7124,19 @@
         <v>5</v>
       </c>
       <c r="F165" s="55" t="n">
-        <v>5500001</v>
+        <v>5500002</v>
       </c>
       <c r="G165" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Hat_Hat_1</t>
+          <t>Minotaur_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K165" s="55" t="n">
-        <v>50100001</v>
+        <v>50100002</v>
       </c>
       <c r="L165" s="55" t="inlineStr">
         <is>
-          <t>红色头巾</t>
+          <t>小花</t>
         </is>
       </c>
       <c r="M165" s="55" t="inlineStr">
@@ -7127,7 +7147,7 @@
     </row>
     <row r="166">
       <c r="A166" s="55" t="n">
-        <v>50100002</v>
+        <v>50100003</v>
       </c>
       <c r="B166" s="55" t="n">
         <v>1</v>
@@ -7139,19 +7159,19 @@
         <v>5</v>
       </c>
       <c r="F166" s="55" t="n">
-        <v>5500002</v>
+        <v>5500003</v>
       </c>
       <c r="G166" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Hat_Hat_2</t>
+          <t>Minotaur_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K166" s="55" t="n">
-        <v>50100002</v>
+        <v>50100003</v>
       </c>
       <c r="L166" s="55" t="inlineStr">
         <is>
-          <t>小花</t>
+          <t>蘑菇</t>
         </is>
       </c>
       <c r="M166" s="55" t="inlineStr">
@@ -7162,10 +7182,10 @@
     </row>
     <row r="167" ht="12" customHeight="1" s="56">
       <c r="A167" s="55" t="n">
-        <v>50100003</v>
+        <v>50200001</v>
       </c>
       <c r="B167" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D167" s="55" t="n">
         <v>1</v>
@@ -7174,19 +7194,19 @@
         <v>5</v>
       </c>
       <c r="F167" s="55" t="n">
-        <v>5500003</v>
+        <v>5510001</v>
       </c>
       <c r="G167" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Hat_Hat_3</t>
+          <t>Minotaur_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K167" s="55" t="n">
-        <v>50100003</v>
+        <v>50200001</v>
       </c>
       <c r="L167" s="55" t="inlineStr">
         <is>
-          <t>蘑菇</t>
+          <t>银制盔甲</t>
         </is>
       </c>
       <c r="M167" s="55" t="inlineStr">
@@ -7197,7 +7217,7 @@
     </row>
     <row r="168">
       <c r="A168" s="55" t="n">
-        <v>50200001</v>
+        <v>50200002</v>
       </c>
       <c r="B168" s="55" t="n">
         <v>2</v>
@@ -7209,30 +7229,30 @@
         <v>5</v>
       </c>
       <c r="F168" s="55" t="n">
-        <v>5510001</v>
+        <v>5510002</v>
       </c>
       <c r="G168" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Clothes_Clothes_1</t>
+          <t>Minotaur_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K168" s="55" t="n">
-        <v>50200001</v>
+        <v>50200002</v>
       </c>
       <c r="L168" s="55" t="inlineStr">
         <is>
-          <t>银制盔甲</t>
+          <t>皮甲</t>
         </is>
       </c>
       <c r="M168" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="55" t="n">
-        <v>50200002</v>
+        <v>50200003</v>
       </c>
       <c r="B169" s="55" t="n">
         <v>2</v>
@@ -7244,19 +7264,19 @@
         <v>5</v>
       </c>
       <c r="F169" s="55" t="n">
-        <v>5510002</v>
+        <v>5510003</v>
       </c>
       <c r="G169" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Clothes_Clothes_2</t>
+          <t>Minotaur_Atlas_Clothes_Clothes_3</t>
         </is>
       </c>
       <c r="K169" s="55" t="n">
-        <v>50200002</v>
+        <v>50200003</v>
       </c>
       <c r="L169" s="55" t="inlineStr">
         <is>
-          <t>皮甲</t>
+          <t>皮带胸甲</t>
         </is>
       </c>
       <c r="M169" s="55" t="inlineStr">
@@ -7267,10 +7287,10 @@
     </row>
     <row r="170">
       <c r="A170" s="55" t="n">
-        <v>50200003</v>
+        <v>50300001</v>
       </c>
       <c r="B170" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D170" s="55" t="n">
         <v>1</v>
@@ -7279,30 +7299,30 @@
         <v>5</v>
       </c>
       <c r="F170" s="55" t="n">
-        <v>5510003</v>
+        <v>5520001</v>
       </c>
       <c r="G170" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Clothes_Clothes_3</t>
+          <t>Minotaur_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K170" s="55" t="n">
-        <v>50200003</v>
+        <v>50300001</v>
       </c>
       <c r="L170" s="55" t="inlineStr">
         <is>
-          <t>皮带胸甲</t>
+          <t>骷髅腰带</t>
         </is>
       </c>
       <c r="M170" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="55" t="n">
-        <v>50300001</v>
+        <v>50300002</v>
       </c>
       <c r="B171" s="55" t="n">
         <v>3</v>
@@ -7314,19 +7334,19 @@
         <v>5</v>
       </c>
       <c r="F171" s="55" t="n">
-        <v>5520001</v>
+        <v>5520002</v>
       </c>
       <c r="G171" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Pants_Pants_1</t>
+          <t>Minotaur_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K171" s="55" t="n">
-        <v>50300001</v>
+        <v>50300002</v>
       </c>
       <c r="L171" s="55" t="inlineStr">
         <is>
-          <t>骷髅腰带</t>
+          <t>红色铁制</t>
         </is>
       </c>
       <c r="M171" s="55" t="inlineStr">
@@ -7337,10 +7357,10 @@
     </row>
     <row r="172">
       <c r="A172" s="55" t="n">
-        <v>50300002</v>
+        <v>50500001</v>
       </c>
       <c r="B172" s="55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D172" s="55" t="n">
         <v>1</v>
@@ -7349,30 +7369,30 @@
         <v>5</v>
       </c>
       <c r="F172" s="55" t="n">
-        <v>5520002</v>
+        <v>5090001</v>
       </c>
       <c r="G172" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Pants_Pants_2</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_1</t>
         </is>
       </c>
       <c r="K172" s="55" t="n">
-        <v>50300002</v>
+        <v>50500001</v>
       </c>
       <c r="L172" s="55" t="inlineStr">
         <is>
-          <t>红色铁制</t>
+          <t>铁制鼻环</t>
         </is>
       </c>
       <c r="M172" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="55" t="n">
-        <v>50500001</v>
+        <v>50500002</v>
       </c>
       <c r="B173" s="55" t="n">
         <v>5</v>
@@ -7384,19 +7404,19 @@
         <v>5</v>
       </c>
       <c r="F173" s="55" t="n">
-        <v>5090001</v>
+        <v>5090002</v>
       </c>
       <c r="G173" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_1</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_2</t>
         </is>
       </c>
       <c r="K173" s="55" t="n">
-        <v>50500001</v>
+        <v>50500002</v>
       </c>
       <c r="L173" s="55" t="inlineStr">
         <is>
-          <t>铁制鼻环</t>
+          <t>反向铁制鼻环</t>
         </is>
       </c>
       <c r="M173" s="55" t="inlineStr">
@@ -7407,7 +7427,7 @@
     </row>
     <row r="174">
       <c r="A174" s="55" t="n">
-        <v>50500002</v>
+        <v>50500003</v>
       </c>
       <c r="B174" s="55" t="n">
         <v>5</v>
@@ -7419,30 +7439,25 @@
         <v>5</v>
       </c>
       <c r="F174" s="55" t="n">
-        <v>5090002</v>
+        <v>5090003</v>
       </c>
       <c r="G174" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_2</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_3</t>
         </is>
       </c>
       <c r="K174" s="55" t="n">
-        <v>50500002</v>
+        <v>50500003</v>
       </c>
       <c r="L174" s="55" t="inlineStr">
         <is>
-          <t>反向铁制鼻环</t>
-        </is>
-      </c>
-      <c r="M174" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>小号铁制鼻环</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="55" t="n">
-        <v>50500003</v>
+        <v>50500004</v>
       </c>
       <c r="B175" s="55" t="n">
         <v>5</v>
@@ -7454,25 +7469,30 @@
         <v>5</v>
       </c>
       <c r="F175" s="55" t="n">
-        <v>5090003</v>
+        <v>5090004</v>
       </c>
       <c r="G175" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_3</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_4</t>
         </is>
       </c>
       <c r="K175" s="55" t="n">
-        <v>50500003</v>
+        <v>50500004</v>
       </c>
       <c r="L175" s="55" t="inlineStr">
         <is>
-          <t>小号铁制鼻环</t>
+          <t>金制鼻环</t>
+        </is>
+      </c>
+      <c r="M175" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="55" t="n">
-        <v>50500004</v>
+        <v>50500005</v>
       </c>
       <c r="B176" s="55" t="n">
         <v>5</v>
@@ -7484,19 +7504,19 @@
         <v>5</v>
       </c>
       <c r="F176" s="55" t="n">
-        <v>5090004</v>
+        <v>5090005</v>
       </c>
       <c r="G176" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_4</t>
+          <t>Minotaur_Atlas_NoseRing_NoseRing_5</t>
         </is>
       </c>
       <c r="K176" s="55" t="n">
-        <v>50500004</v>
+        <v>50500005</v>
       </c>
       <c r="L176" s="55" t="inlineStr">
         <is>
-          <t>金制鼻环</t>
+          <t>连环鼻环</t>
         </is>
       </c>
       <c r="M176" s="55" t="inlineStr">
@@ -7507,10 +7527,13 @@
     </row>
     <row r="177">
       <c r="A177" s="55" t="n">
-        <v>50500005</v>
+        <v>51010001</v>
       </c>
       <c r="B177" s="55" t="n">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="C177" s="55" t="n">
+        <v>8</v>
       </c>
       <c r="D177" s="55" t="n">
         <v>1</v>
@@ -7519,30 +7542,35 @@
         <v>5</v>
       </c>
       <c r="F177" s="55" t="n">
-        <v>5090005</v>
+        <v>5910001</v>
       </c>
       <c r="G177" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_NoseRing_NoseRing_5</t>
+          <t>Minotaur_Atlas_Weapon_Weapon_R_1</t>
+        </is>
+      </c>
+      <c r="I177" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
         </is>
       </c>
       <c r="K177" s="55" t="n">
-        <v>50500005</v>
+        <v>51010001</v>
       </c>
       <c r="L177" s="55" t="inlineStr">
         <is>
-          <t>连环鼻环</t>
+          <t>石头</t>
         </is>
       </c>
       <c r="M177" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="55" t="n">
-        <v>51010001</v>
+        <v>51010002</v>
       </c>
       <c r="B178" s="55" t="n">
         <v>10</v>
@@ -7557,35 +7585,35 @@
         <v>5</v>
       </c>
       <c r="F178" s="55" t="n">
-        <v>5910001</v>
+        <v>5910002</v>
       </c>
       <c r="G178" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Weapon_Weapon_R_1</t>
+          <t>Minotaur_Atlas_Weapon_Weapon_R_2</t>
         </is>
       </c>
       <c r="I178" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
         </is>
       </c>
       <c r="K178" s="55" t="n">
-        <v>51010001</v>
+        <v>51010002</v>
       </c>
       <c r="L178" s="55" t="inlineStr">
         <is>
-          <t>石头</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="M178" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="55" t="n">
-        <v>51010002</v>
+        <v>51010003</v>
       </c>
       <c r="B179" s="55" t="n">
         <v>10</v>
@@ -7600,67 +7628,59 @@
         <v>5</v>
       </c>
       <c r="F179" s="55" t="n">
-        <v>5910002</v>
+        <v>5910003</v>
       </c>
       <c r="G179" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Weapon_Weapon_R_2</t>
+          <t>Minotaur_Atlas_Weapon_Weapon_R_3</t>
         </is>
       </c>
       <c r="I179" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
         </is>
       </c>
       <c r="K179" s="55" t="n">
-        <v>51010002</v>
+        <v>51010003</v>
       </c>
       <c r="L179" s="55" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>宝箱</t>
         </is>
       </c>
       <c r="M179" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="55" t="n">
-        <v>51010003</v>
+        <v>60100001</v>
       </c>
       <c r="B180" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C180" s="55" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D180" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E180" s="55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F180" s="55" t="n">
-        <v>5910003</v>
+        <v>6500001</v>
       </c>
       <c r="G180" s="55" t="inlineStr">
         <is>
-          <t>Minotaur_Atlas_Weapon_Weapon_R_3</t>
-        </is>
-      </c>
-      <c r="I180" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+          <t>Goblin_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K180" s="55" t="n">
-        <v>51010003</v>
+        <v>60100001</v>
       </c>
       <c r="L180" s="55" t="inlineStr">
         <is>
-          <t>宝箱</t>
+          <t>木制面具</t>
         </is>
       </c>
       <c r="M180" s="55" t="inlineStr">
@@ -7671,7 +7691,7 @@
     </row>
     <row r="181">
       <c r="A181" s="55" t="n">
-        <v>60100001</v>
+        <v>60100002</v>
       </c>
       <c r="B181" s="55" t="n">
         <v>1</v>
@@ -7683,30 +7703,25 @@
         <v>6</v>
       </c>
       <c r="F181" s="55" t="n">
-        <v>6500001</v>
+        <v>6500002</v>
       </c>
       <c r="G181" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_1</t>
+          <t>Goblin_Atlas_Hat_Hat_2</t>
         </is>
       </c>
       <c r="K181" s="55" t="n">
-        <v>60100001</v>
+        <v>60100002</v>
       </c>
       <c r="L181" s="55" t="inlineStr">
         <is>
-          <t>木制面具</t>
-        </is>
-      </c>
-      <c r="M181" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>头巾</t>
         </is>
       </c>
     </row>
     <row r="182" ht="12" customHeight="1" s="56">
       <c r="A182" s="55" t="n">
-        <v>60100002</v>
+        <v>60100003</v>
       </c>
       <c r="B182" s="55" t="n">
         <v>1</v>
@@ -7718,25 +7733,30 @@
         <v>6</v>
       </c>
       <c r="F182" s="55" t="n">
-        <v>6500002</v>
+        <v>6500003</v>
       </c>
       <c r="G182" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_2</t>
+          <t>Goblin_Atlas_Hat_Hat_3</t>
         </is>
       </c>
       <c r="K182" s="55" t="n">
-        <v>60100002</v>
+        <v>60100003</v>
       </c>
       <c r="L182" s="55" t="inlineStr">
         <is>
-          <t>头巾</t>
+          <t>金耳环</t>
+        </is>
+      </c>
+      <c r="M182" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="183" ht="12" customHeight="1" s="56">
       <c r="A183" s="55" t="n">
-        <v>60100003</v>
+        <v>60100004</v>
       </c>
       <c r="B183" s="55" t="n">
         <v>1</v>
@@ -7748,19 +7768,19 @@
         <v>6</v>
       </c>
       <c r="F183" s="55" t="n">
-        <v>6500003</v>
+        <v>6500004</v>
       </c>
       <c r="G183" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_3</t>
+          <t>Goblin_Atlas_Hat_Hat_4</t>
         </is>
       </c>
       <c r="K183" s="55" t="n">
-        <v>60100003</v>
+        <v>60100004</v>
       </c>
       <c r="L183" s="55" t="inlineStr">
         <is>
-          <t>金耳环</t>
+          <t>红色头巾</t>
         </is>
       </c>
       <c r="M183" s="55" t="inlineStr">
@@ -7771,7 +7791,7 @@
     </row>
     <row r="184" ht="12" customHeight="1" s="56">
       <c r="A184" s="55" t="n">
-        <v>60100004</v>
+        <v>60100005</v>
       </c>
       <c r="B184" s="55" t="n">
         <v>1</v>
@@ -7783,30 +7803,30 @@
         <v>6</v>
       </c>
       <c r="F184" s="55" t="n">
-        <v>6500004</v>
+        <v>6500005</v>
       </c>
       <c r="G184" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_4</t>
+          <t>Goblin_Atlas_Hat_Hat_5</t>
         </is>
       </c>
       <c r="K184" s="55" t="n">
-        <v>60100004</v>
+        <v>60100005</v>
       </c>
       <c r="L184" s="55" t="inlineStr">
         <is>
-          <t>红色头巾</t>
+          <t>蓝色头巾</t>
         </is>
       </c>
       <c r="M184" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="185" ht="12" customHeight="1" s="56">
       <c r="A185" s="55" t="n">
-        <v>60100005</v>
+        <v>60100006</v>
       </c>
       <c r="B185" s="55" t="n">
         <v>1</v>
@@ -7818,30 +7838,25 @@
         <v>6</v>
       </c>
       <c r="F185" s="55" t="n">
-        <v>6500005</v>
+        <v>6500006</v>
       </c>
       <c r="G185" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_5</t>
+          <t>Goblin_Atlas_Hat_Hat_6</t>
         </is>
       </c>
       <c r="K185" s="55" t="n">
-        <v>60100005</v>
+        <v>60100006</v>
       </c>
       <c r="L185" s="55" t="inlineStr">
         <is>
-          <t>蓝色头巾</t>
-        </is>
-      </c>
-      <c r="M185" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>布头罩</t>
         </is>
       </c>
     </row>
     <row r="186" ht="12" customHeight="1" s="56">
       <c r="A186" s="55" t="n">
-        <v>60100006</v>
+        <v>60100007</v>
       </c>
       <c r="B186" s="55" t="n">
         <v>1</v>
@@ -7853,25 +7868,30 @@
         <v>6</v>
       </c>
       <c r="F186" s="55" t="n">
-        <v>6500006</v>
+        <v>6500007</v>
       </c>
       <c r="G186" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_6</t>
+          <t>Goblin_Atlas_Hat_Hat_7</t>
         </is>
       </c>
       <c r="K186" s="55" t="n">
-        <v>60100006</v>
+        <v>60100007</v>
       </c>
       <c r="L186" s="55" t="inlineStr">
         <is>
-          <t>布头罩</t>
+          <t>红色羽毛帽</t>
+        </is>
+      </c>
+      <c r="M186" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="187" ht="12" customHeight="1" s="56">
       <c r="A187" s="55" t="n">
-        <v>60100007</v>
+        <v>60100008</v>
       </c>
       <c r="B187" s="55" t="n">
         <v>1</v>
@@ -7883,19 +7903,19 @@
         <v>6</v>
       </c>
       <c r="F187" s="55" t="n">
-        <v>6500007</v>
+        <v>6500008</v>
       </c>
       <c r="G187" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_7</t>
+          <t>Goblin_Atlas_Hat_Hat_8</t>
         </is>
       </c>
       <c r="K187" s="55" t="n">
-        <v>60100007</v>
+        <v>60100008</v>
       </c>
       <c r="L187" s="55" t="inlineStr">
         <is>
-          <t>红色羽毛帽</t>
+          <t>熊头帽</t>
         </is>
       </c>
       <c r="M187" s="55" t="inlineStr">
@@ -7906,7 +7926,7 @@
     </row>
     <row r="188" ht="12" customHeight="1" s="56">
       <c r="A188" s="55" t="n">
-        <v>60100008</v>
+        <v>60100009</v>
       </c>
       <c r="B188" s="55" t="n">
         <v>1</v>
@@ -7918,30 +7938,30 @@
         <v>6</v>
       </c>
       <c r="F188" s="55" t="n">
-        <v>6500008</v>
+        <v>6500009</v>
       </c>
       <c r="G188" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_8</t>
+          <t>Goblin_Atlas_Hat_Hat_9</t>
         </is>
       </c>
       <c r="K188" s="55" t="n">
-        <v>60100008</v>
+        <v>60100009</v>
       </c>
       <c r="L188" s="55" t="inlineStr">
         <is>
-          <t>熊头帽</t>
+          <t>独眼罩</t>
         </is>
       </c>
       <c r="M188" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="55" t="n">
-        <v>60100009</v>
+        <v>60100010</v>
       </c>
       <c r="B189" s="55" t="n">
         <v>1</v>
@@ -7953,33 +7973,28 @@
         <v>6</v>
       </c>
       <c r="F189" s="55" t="n">
-        <v>6500009</v>
+        <v>6500010</v>
       </c>
       <c r="G189" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_9</t>
+          <t>Goblin_Atlas_Hat_Hat_10</t>
         </is>
       </c>
       <c r="K189" s="55" t="n">
-        <v>60100009</v>
+        <v>60100010</v>
       </c>
       <c r="L189" s="55" t="inlineStr">
         <is>
-          <t>独眼罩</t>
-        </is>
-      </c>
-      <c r="M189" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>皮头罩</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="55" t="n">
-        <v>60100010</v>
+        <v>60200001</v>
       </c>
       <c r="B190" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D190" s="55" t="n">
         <v>1</v>
@@ -7988,25 +8003,25 @@
         <v>6</v>
       </c>
       <c r="F190" s="55" t="n">
-        <v>6500010</v>
+        <v>6510001</v>
       </c>
       <c r="G190" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Hat_Hat_10</t>
+          <t>Goblin_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K190" s="55" t="n">
-        <v>60100010</v>
+        <v>60200001</v>
       </c>
       <c r="L190" s="55" t="inlineStr">
         <is>
-          <t>皮头罩</t>
+          <t>粉色胸罩</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="55" t="n">
-        <v>60200001</v>
+        <v>60200002</v>
       </c>
       <c r="B191" s="55" t="n">
         <v>2</v>
@@ -8018,28 +8033,28 @@
         <v>6</v>
       </c>
       <c r="F191" s="55" t="n">
-        <v>6510001</v>
+        <v>6510002</v>
       </c>
       <c r="G191" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Clothes_Clothes_1</t>
+          <t>Goblin_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K191" s="55" t="n">
-        <v>60200001</v>
+        <v>60200002</v>
       </c>
       <c r="L191" s="55" t="inlineStr">
         <is>
-          <t>粉色胸罩</t>
+          <t>布衣</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="55" t="n">
-        <v>60200002</v>
+        <v>60300001</v>
       </c>
       <c r="B192" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D192" s="55" t="n">
         <v>1</v>
@@ -8048,25 +8063,25 @@
         <v>6</v>
       </c>
       <c r="F192" s="55" t="n">
-        <v>6510002</v>
+        <v>6520001</v>
       </c>
       <c r="G192" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Clothes_Clothes_2</t>
+          <t>Goblin_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K192" s="55" t="n">
-        <v>60200002</v>
+        <v>60300001</v>
       </c>
       <c r="L192" s="55" t="inlineStr">
         <is>
-          <t>布衣</t>
+          <t>皮裤</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="55" t="n">
-        <v>60300001</v>
+        <v>60300002</v>
       </c>
       <c r="B193" s="55" t="n">
         <v>3</v>
@@ -8078,25 +8093,30 @@
         <v>6</v>
       </c>
       <c r="F193" s="55" t="n">
-        <v>6520001</v>
+        <v>6520002</v>
       </c>
       <c r="G193" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_1</t>
+          <t>Goblin_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K193" s="55" t="n">
-        <v>60300001</v>
+        <v>60300002</v>
       </c>
       <c r="L193" s="55" t="inlineStr">
         <is>
-          <t>皮裤</t>
+          <t>腰盔甲</t>
+        </is>
+      </c>
+      <c r="M193" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="55" t="n">
-        <v>60300002</v>
+        <v>60300003</v>
       </c>
       <c r="B194" s="55" t="n">
         <v>3</v>
@@ -8108,30 +8128,25 @@
         <v>6</v>
       </c>
       <c r="F194" s="55" t="n">
-        <v>6520002</v>
+        <v>6520003</v>
       </c>
       <c r="G194" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_2</t>
+          <t>Goblin_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K194" s="55" t="n">
-        <v>60300002</v>
+        <v>60300003</v>
       </c>
       <c r="L194" s="55" t="inlineStr">
         <is>
-          <t>腰盔甲</t>
-        </is>
-      </c>
-      <c r="M194" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>布裤子</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="55" t="n">
-        <v>60300003</v>
+        <v>60300004</v>
       </c>
       <c r="B195" s="55" t="n">
         <v>3</v>
@@ -8143,25 +8158,30 @@
         <v>6</v>
       </c>
       <c r="F195" s="55" t="n">
-        <v>6520003</v>
+        <v>6520004</v>
       </c>
       <c r="G195" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_3</t>
+          <t>Goblin_Atlas_Pants_Pants_4</t>
         </is>
       </c>
       <c r="K195" s="55" t="n">
-        <v>60300003</v>
+        <v>60300004</v>
       </c>
       <c r="L195" s="55" t="inlineStr">
         <is>
-          <t>布裤子</t>
+          <t>熊裤子</t>
+        </is>
+      </c>
+      <c r="M195" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="55" t="n">
-        <v>60300004</v>
+        <v>60300005</v>
       </c>
       <c r="B196" s="55" t="n">
         <v>3</v>
@@ -8173,33 +8193,36 @@
         <v>6</v>
       </c>
       <c r="F196" s="55" t="n">
-        <v>6520004</v>
+        <v>6520005</v>
       </c>
       <c r="G196" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_4</t>
+          <t>Goblin_Atlas_Pants_Pants_5</t>
         </is>
       </c>
       <c r="K196" s="55" t="n">
-        <v>60300004</v>
+        <v>60300005</v>
       </c>
       <c r="L196" s="55" t="inlineStr">
         <is>
-          <t>熊裤子</t>
+          <t>蓝裤子</t>
         </is>
       </c>
       <c r="M196" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="55" t="n">
-        <v>60300005</v>
+        <v>61010001</v>
       </c>
       <c r="B197" s="55" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C197" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="D197" s="55" t="n">
         <v>1</v>
@@ -8208,36 +8231,36 @@
         <v>6</v>
       </c>
       <c r="F197" s="55" t="n">
-        <v>6520005</v>
+        <v>6910001</v>
       </c>
       <c r="G197" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Pants_Pants_5</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_1</t>
         </is>
       </c>
       <c r="K197" s="55" t="n">
-        <v>60300005</v>
+        <v>61010001</v>
       </c>
       <c r="L197" s="55" t="inlineStr">
         <is>
-          <t>蓝裤子</t>
+          <t>金刀</t>
         </is>
       </c>
       <c r="M197" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="55" t="n">
-        <v>61010001</v>
+        <v>61010002</v>
       </c>
       <c r="B198" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C198" s="55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D198" s="55" t="n">
         <v>1</v>
@@ -8246,36 +8269,36 @@
         <v>6</v>
       </c>
       <c r="F198" s="55" t="n">
-        <v>6910001</v>
+        <v>6910002</v>
       </c>
       <c r="G198" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_1</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_2</t>
+        </is>
+      </c>
+      <c r="I198" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
         </is>
       </c>
       <c r="K198" s="55" t="n">
-        <v>61010001</v>
+        <v>61010002</v>
       </c>
       <c r="L198" s="55" t="inlineStr">
         <is>
-          <t>金刀</t>
-        </is>
-      </c>
-      <c r="M198" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>木弓</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="55" t="n">
-        <v>61010002</v>
+        <v>61010003</v>
       </c>
       <c r="B199" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C199" s="55" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D199" s="55" t="n">
         <v>1</v>
@@ -8284,30 +8307,30 @@
         <v>6</v>
       </c>
       <c r="F199" s="55" t="n">
-        <v>6910002</v>
+        <v>6910003</v>
       </c>
       <c r="G199" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_2</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_3</t>
         </is>
       </c>
       <c r="I199" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>StartSize:0.65</t>
         </is>
       </c>
       <c r="K199" s="55" t="n">
-        <v>61010002</v>
+        <v>61010003</v>
       </c>
       <c r="L199" s="55" t="inlineStr">
         <is>
-          <t>木弓</t>
+          <t>木法杖</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="55" t="n">
-        <v>61010003</v>
+        <v>61010004</v>
       </c>
       <c r="B200" s="55" t="n">
         <v>10</v>
@@ -8322,30 +8345,33 @@
         <v>6</v>
       </c>
       <c r="F200" s="55" t="n">
-        <v>6910003</v>
+        <v>6910004</v>
       </c>
       <c r="G200" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_3</t>
-        </is>
-      </c>
-      <c r="I200" s="55" t="inlineStr">
-        <is>
-          <t>StartSize:0.65</t>
-        </is>
+          <t>Goblin_Atlas_Weapon_Weapon_R_4</t>
+        </is>
+      </c>
+      <c r="H200" s="55" t="n">
+        <v>-45</v>
       </c>
       <c r="K200" s="55" t="n">
-        <v>61010003</v>
+        <v>61010004</v>
       </c>
       <c r="L200" s="55" t="inlineStr">
         <is>
-          <t>木法杖</t>
+          <t>骷髅法杖</t>
+        </is>
+      </c>
+      <c r="M200" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="55" t="n">
-        <v>61010004</v>
+        <v>61010005</v>
       </c>
       <c r="B201" s="55" t="n">
         <v>10</v>
@@ -8360,22 +8386,22 @@
         <v>6</v>
       </c>
       <c r="F201" s="55" t="n">
-        <v>6910004</v>
+        <v>6910005</v>
       </c>
       <c r="G201" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_4</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_5</t>
         </is>
       </c>
       <c r="H201" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K201" s="55" t="n">
-        <v>61010004</v>
+        <v>61010005</v>
       </c>
       <c r="L201" s="55" t="inlineStr">
         <is>
-          <t>骷髅法杖</t>
+          <t>十字法杖</t>
         </is>
       </c>
       <c r="M201" s="55" t="inlineStr">
@@ -8386,7 +8412,7 @@
     </row>
     <row r="202">
       <c r="A202" s="55" t="n">
-        <v>61010005</v>
+        <v>61010006</v>
       </c>
       <c r="B202" s="55" t="n">
         <v>10</v>
@@ -8401,33 +8427,33 @@
         <v>6</v>
       </c>
       <c r="F202" s="55" t="n">
-        <v>6910005</v>
+        <v>6910006</v>
       </c>
       <c r="G202" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_5</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_6</t>
         </is>
       </c>
       <c r="H202" s="55" t="n">
         <v>-45</v>
       </c>
       <c r="K202" s="55" t="n">
-        <v>61010005</v>
+        <v>61010006</v>
       </c>
       <c r="L202" s="55" t="inlineStr">
         <is>
-          <t>十字法杖</t>
+          <t>蔚蓝法棍</t>
         </is>
       </c>
       <c r="M202" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="55" t="n">
-        <v>61010006</v>
+        <v>61010007</v>
       </c>
       <c r="B203" s="55" t="n">
         <v>10</v>
@@ -8442,39 +8468,36 @@
         <v>6</v>
       </c>
       <c r="F203" s="55" t="n">
-        <v>6910006</v>
+        <v>6910007</v>
       </c>
       <c r="G203" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_6</t>
-        </is>
-      </c>
-      <c r="H203" s="55" t="n">
-        <v>-45</v>
+          <t>Goblin_Atlas_Weapon_Weapon_R_7</t>
+        </is>
       </c>
       <c r="K203" s="55" t="n">
-        <v>61010006</v>
+        <v>61010007</v>
       </c>
       <c r="L203" s="55" t="inlineStr">
         <is>
-          <t>蔚蓝法棍</t>
+          <t>死亡之书</t>
         </is>
       </c>
       <c r="M203" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="55" t="n">
-        <v>61010007</v>
+        <v>61010008</v>
       </c>
       <c r="B204" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C204" s="55" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D204" s="55" t="n">
         <v>1</v>
@@ -8483,36 +8506,36 @@
         <v>6</v>
       </c>
       <c r="F204" s="55" t="n">
-        <v>6910007</v>
+        <v>6910008</v>
       </c>
       <c r="G204" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_7</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_8</t>
         </is>
       </c>
       <c r="K204" s="55" t="n">
-        <v>61010007</v>
+        <v>61010008</v>
       </c>
       <c r="L204" s="55" t="inlineStr">
         <is>
-          <t>死亡之书</t>
+          <t>猩红之酒</t>
         </is>
       </c>
       <c r="M204" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="55" t="n">
-        <v>61010008</v>
+        <v>61010009</v>
       </c>
       <c r="B205" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C205" s="55" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D205" s="55" t="n">
         <v>1</v>
@@ -8521,30 +8544,30 @@
         <v>6</v>
       </c>
       <c r="F205" s="55" t="n">
-        <v>6910008</v>
+        <v>6910009</v>
       </c>
       <c r="G205" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_8</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_9</t>
         </is>
       </c>
       <c r="K205" s="55" t="n">
-        <v>61010008</v>
+        <v>61010009</v>
       </c>
       <c r="L205" s="55" t="inlineStr">
         <is>
-          <t>猩红之酒</t>
+          <t>铁剑</t>
         </is>
       </c>
       <c r="M205" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="55" t="n">
-        <v>61010009</v>
+        <v>61010010</v>
       </c>
       <c r="B206" s="55" t="n">
         <v>10</v>
@@ -8559,30 +8582,30 @@
         <v>6</v>
       </c>
       <c r="F206" s="55" t="n">
-        <v>6910009</v>
+        <v>6910010</v>
       </c>
       <c r="G206" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_9</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_10</t>
         </is>
       </c>
       <c r="K206" s="55" t="n">
-        <v>61010009</v>
+        <v>61010010</v>
       </c>
       <c r="L206" s="55" t="inlineStr">
         <is>
-          <t>铁剑</t>
+          <t>三叉戟</t>
         </is>
       </c>
       <c r="M206" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="55" t="n">
-        <v>61010010</v>
+        <v>61010011</v>
       </c>
       <c r="B207" s="55" t="n">
         <v>10</v>
@@ -8597,19 +8620,19 @@
         <v>6</v>
       </c>
       <c r="F207" s="55" t="n">
-        <v>6910010</v>
+        <v>6910011</v>
       </c>
       <c r="G207" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_10</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_11</t>
         </is>
       </c>
       <c r="K207" s="55" t="n">
-        <v>61010010</v>
+        <v>61010011</v>
       </c>
       <c r="L207" s="55" t="inlineStr">
         <is>
-          <t>三叉戟</t>
+          <t>华丽刺剑</t>
         </is>
       </c>
       <c r="M207" s="55" t="inlineStr">
@@ -8620,7 +8643,7 @@
     </row>
     <row r="208">
       <c r="A208" s="55" t="n">
-        <v>61010011</v>
+        <v>61010012</v>
       </c>
       <c r="B208" s="55" t="n">
         <v>10</v>
@@ -8635,36 +8658,36 @@
         <v>6</v>
       </c>
       <c r="F208" s="55" t="n">
-        <v>6910011</v>
+        <v>6910012</v>
       </c>
       <c r="G208" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_11</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_12</t>
         </is>
       </c>
       <c r="K208" s="55" t="n">
-        <v>61010011</v>
+        <v>61010012</v>
       </c>
       <c r="L208" s="55" t="inlineStr">
         <is>
-          <t>华丽刺剑</t>
+          <t>拐杖剑</t>
         </is>
       </c>
       <c r="M208" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="55" t="n">
-        <v>61010012</v>
+        <v>61010013</v>
       </c>
       <c r="B209" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C209" s="55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D209" s="55" t="n">
         <v>1</v>
@@ -8673,19 +8696,24 @@
         <v>6</v>
       </c>
       <c r="F209" s="55" t="n">
-        <v>6910012</v>
+        <v>6910013</v>
       </c>
       <c r="G209" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_12</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_13</t>
+        </is>
+      </c>
+      <c r="I209" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
         </is>
       </c>
       <c r="K209" s="55" t="n">
-        <v>61010012</v>
+        <v>61010013</v>
       </c>
       <c r="L209" s="55" t="inlineStr">
         <is>
-          <t>拐杖剑</t>
+          <t>木铁弓</t>
         </is>
       </c>
       <c r="M209" s="55" t="inlineStr">
@@ -8696,7 +8724,7 @@
     </row>
     <row r="210">
       <c r="A210" s="55" t="n">
-        <v>61010013</v>
+        <v>61010014</v>
       </c>
       <c r="B210" s="55" t="n">
         <v>10</v>
@@ -8711,11 +8739,11 @@
         <v>6</v>
       </c>
       <c r="F210" s="55" t="n">
-        <v>6910013</v>
+        <v>6910014</v>
       </c>
       <c r="G210" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_13</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_14</t>
         </is>
       </c>
       <c r="I210" s="55" t="inlineStr">
@@ -8724,11 +8752,11 @@
         </is>
       </c>
       <c r="K210" s="55" t="n">
-        <v>61010013</v>
+        <v>61010014</v>
       </c>
       <c r="L210" s="55" t="inlineStr">
         <is>
-          <t>木铁弓</t>
+          <t>直弓</t>
         </is>
       </c>
       <c r="M210" s="55" t="inlineStr">
@@ -8739,7 +8767,7 @@
     </row>
     <row r="211">
       <c r="A211" s="55" t="n">
-        <v>61010014</v>
+        <v>61010015</v>
       </c>
       <c r="B211" s="55" t="n">
         <v>10</v>
@@ -8754,11 +8782,11 @@
         <v>6</v>
       </c>
       <c r="F211" s="55" t="n">
-        <v>6910014</v>
+        <v>6910015</v>
       </c>
       <c r="G211" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_14</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_15</t>
         </is>
       </c>
       <c r="I211" s="55" t="inlineStr">
@@ -8767,22 +8795,22 @@
         </is>
       </c>
       <c r="K211" s="55" t="n">
-        <v>61010014</v>
+        <v>61010015</v>
       </c>
       <c r="L211" s="55" t="inlineStr">
         <is>
-          <t>直弓</t>
+          <t>魔力弓</t>
         </is>
       </c>
       <c r="M211" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="55" t="n">
-        <v>61010015</v>
+        <v>61010016</v>
       </c>
       <c r="B212" s="55" t="n">
         <v>10</v>
@@ -8797,11 +8825,11 @@
         <v>6</v>
       </c>
       <c r="F212" s="55" t="n">
-        <v>6910015</v>
+        <v>6910016</v>
       </c>
       <c r="G212" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_15</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_16</t>
         </is>
       </c>
       <c r="I212" s="55" t="inlineStr">
@@ -8810,11 +8838,11 @@
         </is>
       </c>
       <c r="K212" s="55" t="n">
-        <v>61010015</v>
+        <v>61010016</v>
       </c>
       <c r="L212" s="55" t="inlineStr">
         <is>
-          <t>魔力弓</t>
+          <t>金闪闪弓</t>
         </is>
       </c>
       <c r="M212" s="55" t="inlineStr">
@@ -8825,13 +8853,13 @@
     </row>
     <row r="213">
       <c r="A213" s="55" t="n">
-        <v>61010016</v>
+        <v>61010017</v>
       </c>
       <c r="B213" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C213" s="55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D213" s="55" t="n">
         <v>1</v>
@@ -8840,35 +8868,25 @@
         <v>6</v>
       </c>
       <c r="F213" s="55" t="n">
-        <v>6910016</v>
+        <v>6910017</v>
       </c>
       <c r="G213" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_16</t>
-        </is>
-      </c>
-      <c r="I213" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_17</t>
         </is>
       </c>
       <c r="K213" s="55" t="n">
-        <v>61010016</v>
+        <v>61010017</v>
       </c>
       <c r="L213" s="55" t="inlineStr">
         <is>
-          <t>金闪闪弓</t>
-        </is>
-      </c>
-      <c r="M213" s="55" t="inlineStr">
-        <is>
-          <t>4,5,6</t>
+          <t>炸弹</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="55" t="n">
-        <v>61010017</v>
+        <v>61010018</v>
       </c>
       <c r="B214" s="55" t="n">
         <v>10</v>
@@ -8883,25 +8901,30 @@
         <v>6</v>
       </c>
       <c r="F214" s="55" t="n">
-        <v>6910017</v>
+        <v>6910018</v>
       </c>
       <c r="G214" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_17</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_18</t>
         </is>
       </c>
       <c r="K214" s="55" t="n">
-        <v>61010017</v>
+        <v>61010018</v>
       </c>
       <c r="L214" s="55" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>火药</t>
+        </is>
+      </c>
+      <c r="M214" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="55" t="n">
-        <v>61010018</v>
+        <v>61010019</v>
       </c>
       <c r="B215" s="55" t="n">
         <v>10</v>
@@ -8916,30 +8939,30 @@
         <v>6</v>
       </c>
       <c r="F215" s="55" t="n">
-        <v>6910018</v>
+        <v>6910019</v>
       </c>
       <c r="G215" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_18</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_19</t>
         </is>
       </c>
       <c r="K215" s="55" t="n">
-        <v>61010018</v>
+        <v>61010019</v>
       </c>
       <c r="L215" s="55" t="inlineStr">
         <is>
-          <t>火药</t>
+          <t>危险药剂</t>
         </is>
       </c>
       <c r="M215" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>4,5,6</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="55" t="n">
-        <v>61010019</v>
+        <v>61010020</v>
       </c>
       <c r="B216" s="55" t="n">
         <v>10</v>
@@ -8954,19 +8977,19 @@
         <v>6</v>
       </c>
       <c r="F216" s="55" t="n">
-        <v>6910019</v>
+        <v>6910020</v>
       </c>
       <c r="G216" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_19</t>
+          <t>Goblin_Atlas_Weapon_Weapon_R_20</t>
         </is>
       </c>
       <c r="K216" s="55" t="n">
-        <v>61010019</v>
+        <v>61010020</v>
       </c>
       <c r="L216" s="55" t="inlineStr">
         <is>
-          <t>危险药剂</t>
+          <t>奥里给</t>
         </is>
       </c>
       <c r="M216" s="55" t="inlineStr">
@@ -8977,48 +9000,45 @@
     </row>
     <row r="217">
       <c r="A217" s="55" t="n">
-        <v>61010020</v>
+        <v>70100001</v>
       </c>
       <c r="B217" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C217" s="55" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D217" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E217" s="55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F217" s="55" t="n">
-        <v>6910020</v>
+        <v>7500001</v>
       </c>
       <c r="G217" s="55" t="inlineStr">
         <is>
-          <t>Goblin_Atlas_Weapon_Weapon_R_20</t>
+          <t>Orc_Atlas_Hat_Hat_1</t>
         </is>
       </c>
       <c r="K217" s="55" t="n">
-        <v>61010020</v>
+        <v>70100001</v>
       </c>
       <c r="L217" s="55" t="inlineStr">
         <is>
-          <t>奥里给</t>
+          <t>皮套帽</t>
         </is>
       </c>
       <c r="M217" s="55" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="55" t="n">
-        <v>70100001</v>
+        <v>70200001</v>
       </c>
       <c r="B218" s="55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D218" s="55" t="n">
         <v>1</v>
@@ -9027,19 +9047,19 @@
         <v>7</v>
       </c>
       <c r="F218" s="55" t="n">
-        <v>7500001</v>
+        <v>7510001</v>
       </c>
       <c r="G218" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Hat_Hat_1</t>
+          <t>Orc_Atlas_Clothes_Clothes_1</t>
         </is>
       </c>
       <c r="K218" s="55" t="n">
-        <v>70100001</v>
+        <v>70200001</v>
       </c>
       <c r="L218" s="55" t="inlineStr">
         <is>
-          <t>皮套帽</t>
+          <t>带刺肩甲</t>
         </is>
       </c>
       <c r="M218" s="55" t="inlineStr">
@@ -9050,7 +9070,7 @@
     </row>
     <row r="219">
       <c r="A219" s="55" t="n">
-        <v>70200001</v>
+        <v>70200002</v>
       </c>
       <c r="B219" s="55" t="n">
         <v>2</v>
@@ -9062,19 +9082,19 @@
         <v>7</v>
       </c>
       <c r="F219" s="55" t="n">
-        <v>7510001</v>
+        <v>7510002</v>
       </c>
       <c r="G219" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Clothes_Clothes_1</t>
+          <t>Orc_Atlas_Clothes_Clothes_2</t>
         </is>
       </c>
       <c r="K219" s="55" t="n">
-        <v>70200001</v>
+        <v>70200002</v>
       </c>
       <c r="L219" s="55" t="inlineStr">
         <is>
-          <t>带刺肩甲</t>
+          <t>皮甲</t>
         </is>
       </c>
       <c r="M219" s="55" t="inlineStr">
@@ -9085,10 +9105,10 @@
     </row>
     <row r="220">
       <c r="A220" s="55" t="n">
-        <v>70200002</v>
+        <v>70300001</v>
       </c>
       <c r="B220" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D220" s="55" t="n">
         <v>1</v>
@@ -9097,30 +9117,30 @@
         <v>7</v>
       </c>
       <c r="F220" s="55" t="n">
-        <v>7510002</v>
+        <v>7520001</v>
       </c>
       <c r="G220" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Clothes_Clothes_2</t>
+          <t>Orc_Atlas_Pants_Pants_1</t>
         </is>
       </c>
       <c r="K220" s="55" t="n">
-        <v>70200002</v>
+        <v>70300001</v>
       </c>
       <c r="L220" s="55" t="inlineStr">
         <is>
-          <t>皮甲</t>
+          <t>华丽皮带</t>
         </is>
       </c>
       <c r="M220" s="55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="55" t="n">
-        <v>70300001</v>
+        <v>70300002</v>
       </c>
       <c r="B221" s="55" t="n">
         <v>3</v>
@@ -9132,30 +9152,25 @@
         <v>7</v>
       </c>
       <c r="F221" s="55" t="n">
-        <v>7520001</v>
+        <v>7520002</v>
       </c>
       <c r="G221" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Pants_Pants_1</t>
+          <t>Orc_Atlas_Pants_Pants_2</t>
         </is>
       </c>
       <c r="K221" s="55" t="n">
-        <v>70300001</v>
+        <v>70300002</v>
       </c>
       <c r="L221" s="55" t="inlineStr">
         <is>
-          <t>华丽皮带</t>
-        </is>
-      </c>
-      <c r="M221" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>布腰带</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="55" t="n">
-        <v>70300002</v>
+        <v>70300003</v>
       </c>
       <c r="B222" s="55" t="n">
         <v>3</v>
@@ -9167,25 +9182,30 @@
         <v>7</v>
       </c>
       <c r="F222" s="55" t="n">
-        <v>7520002</v>
+        <v>7520003</v>
       </c>
       <c r="G222" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Pants_Pants_2</t>
+          <t>Orc_Atlas_Pants_Pants_3</t>
         </is>
       </c>
       <c r="K222" s="55" t="n">
-        <v>70300002</v>
+        <v>70300003</v>
       </c>
       <c r="L222" s="55" t="inlineStr">
         <is>
-          <t>布腰带</t>
+          <t>金属裤带</t>
+        </is>
+      </c>
+      <c r="M222" s="55" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="55" t="n">
-        <v>70300003</v>
+        <v>70300004</v>
       </c>
       <c r="B223" s="55" t="n">
         <v>3</v>
@@ -9197,19 +9217,19 @@
         <v>7</v>
       </c>
       <c r="F223" s="55" t="n">
-        <v>7520003</v>
+        <v>7520004</v>
       </c>
       <c r="G223" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Pants_Pants_3</t>
+          <t>Orc_Atlas_Pants_Pants_4</t>
         </is>
       </c>
       <c r="K223" s="55" t="n">
-        <v>70300003</v>
+        <v>70300004</v>
       </c>
       <c r="L223" s="55" t="inlineStr">
         <is>
-          <t>金属裤带</t>
+          <t>皮腰带</t>
         </is>
       </c>
       <c r="M223" s="55" t="inlineStr">
@@ -9220,10 +9240,13 @@
     </row>
     <row r="224">
       <c r="A224" s="55" t="n">
-        <v>70300004</v>
+        <v>71000001</v>
       </c>
       <c r="B224" s="55" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C224" s="55" t="n">
+        <v>8</v>
       </c>
       <c r="D224" s="55" t="n">
         <v>1</v>
@@ -9232,30 +9255,30 @@
         <v>7</v>
       </c>
       <c r="F224" s="55" t="n">
-        <v>7520004</v>
+        <v>7900001</v>
       </c>
       <c r="G224" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Pants_Pants_4</t>
+          <t>Orc_Atlas_Weapon_Weapon_L_1</t>
+        </is>
+      </c>
+      <c r="I224" s="55" t="inlineStr">
+        <is>
+          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1.5</t>
         </is>
       </c>
       <c r="K224" s="55" t="n">
-        <v>70300004</v>
+        <v>71000001</v>
       </c>
       <c r="L224" s="55" t="inlineStr">
         <is>
-          <t>皮腰带</t>
-        </is>
-      </c>
-      <c r="M224" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>木制标枪</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="55" t="n">
-        <v>71000001</v>
+        <v>71000002</v>
       </c>
       <c r="B225" s="55" t="n">
         <v>10</v>
@@ -9270,30 +9293,35 @@
         <v>7</v>
       </c>
       <c r="F225" s="55" t="n">
-        <v>7900001</v>
+        <v>7900002</v>
       </c>
       <c r="G225" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_L_1</t>
+          <t>Orc_Atlas_Weapon_Weapon_L_2</t>
         </is>
       </c>
       <c r="I225" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1.5</t>
+          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
         </is>
       </c>
       <c r="K225" s="55" t="n">
-        <v>71000001</v>
+        <v>71000002</v>
       </c>
       <c r="L225" s="55" t="inlineStr">
         <is>
-          <t>木制标枪</t>
+          <t>骨制标枪</t>
+        </is>
+      </c>
+      <c r="M225" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="55" t="n">
-        <v>71000002</v>
+        <v>71000003</v>
       </c>
       <c r="B226" s="55" t="n">
         <v>10</v>
@@ -9308,35 +9336,35 @@
         <v>7</v>
       </c>
       <c r="F226" s="55" t="n">
-        <v>7900002</v>
+        <v>7900003</v>
       </c>
       <c r="G226" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_L_2</t>
+          <t>Orc_Atlas_Weapon_Weapon_L_3</t>
         </is>
       </c>
       <c r="I226" s="55" t="inlineStr">
         <is>
-          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_3&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
         </is>
       </c>
       <c r="K226" s="55" t="n">
-        <v>71000002</v>
+        <v>71000003</v>
       </c>
       <c r="L226" s="55" t="inlineStr">
         <is>
-          <t>骨制标枪</t>
+          <t>铁制三叉戟</t>
         </is>
       </c>
       <c r="M226" s="55" t="inlineStr">
         <is>
-          <t>3,4,5,6</t>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="55" t="n">
-        <v>71000003</v>
+        <v>71010001</v>
       </c>
       <c r="B227" s="55" t="n">
         <v>10</v>
@@ -9351,35 +9379,25 @@
         <v>7</v>
       </c>
       <c r="F227" s="55" t="n">
-        <v>7900003</v>
+        <v>7910001</v>
       </c>
       <c r="G227" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_L_3</t>
-        </is>
-      </c>
-      <c r="I227" s="55" t="inlineStr">
-        <is>
-          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_3&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_1</t>
         </is>
       </c>
       <c r="K227" s="55" t="n">
-        <v>71000003</v>
+        <v>71010001</v>
       </c>
       <c r="L227" s="55" t="inlineStr">
         <is>
-          <t>铁制三叉戟</t>
-        </is>
-      </c>
-      <c r="M227" s="55" t="inlineStr">
-        <is>
-          <t>2,3,4,5,6</t>
+          <t>血腥骨锤</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="55" t="n">
-        <v>71010001</v>
+        <v>71010002</v>
       </c>
       <c r="B228" s="55" t="n">
         <v>10</v>
@@ -9394,25 +9412,25 @@
         <v>7</v>
       </c>
       <c r="F228" s="55" t="n">
-        <v>7910001</v>
+        <v>7910002</v>
       </c>
       <c r="G228" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_1</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_2</t>
         </is>
       </c>
       <c r="K228" s="55" t="n">
-        <v>71010001</v>
+        <v>71010002</v>
       </c>
       <c r="L228" s="55" t="inlineStr">
         <is>
-          <t>血腥骨锤</t>
+          <t>石斧</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="55" t="n">
-        <v>71010002</v>
+        <v>71010003</v>
       </c>
       <c r="B229" s="55" t="n">
         <v>10</v>
@@ -9427,31 +9445,36 @@
         <v>7</v>
       </c>
       <c r="F229" s="55" t="n">
-        <v>7910002</v>
+        <v>7910003</v>
       </c>
       <c r="G229" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_2</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_3</t>
         </is>
       </c>
       <c r="K229" s="55" t="n">
-        <v>71010002</v>
+        <v>71010003</v>
       </c>
       <c r="L229" s="55" t="inlineStr">
         <is>
-          <t>石斧</t>
+          <t>水晶劈刀</t>
+        </is>
+      </c>
+      <c r="M229" s="55" t="inlineStr">
+        <is>
+          <t>3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="55" t="n">
-        <v>71010003</v>
+        <v>71010004</v>
       </c>
       <c r="B230" s="55" t="n">
         <v>10</v>
       </c>
       <c r="C230" s="55" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D230" s="55" t="n">
         <v>1</v>
@@ -9460,19 +9483,19 @@
         <v>7</v>
       </c>
       <c r="F230" s="55" t="n">
-        <v>7910003</v>
+        <v>7910004</v>
       </c>
       <c r="G230" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_3</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_4</t>
         </is>
       </c>
       <c r="K230" s="55" t="n">
-        <v>71010003</v>
+        <v>71010004</v>
       </c>
       <c r="L230" s="55" t="inlineStr">
         <is>
-          <t>水晶劈刀</t>
+          <t>黑色法杖</t>
         </is>
       </c>
       <c r="M230" s="55" t="inlineStr">
@@ -9483,7 +9506,7 @@
     </row>
     <row r="231">
       <c r="A231" s="55" t="n">
-        <v>71010004</v>
+        <v>71010005</v>
       </c>
       <c r="B231" s="55" t="n">
         <v>10</v>
@@ -9498,19 +9521,19 @@
         <v>7</v>
       </c>
       <c r="F231" s="55" t="n">
-        <v>7910004</v>
+        <v>7910005</v>
       </c>
       <c r="G231" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_4</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_5</t>
         </is>
       </c>
       <c r="K231" s="55" t="n">
-        <v>71010004</v>
+        <v>71010005</v>
       </c>
       <c r="L231" s="55" t="inlineStr">
         <is>
-          <t>黑色法杖</t>
+          <t>诡异魔法书</t>
         </is>
       </c>
       <c r="M231" s="55" t="inlineStr">
@@ -9521,7 +9544,7 @@
     </row>
     <row r="232">
       <c r="A232" s="55" t="n">
-        <v>71010005</v>
+        <v>71010006</v>
       </c>
       <c r="B232" s="55" t="n">
         <v>10</v>
@@ -9536,85 +9559,47 @@
         <v>7</v>
       </c>
       <c r="F232" s="55" t="n">
-        <v>7910005</v>
+        <v>7910006</v>
       </c>
       <c r="G232" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_5</t>
+          <t>Orc_Atlas_Weapon_Weapon_R_6</t>
         </is>
       </c>
       <c r="K232" s="55" t="n">
-        <v>71010005</v>
+        <v>71010006</v>
       </c>
       <c r="L232" s="55" t="inlineStr">
         <is>
-          <t>诡异魔法书</t>
-        </is>
-      </c>
-      <c r="M232" s="55" t="inlineStr">
-        <is>
-          <t>3,4,5,6</t>
+          <t>木制法杖</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="55" t="n">
-        <v>71010006</v>
+        <v>200001</v>
       </c>
       <c r="B233" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C233" s="55" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D233" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E233" s="55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F233" s="55" t="n">
-        <v>7910006</v>
+        <v>0</v>
       </c>
       <c r="G233" s="55" t="inlineStr">
         <is>
-          <t>Orc_Atlas_Weapon_Weapon_R_6</t>
+          <t>Item_Juicer_1</t>
         </is>
       </c>
       <c r="K233" s="55" t="n">
-        <v>71010006</v>
+        <v>200001</v>
       </c>
       <c r="L233" s="55" t="inlineStr">
-        <is>
-          <t>木制法杖</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="55" t="n">
-        <v>200001</v>
-      </c>
-      <c r="B234" s="55" t="n">
-        <v>11</v>
-      </c>
-      <c r="D234" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E234" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F234" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" s="55" t="inlineStr">
-        <is>
-          <t>Item_Juicer_1</t>
-        </is>
-      </c>
-      <c r="K234" s="55" t="n">
-        <v>200001</v>
-      </c>
-      <c r="L234" s="55" t="inlineStr">
         <is>
           <t>魔汁(榨汁产物,对魔物使用后增加经验)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -1182,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N233"/>
+  <dimension ref="A1:N234"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="10.75" customWidth="1" style="56" min="1" max="1"/>
@@ -1265,7 +1265,7 @@
           <t>reward_rarity</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="55" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -1337,7 +1337,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="55" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1409,7 +1409,7 @@
           <t>奖励可出的稀有度白名单(逗号分隔,空=全稀有度) 1N 2R 3SR 4SSR 5UR 6L</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="55" t="inlineStr">
         <is>
           <t>道具来源白名单(逗号分隔枚举值,空=默认来源) 1=征服模式奖励</t>
         </is>
@@ -9602,6 +9602,44 @@
       <c r="L233" s="55" t="inlineStr">
         <is>
           <t>魔汁(榨汁产物,对魔物使用后增加经验)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>11020016</v>
+      </c>
+      <c r="B234" t="n">
+        <v>10</v>
+      </c>
+      <c r="C234" t="n">
+        <v>10</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1920016</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Human_Atlas_Weapon_Weapon_LR_16</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>11020016</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>长枪</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G6" s="55" t="inlineStr">
         <is>
-          <t>Item_RestorePotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="K6" s="55" t="n">
@@ -9606,38 +9606,38 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
+      <c r="A234" s="55" t="n">
         <v>11020016</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B234" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="C234" t="n">
+      <c r="C234" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="D234" t="n">
-        <v>1</v>
-      </c>
-      <c r="E234" t="n">
-        <v>1</v>
-      </c>
-      <c r="F234" t="n">
+      <c r="D234" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" s="55" t="n">
         <v>1920016</v>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G234" s="55" t="inlineStr">
         <is>
           <t>Human_Atlas_Weapon_Weapon_LR_16</t>
         </is>
       </c>
-      <c r="K234" t="n">
+      <c r="K234" s="55" t="n">
         <v>11020016</v>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="L234" s="55" t="inlineStr">
         <is>
           <t>长枪</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr">
+      <c r="M234" s="55" t="inlineStr">
         <is>
           <t>2,3,4,5,6</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -1478,7 +1478,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E6" s="55" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G6" s="55" t="inlineStr">
         <is>
-          <t>Item_Potion_1</t>
+          <t>Item_Potion_2</t>
         </is>
       </c>
       <c r="K6" s="55" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -1182,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N256"/>
+  <dimension ref="A1:O256"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="10.75" customWidth="1" style="56" min="1" max="1"/>
@@ -1270,6 +1270,11 @@
           <t>source</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>use_sound</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="55" t="inlineStr">
@@ -1342,6 +1347,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="55" t="inlineStr">
@@ -1412,6 +1422,11 @@
       <c r="N3" s="55" t="inlineStr">
         <is>
           <t>道具来源白名单(逗号分隔枚举值,空=默认来源) 1=征服模式奖励</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>道具使用音效ID(音频表id,0或空=不播放;使用成功时播放)</t>
         </is>
       </c>
     </row>
@@ -1499,6 +1514,9 @@
           <t>幻原药(清除幻化,恢复原本形象)</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="55" t="n">
@@ -1529,6 +1547,9 @@
           <t>升级药水(GM道具,对普通魔物使用后等级+1并进入加点界面)</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="55" t="n">
@@ -1559,6 +1580,9 @@
           <t>降级药水(GM道具,对普通魔物使用后等级-1并随机回退本级加点)</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="55" t="n">
@@ -1589,6 +1613,9 @@
           <t>升阶药水(GM道具,对普通魔物使用后稀有度+1并随机获得新档位BUFF)</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="55" t="n">
@@ -1619,6 +1646,9 @@
           <t>降阶药水(GM道具,对普通魔物使用后稀有度-1并移除高档位BUFF)</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="55" t="n">
@@ -1654,6 +1684,9 @@
           <t>升级药水+2(GM道具,对普通魔物使用后等级最多+2并进入加点界面)</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="55" t="n">
@@ -1689,6 +1722,9 @@
           <t>升级药水+3(GM道具,对普通魔物使用后等级最多+3并进入加点界面)</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="55" t="n">
@@ -1724,6 +1760,9 @@
           <t>升级药水+4(GM道具,对普通魔物使用后等级最多+4并进入加点界面)</t>
         </is>
       </c>
+      <c r="O13" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="55" t="n">
@@ -1759,6 +1798,9 @@
           <t>升级药水+5(GM道具,对普通魔物使用后等级最多+5并进入加点界面)</t>
         </is>
       </c>
+      <c r="O14" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="55" t="n">
@@ -1794,6 +1836,9 @@
           <t>升级药水+6(GM道具,对普通魔物使用后等级最多+6并进入加点界面)</t>
         </is>
       </c>
+      <c r="O15" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="55" t="n">
@@ -1829,6 +1874,9 @@
           <t>升级药水+7(GM道具,对普通魔物使用后等级最多+7并进入加点界面)</t>
         </is>
       </c>
+      <c r="O16" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="55" t="n">
@@ -1864,6 +1912,9 @@
           <t>升级药水+8(GM道具,对普通魔物使用后等级最多+8并进入加点界面)</t>
         </is>
       </c>
+      <c r="O17" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="55" t="n">
@@ -1899,6 +1950,9 @@
           <t>升级药水+9(GM道具,对普通魔物使用后等级最多+9并进入加点界面)</t>
         </is>
       </c>
+      <c r="O18" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="55" t="n">
@@ -1934,6 +1988,9 @@
           <t>升级药水+10(GM道具,对普通魔物使用后等级最多+10并进入加点界面)</t>
         </is>
       </c>
+      <c r="O19" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="55" t="n">
@@ -1969,6 +2026,9 @@
           <t>降级药水-2(GM道具,对普通魔物使用后等级最多-2并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O20" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="55" t="n">
@@ -2004,6 +2064,9 @@
           <t>降级药水-3(GM道具,对普通魔物使用后等级最多-3并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O21" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="55" t="n">
@@ -2039,6 +2102,9 @@
           <t>降级药水-4(GM道具,对普通魔物使用后等级最多-4并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O22" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="55" t="n">
@@ -2074,6 +2140,9 @@
           <t>降级药水-5(GM道具,对普通魔物使用后等级最多-5并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O23" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="55" t="n">
@@ -2109,6 +2178,9 @@
           <t>降级药水-6(GM道具,对普通魔物使用后等级最多-6并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O24" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="55" t="n">
@@ -2144,6 +2216,9 @@
           <t>降级药水-7(GM道具,对普通魔物使用后等级最多-7并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O25" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="55" t="n">
@@ -2179,6 +2254,9 @@
           <t>降级药水-8(GM道具,对普通魔物使用后等级最多-8并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O26" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="55" t="n">
@@ -2214,6 +2292,9 @@
           <t>降级药水-9(GM道具,对普通魔物使用后等级最多-9并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O27" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="55" t="n">
@@ -2249,6 +2330,9 @@
           <t>降级药水-10(GM道具,对普通魔物使用后等级最多-10并随机回退对应加点)</t>
         </is>
       </c>
+      <c r="O28" t="n">
+        <v>470001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="55" t="n">
@@ -10353,6 +10437,9 @@
         <is>
           <t>魔汁(榨汁产物,对魔物使用后增加经验)</t>
         </is>
+      </c>
+      <c r="O255" t="n">
+        <v>470001</v>
       </c>
     </row>
     <row r="256">
